--- a/storage/app/estimateTemplate/all.xlsx
+++ b/storage/app/estimateTemplate/all.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\ohno\eruful\mitumo\storage\app\estimateTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AC2F04D-FEBF-4208-98DE-09BB5C7FE150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C6CF19B-00DC-4CFC-9F8B-58715B970AF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{5432EA10-F847-46F9-8033-2A67B2C19C32}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{5432EA10-F847-46F9-8033-2A67B2C19C32}"/>
   </bookViews>
   <sheets>
-    <sheet name="普通" sheetId="2" r:id="rId1"/>
+    <sheet name="普通" sheetId="11" r:id="rId1"/>
     <sheet name="総合" sheetId="3" r:id="rId2"/>
     <sheet name="普通&amp;総合" sheetId="4" r:id="rId3"/>
     <sheet name="おすすめ(普通)" sheetId="5" r:id="rId4"/>
@@ -1800,6 +1800,24 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="31" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="30" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="31" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="32" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="32" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="30" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
     <xf numFmtId="179" fontId="10" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1812,26 +1830,8 @@
     <xf numFmtId="0" fontId="19" fillId="2" borderId="31" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="distributed" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="30" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="32" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="31" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="32" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="32" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="30" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
     </xf>
@@ -1907,16 +1907,67 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1929,57 +1980,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2049,6 +2049,9 @@
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2075,9 +2078,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2653,21 +2653,21 @@
     <xdr:from>
       <xdr:col>14</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>168519</xdr:rowOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>376497</xdr:colOff>
+      <xdr:colOff>375036</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>146537</xdr:rowOff>
+      <xdr:rowOff>145569</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
+        <xdr:cNvPr id="2" name="図 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8EE48364-5330-DA83-7A8B-657F110B8C4D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{093AA538-3C88-40D9-B1E1-5A3619F84BBC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2676,21 +2676,15 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5334000" y="337038"/>
-          <a:ext cx="1519497" cy="315057"/>
+          <a:off x="5334000" y="342900"/>
+          <a:ext cx="1518036" cy="317019"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3341,7 +3335,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFC78FD0-9C26-49E8-BEC9-BF13FF00AA26}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC9CAE76-357B-4E12-9E06-DC044098D2D2}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -3365,16 +3359,16 @@
     </row>
     <row r="3" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A3" s="3"/>
-      <c r="O3" s="145"/>
-      <c r="P3" s="145"/>
-      <c r="Q3" s="145"/>
-      <c r="R3" s="145"/>
+      <c r="O3" s="136"/>
+      <c r="P3" s="136"/>
+      <c r="Q3" s="136"/>
+      <c r="R3" s="136"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="O4" s="145"/>
-      <c r="P4" s="145"/>
-      <c r="Q4" s="145"/>
-      <c r="R4" s="145"/>
+      <c r="O4" s="136"/>
+      <c r="P4" s="136"/>
+      <c r="Q4" s="136"/>
+      <c r="R4" s="136"/>
     </row>
     <row r="5" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="N5" s="4"/>
@@ -3437,121 +3431,121 @@
       <c r="R10" s="8"/>
     </row>
     <row r="11" spans="1:18" ht="21" x14ac:dyDescent="0.4">
-      <c r="A11" s="136" t="s">
+      <c r="A11" s="137" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="136"/>
-      <c r="C11" s="136"/>
-      <c r="D11" s="136"/>
-      <c r="E11" s="136"/>
-      <c r="F11" s="136"/>
-      <c r="G11" s="136"/>
-      <c r="H11" s="136"/>
-      <c r="I11" s="136"/>
-      <c r="J11" s="136"/>
-      <c r="K11" s="136"/>
-      <c r="L11" s="136"/>
-      <c r="M11" s="136"/>
-      <c r="N11" s="136"/>
-      <c r="O11" s="136"/>
-      <c r="P11" s="136"/>
-      <c r="Q11" s="136"/>
-      <c r="R11" s="136"/>
+      <c r="B11" s="137"/>
+      <c r="C11" s="137"/>
+      <c r="D11" s="137"/>
+      <c r="E11" s="137"/>
+      <c r="F11" s="137"/>
+      <c r="G11" s="137"/>
+      <c r="H11" s="137"/>
+      <c r="I11" s="137"/>
+      <c r="J11" s="137"/>
+      <c r="K11" s="137"/>
+      <c r="L11" s="137"/>
+      <c r="M11" s="137"/>
+      <c r="N11" s="137"/>
+      <c r="O11" s="137"/>
+      <c r="P11" s="137"/>
+      <c r="Q11" s="137"/>
+      <c r="R11" s="137"/>
     </row>
     <row r="14" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="15" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A15" s="137" t="s">
+      <c r="A15" s="138" t="s">
         <v>1</v>
       </c>
-      <c r="B15" s="137"/>
-      <c r="C15" s="137"/>
-      <c r="D15" s="137"/>
-      <c r="E15" s="137"/>
-      <c r="F15" s="137"/>
-      <c r="G15" s="137"/>
-      <c r="H15" s="137"/>
-      <c r="I15" s="137"/>
-      <c r="J15" s="137"/>
-      <c r="K15" s="137"/>
-      <c r="L15" s="137"/>
-      <c r="M15" s="137"/>
-      <c r="N15" s="137"/>
-      <c r="O15" s="137"/>
-      <c r="P15" s="137"/>
-      <c r="Q15" s="137"/>
-      <c r="R15" s="137"/>
+      <c r="B15" s="138"/>
+      <c r="C15" s="138"/>
+      <c r="D15" s="138"/>
+      <c r="E15" s="138"/>
+      <c r="F15" s="138"/>
+      <c r="G15" s="138"/>
+      <c r="H15" s="138"/>
+      <c r="I15" s="138"/>
+      <c r="J15" s="138"/>
+      <c r="K15" s="138"/>
+      <c r="L15" s="138"/>
+      <c r="M15" s="138"/>
+      <c r="N15" s="138"/>
+      <c r="O15" s="138"/>
+      <c r="P15" s="138"/>
+      <c r="Q15" s="138"/>
+      <c r="R15" s="138"/>
     </row>
     <row r="18" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A18" s="138" t="s">
+      <c r="A18" s="139" t="s">
         <v>2</v>
       </c>
-      <c r="B18" s="138"/>
-      <c r="C18" s="138"/>
-      <c r="D18" s="138"/>
-      <c r="E18" s="138"/>
-      <c r="F18" s="138"/>
-      <c r="G18" s="138"/>
-      <c r="H18" s="138"/>
-      <c r="I18" s="138"/>
-      <c r="J18" s="138"/>
-      <c r="K18" s="138"/>
-      <c r="L18" s="138"/>
-      <c r="M18" s="138"/>
-      <c r="N18" s="138"/>
-      <c r="O18" s="138"/>
-      <c r="P18" s="138"/>
-      <c r="Q18" s="138"/>
-      <c r="R18" s="138"/>
+      <c r="B18" s="139"/>
+      <c r="C18" s="139"/>
+      <c r="D18" s="139"/>
+      <c r="E18" s="139"/>
+      <c r="F18" s="139"/>
+      <c r="G18" s="139"/>
+      <c r="H18" s="139"/>
+      <c r="I18" s="139"/>
+      <c r="J18" s="139"/>
+      <c r="K18" s="139"/>
+      <c r="L18" s="139"/>
+      <c r="M18" s="139"/>
+      <c r="N18" s="139"/>
+      <c r="O18" s="139"/>
+      <c r="P18" s="139"/>
+      <c r="Q18" s="139"/>
+      <c r="R18" s="139"/>
     </row>
     <row r="19" spans="1:18" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="20" spans="1:18" ht="12.75" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="89" t="s">
+      <c r="A20" s="108" t="s">
         <v>3</v>
       </c>
-      <c r="B20" s="90"/>
-      <c r="C20" s="90"/>
-      <c r="D20" s="139"/>
-      <c r="E20" s="140"/>
-      <c r="F20" s="140"/>
-      <c r="G20" s="140"/>
-      <c r="H20" s="140"/>
-      <c r="I20" s="140"/>
-      <c r="J20" s="140"/>
-      <c r="K20" s="140"/>
-      <c r="L20" s="140"/>
-      <c r="M20" s="140"/>
-      <c r="N20" s="140"/>
-      <c r="O20" s="140"/>
-      <c r="P20" s="140"/>
-      <c r="Q20" s="140"/>
-      <c r="R20" s="141"/>
+      <c r="B20" s="109"/>
+      <c r="C20" s="109"/>
+      <c r="D20" s="140"/>
+      <c r="E20" s="141"/>
+      <c r="F20" s="141"/>
+      <c r="G20" s="141"/>
+      <c r="H20" s="141"/>
+      <c r="I20" s="141"/>
+      <c r="J20" s="141"/>
+      <c r="K20" s="141"/>
+      <c r="L20" s="141"/>
+      <c r="M20" s="141"/>
+      <c r="N20" s="141"/>
+      <c r="O20" s="141"/>
+      <c r="P20" s="141"/>
+      <c r="Q20" s="141"/>
+      <c r="R20" s="142"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A21" s="91"/>
-      <c r="B21" s="92"/>
-      <c r="C21" s="92"/>
-      <c r="D21" s="142"/>
-      <c r="E21" s="143"/>
-      <c r="F21" s="143"/>
-      <c r="G21" s="143"/>
-      <c r="H21" s="143"/>
-      <c r="I21" s="143"/>
-      <c r="J21" s="143"/>
-      <c r="K21" s="143"/>
-      <c r="L21" s="143"/>
-      <c r="M21" s="143"/>
-      <c r="N21" s="143"/>
-      <c r="O21" s="143"/>
-      <c r="P21" s="143"/>
-      <c r="Q21" s="143"/>
-      <c r="R21" s="144"/>
+      <c r="A21" s="89"/>
+      <c r="B21" s="90"/>
+      <c r="C21" s="90"/>
+      <c r="D21" s="143"/>
+      <c r="E21" s="144"/>
+      <c r="F21" s="144"/>
+      <c r="G21" s="144"/>
+      <c r="H21" s="144"/>
+      <c r="I21" s="144"/>
+      <c r="J21" s="144"/>
+      <c r="K21" s="144"/>
+      <c r="L21" s="144"/>
+      <c r="M21" s="144"/>
+      <c r="N21" s="144"/>
+      <c r="O21" s="144"/>
+      <c r="P21" s="144"/>
+      <c r="Q21" s="144"/>
+      <c r="R21" s="145"/>
     </row>
     <row r="22" spans="1:18" ht="5.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="91" t="s">
+      <c r="A22" s="89" t="s">
         <v>4</v>
       </c>
-      <c r="B22" s="92"/>
-      <c r="C22" s="92"/>
+      <c r="B22" s="90"/>
+      <c r="C22" s="90"/>
       <c r="D22" s="9"/>
       <c r="L22" s="10"/>
       <c r="M22" s="114" t="s">
@@ -3564,9 +3558,9 @@
       <c r="R22" s="120"/>
     </row>
     <row r="23" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="91"/>
-      <c r="B23" s="92"/>
-      <c r="C23" s="92"/>
+      <c r="A23" s="89"/>
+      <c r="B23" s="90"/>
+      <c r="C23" s="90"/>
       <c r="D23" s="127"/>
       <c r="E23" s="128"/>
       <c r="F23" s="128"/>
@@ -3584,9 +3578,9 @@
       <c r="R23" s="123"/>
     </row>
     <row r="24" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="91"/>
-      <c r="B24" s="92"/>
-      <c r="C24" s="92"/>
+      <c r="A24" s="89"/>
+      <c r="B24" s="90"/>
+      <c r="C24" s="90"/>
       <c r="D24" s="130"/>
       <c r="E24" s="128"/>
       <c r="F24" s="128"/>
@@ -3604,9 +3598,9 @@
       <c r="R24" s="123"/>
     </row>
     <row r="25" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="91"/>
-      <c r="B25" s="92"/>
-      <c r="C25" s="92"/>
+      <c r="A25" s="89"/>
+      <c r="B25" s="90"/>
+      <c r="C25" s="90"/>
       <c r="D25" s="130"/>
       <c r="E25" s="128"/>
       <c r="F25" s="128"/>
@@ -3624,9 +3618,9 @@
       <c r="R25" s="123"/>
     </row>
     <row r="26" spans="1:18" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="91"/>
-      <c r="B26" s="92"/>
-      <c r="C26" s="92"/>
+      <c r="A26" s="89"/>
+      <c r="B26" s="90"/>
+      <c r="C26" s="90"/>
       <c r="D26" s="11"/>
       <c r="E26" s="12"/>
       <c r="F26" s="13"/>
@@ -3644,9 +3638,9 @@
       <c r="R26" s="123"/>
     </row>
     <row r="27" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="91"/>
-      <c r="B27" s="92"/>
-      <c r="C27" s="92"/>
+      <c r="A27" s="89"/>
+      <c r="B27" s="90"/>
+      <c r="C27" s="90"/>
       <c r="D27" s="16"/>
       <c r="F27" s="17"/>
       <c r="G27" s="18"/>
@@ -3684,22 +3678,22 @@
     <row r="29" spans="1:18" ht="12.75" thickTop="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="1:18" ht="12.75" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="31" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="89" t="s">
+      <c r="A31" s="108" t="s">
         <v>6</v>
       </c>
-      <c r="B31" s="90"/>
-      <c r="C31" s="90"/>
+      <c r="B31" s="109"/>
+      <c r="C31" s="109"/>
       <c r="D31" s="131"/>
       <c r="E31" s="131"/>
       <c r="F31" s="131"/>
       <c r="G31" s="131"/>
       <c r="H31" s="131"/>
       <c r="I31" s="131"/>
-      <c r="J31" s="90" t="s">
+      <c r="J31" s="109" t="s">
         <v>7</v>
       </c>
-      <c r="K31" s="90"/>
-      <c r="L31" s="90"/>
+      <c r="K31" s="109"/>
+      <c r="L31" s="109"/>
       <c r="M31" s="131"/>
       <c r="N31" s="131"/>
       <c r="O31" s="131"/>
@@ -3708,18 +3702,18 @@
       <c r="R31" s="133"/>
     </row>
     <row r="32" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="91"/>
-      <c r="B32" s="92"/>
-      <c r="C32" s="92"/>
+      <c r="A32" s="89"/>
+      <c r="B32" s="90"/>
+      <c r="C32" s="90"/>
       <c r="D32" s="132"/>
       <c r="E32" s="132"/>
       <c r="F32" s="132"/>
       <c r="G32" s="132"/>
       <c r="H32" s="132"/>
       <c r="I32" s="132"/>
-      <c r="J32" s="92"/>
-      <c r="K32" s="92"/>
-      <c r="L32" s="92"/>
+      <c r="J32" s="90"/>
+      <c r="K32" s="90"/>
+      <c r="L32" s="90"/>
       <c r="M32" s="132"/>
       <c r="N32" s="132"/>
       <c r="O32" s="132"/>
@@ -3728,53 +3722,53 @@
       <c r="R32" s="134"/>
     </row>
     <row r="33" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="91" t="s">
+      <c r="A33" s="89" t="s">
         <v>8</v>
       </c>
-      <c r="B33" s="92"/>
-      <c r="C33" s="92"/>
-      <c r="D33" s="105"/>
-      <c r="E33" s="106"/>
-      <c r="F33" s="106"/>
-      <c r="G33" s="106"/>
-      <c r="H33" s="106"/>
-      <c r="I33" s="106"/>
-      <c r="J33" s="106"/>
-      <c r="K33" s="106"/>
-      <c r="L33" s="106"/>
-      <c r="M33" s="106"/>
-      <c r="N33" s="106"/>
-      <c r="O33" s="106"/>
-      <c r="P33" s="106"/>
-      <c r="Q33" s="106"/>
-      <c r="R33" s="107"/>
+      <c r="B33" s="90"/>
+      <c r="C33" s="90"/>
+      <c r="D33" s="91"/>
+      <c r="E33" s="92"/>
+      <c r="F33" s="92"/>
+      <c r="G33" s="92"/>
+      <c r="H33" s="92"/>
+      <c r="I33" s="92"/>
+      <c r="J33" s="92"/>
+      <c r="K33" s="92"/>
+      <c r="L33" s="92"/>
+      <c r="M33" s="92"/>
+      <c r="N33" s="92"/>
+      <c r="O33" s="92"/>
+      <c r="P33" s="92"/>
+      <c r="Q33" s="92"/>
+      <c r="R33" s="93"/>
     </row>
     <row r="34" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="91"/>
-      <c r="B34" s="92"/>
-      <c r="C34" s="92"/>
-      <c r="D34" s="108"/>
-      <c r="E34" s="109"/>
-      <c r="F34" s="109"/>
-      <c r="G34" s="109"/>
-      <c r="H34" s="109"/>
-      <c r="I34" s="109"/>
-      <c r="J34" s="109"/>
-      <c r="K34" s="109"/>
-      <c r="L34" s="109"/>
-      <c r="M34" s="109"/>
-      <c r="N34" s="109"/>
-      <c r="O34" s="109"/>
-      <c r="P34" s="109"/>
-      <c r="Q34" s="109"/>
-      <c r="R34" s="110"/>
+      <c r="A34" s="89"/>
+      <c r="B34" s="90"/>
+      <c r="C34" s="90"/>
+      <c r="D34" s="94"/>
+      <c r="E34" s="95"/>
+      <c r="F34" s="95"/>
+      <c r="G34" s="95"/>
+      <c r="H34" s="95"/>
+      <c r="I34" s="95"/>
+      <c r="J34" s="95"/>
+      <c r="K34" s="95"/>
+      <c r="L34" s="95"/>
+      <c r="M34" s="95"/>
+      <c r="N34" s="95"/>
+      <c r="O34" s="95"/>
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="96"/>
     </row>
     <row r="35" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="91" t="s">
+      <c r="A35" s="89" t="s">
         <v>9</v>
       </c>
-      <c r="B35" s="92"/>
-      <c r="C35" s="92"/>
+      <c r="B35" s="90"/>
+      <c r="C35" s="90"/>
       <c r="D35" s="99"/>
       <c r="E35" s="100"/>
       <c r="F35" s="100"/>
@@ -3812,94 +3806,94 @@
       <c r="R36" s="104"/>
     </row>
     <row r="37" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="111"/>
-      <c r="B37" s="112"/>
-      <c r="C37" s="112"/>
-      <c r="D37" s="112"/>
-      <c r="E37" s="112"/>
-      <c r="F37" s="112"/>
-      <c r="G37" s="112"/>
-      <c r="H37" s="112"/>
-      <c r="I37" s="112"/>
-      <c r="J37" s="112"/>
-      <c r="K37" s="112"/>
-      <c r="L37" s="112"/>
-      <c r="M37" s="112"/>
-      <c r="N37" s="112"/>
-      <c r="O37" s="112"/>
-      <c r="P37" s="112"/>
-      <c r="Q37" s="112"/>
-      <c r="R37" s="112"/>
+      <c r="A37" s="105"/>
+      <c r="B37" s="106"/>
+      <c r="C37" s="106"/>
+      <c r="D37" s="106"/>
+      <c r="E37" s="106"/>
+      <c r="F37" s="106"/>
+      <c r="G37" s="106"/>
+      <c r="H37" s="106"/>
+      <c r="I37" s="106"/>
+      <c r="J37" s="106"/>
+      <c r="K37" s="106"/>
+      <c r="L37" s="106"/>
+      <c r="M37" s="106"/>
+      <c r="N37" s="106"/>
+      <c r="O37" s="106"/>
+      <c r="P37" s="106"/>
+      <c r="Q37" s="106"/>
+      <c r="R37" s="106"/>
     </row>
     <row r="38" spans="1:18" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="113"/>
-      <c r="B38" s="113"/>
-      <c r="C38" s="113"/>
-      <c r="D38" s="113"/>
-      <c r="E38" s="113"/>
-      <c r="F38" s="113"/>
-      <c r="G38" s="113"/>
-      <c r="H38" s="113"/>
-      <c r="I38" s="113"/>
-      <c r="J38" s="113"/>
-      <c r="K38" s="113"/>
-      <c r="L38" s="113"/>
-      <c r="M38" s="113"/>
-      <c r="N38" s="113"/>
-      <c r="O38" s="113"/>
-      <c r="P38" s="113"/>
-      <c r="Q38" s="113"/>
-      <c r="R38" s="113"/>
+      <c r="A38" s="107"/>
+      <c r="B38" s="107"/>
+      <c r="C38" s="107"/>
+      <c r="D38" s="107"/>
+      <c r="E38" s="107"/>
+      <c r="F38" s="107"/>
+      <c r="G38" s="107"/>
+      <c r="H38" s="107"/>
+      <c r="I38" s="107"/>
+      <c r="J38" s="107"/>
+      <c r="K38" s="107"/>
+      <c r="L38" s="107"/>
+      <c r="M38" s="107"/>
+      <c r="N38" s="107"/>
+      <c r="O38" s="107"/>
+      <c r="P38" s="107"/>
+      <c r="Q38" s="107"/>
+      <c r="R38" s="107"/>
     </row>
     <row r="39" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="89" t="s">
+      <c r="A39" s="108" t="s">
         <v>10</v>
       </c>
-      <c r="B39" s="90"/>
-      <c r="C39" s="90"/>
-      <c r="D39" s="90" t="s">
+      <c r="B39" s="109"/>
+      <c r="C39" s="109"/>
+      <c r="D39" s="109" t="s">
         <v>11</v>
       </c>
-      <c r="E39" s="90"/>
-      <c r="F39" s="90"/>
-      <c r="G39" s="93"/>
-      <c r="H39" s="90" t="s">
+      <c r="E39" s="109"/>
+      <c r="F39" s="109"/>
+      <c r="G39" s="110"/>
+      <c r="H39" s="109" t="s">
         <v>10</v>
       </c>
-      <c r="I39" s="90"/>
-      <c r="J39" s="90"/>
-      <c r="K39" s="90" t="s">
+      <c r="I39" s="109"/>
+      <c r="J39" s="109"/>
+      <c r="K39" s="109" t="s">
         <v>11</v>
       </c>
-      <c r="L39" s="90"/>
-      <c r="M39" s="90"/>
-      <c r="N39" s="93"/>
-      <c r="O39" s="90" t="s">
+      <c r="L39" s="109"/>
+      <c r="M39" s="109"/>
+      <c r="N39" s="110"/>
+      <c r="O39" s="109" t="s">
         <v>12</v>
       </c>
-      <c r="P39" s="90"/>
-      <c r="Q39" s="90"/>
-      <c r="R39" s="95"/>
+      <c r="P39" s="109"/>
+      <c r="Q39" s="109"/>
+      <c r="R39" s="112"/>
     </row>
     <row r="40" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="91"/>
-      <c r="B40" s="92"/>
-      <c r="C40" s="92"/>
-      <c r="D40" s="92"/>
-      <c r="E40" s="92"/>
-      <c r="F40" s="92"/>
-      <c r="G40" s="94"/>
-      <c r="H40" s="92"/>
-      <c r="I40" s="92"/>
-      <c r="J40" s="92"/>
-      <c r="K40" s="92"/>
-      <c r="L40" s="92"/>
-      <c r="M40" s="92"/>
-      <c r="N40" s="94"/>
-      <c r="O40" s="92"/>
-      <c r="P40" s="92"/>
-      <c r="Q40" s="92"/>
-      <c r="R40" s="96"/>
+      <c r="A40" s="89"/>
+      <c r="B40" s="90"/>
+      <c r="C40" s="90"/>
+      <c r="D40" s="90"/>
+      <c r="E40" s="90"/>
+      <c r="F40" s="90"/>
+      <c r="G40" s="111"/>
+      <c r="H40" s="90"/>
+      <c r="I40" s="90"/>
+      <c r="J40" s="90"/>
+      <c r="K40" s="90"/>
+      <c r="L40" s="90"/>
+      <c r="M40" s="90"/>
+      <c r="N40" s="111"/>
+      <c r="O40" s="90"/>
+      <c r="P40" s="90"/>
+      <c r="Q40" s="90"/>
+      <c r="R40" s="113"/>
     </row>
     <row r="41" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="64" t="s">
@@ -3993,21 +3987,21 @@
       <c r="A45" s="88" t="s">
         <v>17</v>
       </c>
-      <c r="B45" s="54"/>
-      <c r="C45" s="54"/>
-      <c r="D45" s="52"/>
-      <c r="E45" s="52"/>
-      <c r="F45" s="52"/>
-      <c r="G45" s="53"/>
-      <c r="H45" s="54" t="s">
+      <c r="B45" s="60"/>
+      <c r="C45" s="60"/>
+      <c r="D45" s="58"/>
+      <c r="E45" s="58"/>
+      <c r="F45" s="58"/>
+      <c r="G45" s="59"/>
+      <c r="H45" s="60" t="s">
         <v>17</v>
       </c>
-      <c r="I45" s="54"/>
-      <c r="J45" s="54"/>
-      <c r="K45" s="52"/>
-      <c r="L45" s="52"/>
-      <c r="M45" s="52"/>
-      <c r="N45" s="53"/>
+      <c r="I45" s="60"/>
+      <c r="J45" s="60"/>
+      <c r="K45" s="58"/>
+      <c r="L45" s="58"/>
+      <c r="M45" s="58"/>
+      <c r="N45" s="59"/>
       <c r="O45" s="84"/>
       <c r="P45" s="84"/>
       <c r="Q45" s="84"/>
@@ -4017,31 +4011,31 @@
     <row r="47" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="48" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="24"/>
-      <c r="B48" s="55" t="s">
+      <c r="B48" s="61" t="s">
         <v>18</v>
       </c>
-      <c r="C48" s="55"/>
-      <c r="D48" s="55"/>
-      <c r="E48" s="55"/>
+      <c r="C48" s="61"/>
+      <c r="D48" s="61"/>
+      <c r="E48" s="61"/>
       <c r="F48" s="25"/>
-      <c r="G48" s="56" t="s">
+      <c r="G48" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="H48" s="57"/>
-      <c r="I48" s="58"/>
+      <c r="H48" s="62"/>
+      <c r="I48" s="63"/>
       <c r="J48" s="24"/>
-      <c r="K48" s="55" t="s">
+      <c r="K48" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="L48" s="55"/>
-      <c r="M48" s="55"/>
-      <c r="N48" s="55"/>
+      <c r="L48" s="61"/>
+      <c r="M48" s="61"/>
+      <c r="N48" s="61"/>
       <c r="O48" s="25"/>
-      <c r="P48" s="56" t="s">
+      <c r="P48" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="Q48" s="59"/>
-      <c r="R48" s="60"/>
+      <c r="Q48" s="53"/>
+      <c r="R48" s="54"/>
     </row>
     <row r="49" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="26"/>
@@ -4055,12 +4049,12 @@
       <c r="H49" s="51"/>
       <c r="I49" s="50"/>
       <c r="J49" s="29"/>
-      <c r="K49" s="61" t="s">
+      <c r="K49" s="55" t="s">
         <v>22</v>
       </c>
-      <c r="L49" s="62"/>
-      <c r="M49" s="62"/>
-      <c r="N49" s="63"/>
+      <c r="L49" s="56"/>
+      <c r="M49" s="56"/>
+      <c r="N49" s="57"/>
       <c r="O49" s="30"/>
       <c r="P49" s="48"/>
       <c r="Q49" s="51"/>
@@ -4239,6 +4233,1002 @@
       <c r="F57" s="28"/>
       <c r="G57" s="48"/>
       <c r="H57" s="49"/>
+      <c r="I57" s="50"/>
+      <c r="J57" s="37"/>
+      <c r="K57" s="38"/>
+      <c r="L57" s="38"/>
+      <c r="M57" s="38"/>
+      <c r="N57" s="38"/>
+      <c r="O57" s="38"/>
+      <c r="P57" s="38"/>
+      <c r="Q57" s="38"/>
+      <c r="R57" s="39"/>
+    </row>
+  </sheetData>
+  <sheetProtection formatCells="0"/>
+  <mergeCells count="70">
+    <mergeCell ref="A20:C21"/>
+    <mergeCell ref="D20:R21"/>
+    <mergeCell ref="O1:R1"/>
+    <mergeCell ref="O3:R4"/>
+    <mergeCell ref="A11:R11"/>
+    <mergeCell ref="A15:R15"/>
+    <mergeCell ref="A18:R18"/>
+    <mergeCell ref="A22:C28"/>
+    <mergeCell ref="M22:N28"/>
+    <mergeCell ref="O22:R28"/>
+    <mergeCell ref="D23:L25"/>
+    <mergeCell ref="A31:C32"/>
+    <mergeCell ref="D31:I32"/>
+    <mergeCell ref="J31:L32"/>
+    <mergeCell ref="M31:R32"/>
+    <mergeCell ref="A39:C40"/>
+    <mergeCell ref="D39:G40"/>
+    <mergeCell ref="H39:J40"/>
+    <mergeCell ref="K39:N40"/>
+    <mergeCell ref="O39:R40"/>
+    <mergeCell ref="A33:C34"/>
+    <mergeCell ref="D33:R34"/>
+    <mergeCell ref="A35:C36"/>
+    <mergeCell ref="D35:R36"/>
+    <mergeCell ref="A37:R38"/>
+    <mergeCell ref="A41:C42"/>
+    <mergeCell ref="D41:G42"/>
+    <mergeCell ref="H41:J42"/>
+    <mergeCell ref="K41:N42"/>
+    <mergeCell ref="O41:R45"/>
+    <mergeCell ref="A43:C44"/>
+    <mergeCell ref="D43:G44"/>
+    <mergeCell ref="H43:J44"/>
+    <mergeCell ref="K43:N44"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="G50:I50"/>
+    <mergeCell ref="K50:N50"/>
+    <mergeCell ref="P50:R50"/>
+    <mergeCell ref="D45:G45"/>
+    <mergeCell ref="H45:J45"/>
+    <mergeCell ref="K45:N45"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="G48:I48"/>
+    <mergeCell ref="K48:N48"/>
+    <mergeCell ref="P48:R48"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="G49:I49"/>
+    <mergeCell ref="K49:N49"/>
+    <mergeCell ref="P49:R49"/>
+    <mergeCell ref="B51:E51"/>
+    <mergeCell ref="G51:I51"/>
+    <mergeCell ref="K51:N51"/>
+    <mergeCell ref="P51:R51"/>
+    <mergeCell ref="B52:E52"/>
+    <mergeCell ref="G52:I52"/>
+    <mergeCell ref="K52:N52"/>
+    <mergeCell ref="P52:R52"/>
+    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="G53:I53"/>
+    <mergeCell ref="K53:N53"/>
+    <mergeCell ref="P53:R53"/>
+    <mergeCell ref="B54:E54"/>
+    <mergeCell ref="G54:I54"/>
+    <mergeCell ref="B55:E55"/>
+    <mergeCell ref="G55:I55"/>
+    <mergeCell ref="B56:E56"/>
+    <mergeCell ref="G56:I56"/>
+    <mergeCell ref="B57:E57"/>
+    <mergeCell ref="G57:I57"/>
+  </mergeCells>
+  <phoneticPr fontId="3"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.47244094488188981" right="0.47244094488188981" top="0.43307086614173229" bottom="0.55118110236220474" header="0.23622047244094491" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="95" orientation="portrait" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="18" max="1048575" man="1"/>
+  </colBreaks>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F598854D-5A4C-4289-91C2-F1136C69061F}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:R57"/>
+  <sheetFormatPr defaultColWidth="5" defaultRowHeight="12" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="16384" width="5" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="O1" s="135"/>
+      <c r="P1" s="135"/>
+      <c r="Q1" s="135"/>
+      <c r="R1" s="135"/>
+    </row>
+    <row r="2" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+    </row>
+    <row r="3" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
+      <c r="A3" s="3"/>
+      <c r="O3" s="136"/>
+      <c r="P3" s="136"/>
+      <c r="Q3" s="136"/>
+      <c r="R3" s="136"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="O4" s="136"/>
+      <c r="P4" s="136"/>
+      <c r="Q4" s="136"/>
+      <c r="R4" s="136"/>
+    </row>
+    <row r="5" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="N5" s="4"/>
+      <c r="O5" s="4"/>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="5"/>
+    </row>
+    <row r="6" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="N6" s="4"/>
+      <c r="O6" s="4"/>
+      <c r="P6" s="4"/>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="5"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="R7" s="5"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="R8" s="5"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="6"/>
+      <c r="P9" s="6"/>
+      <c r="Q9" s="6"/>
+      <c r="R9" s="7"/>
+    </row>
+    <row r="10" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="6"/>
+      <c r="P10" s="6"/>
+      <c r="Q10" s="6"/>
+      <c r="R10" s="8"/>
+    </row>
+    <row r="11" spans="1:18" ht="21" x14ac:dyDescent="0.4">
+      <c r="A11" s="137" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="137"/>
+      <c r="C11" s="137"/>
+      <c r="D11" s="137"/>
+      <c r="E11" s="137"/>
+      <c r="F11" s="137"/>
+      <c r="G11" s="137"/>
+      <c r="H11" s="137"/>
+      <c r="I11" s="137"/>
+      <c r="J11" s="137"/>
+      <c r="K11" s="137"/>
+      <c r="L11" s="137"/>
+      <c r="M11" s="137"/>
+      <c r="N11" s="137"/>
+      <c r="O11" s="137"/>
+      <c r="P11" s="137"/>
+      <c r="Q11" s="137"/>
+      <c r="R11" s="137"/>
+    </row>
+    <row r="14" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="15" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
+      <c r="A15" s="138" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="138"/>
+      <c r="C15" s="138"/>
+      <c r="D15" s="138"/>
+      <c r="E15" s="138"/>
+      <c r="F15" s="138"/>
+      <c r="G15" s="138"/>
+      <c r="H15" s="138"/>
+      <c r="I15" s="138"/>
+      <c r="J15" s="138"/>
+      <c r="K15" s="138"/>
+      <c r="L15" s="138"/>
+      <c r="M15" s="138"/>
+      <c r="N15" s="138"/>
+      <c r="O15" s="138"/>
+      <c r="P15" s="138"/>
+      <c r="Q15" s="138"/>
+      <c r="R15" s="138"/>
+    </row>
+    <row r="18" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
+      <c r="A18" s="139" t="s">
+        <v>2</v>
+      </c>
+      <c r="B18" s="139"/>
+      <c r="C18" s="139"/>
+      <c r="D18" s="139"/>
+      <c r="E18" s="139"/>
+      <c r="F18" s="139"/>
+      <c r="G18" s="139"/>
+      <c r="H18" s="139"/>
+      <c r="I18" s="139"/>
+      <c r="J18" s="139"/>
+      <c r="K18" s="139"/>
+      <c r="L18" s="139"/>
+      <c r="M18" s="139"/>
+      <c r="N18" s="139"/>
+      <c r="O18" s="139"/>
+      <c r="P18" s="139"/>
+      <c r="Q18" s="139"/>
+      <c r="R18" s="139"/>
+    </row>
+    <row r="19" spans="1:18" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="20" spans="1:18" ht="12.75" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="108" t="s">
+        <v>3</v>
+      </c>
+      <c r="B20" s="109"/>
+      <c r="C20" s="109"/>
+      <c r="D20" s="140"/>
+      <c r="E20" s="141"/>
+      <c r="F20" s="141"/>
+      <c r="G20" s="141"/>
+      <c r="H20" s="141"/>
+      <c r="I20" s="141"/>
+      <c r="J20" s="141"/>
+      <c r="K20" s="141"/>
+      <c r="L20" s="141"/>
+      <c r="M20" s="141"/>
+      <c r="N20" s="141"/>
+      <c r="O20" s="141"/>
+      <c r="P20" s="141"/>
+      <c r="Q20" s="141"/>
+      <c r="R20" s="142"/>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A21" s="89"/>
+      <c r="B21" s="90"/>
+      <c r="C21" s="90"/>
+      <c r="D21" s="143"/>
+      <c r="E21" s="144"/>
+      <c r="F21" s="144"/>
+      <c r="G21" s="144"/>
+      <c r="H21" s="144"/>
+      <c r="I21" s="144"/>
+      <c r="J21" s="144"/>
+      <c r="K21" s="144"/>
+      <c r="L21" s="144"/>
+      <c r="M21" s="144"/>
+      <c r="N21" s="144"/>
+      <c r="O21" s="144"/>
+      <c r="P21" s="144"/>
+      <c r="Q21" s="144"/>
+      <c r="R21" s="145"/>
+    </row>
+    <row r="22" spans="1:18" ht="5.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="89" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" s="90"/>
+      <c r="C22" s="90"/>
+      <c r="D22" s="9"/>
+      <c r="L22" s="10"/>
+      <c r="M22" s="114" t="s">
+        <v>5</v>
+      </c>
+      <c r="N22" s="115"/>
+      <c r="O22" s="118"/>
+      <c r="P22" s="119"/>
+      <c r="Q22" s="119"/>
+      <c r="R22" s="120"/>
+    </row>
+    <row r="23" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="89"/>
+      <c r="B23" s="90"/>
+      <c r="C23" s="90"/>
+      <c r="D23" s="127"/>
+      <c r="E23" s="128"/>
+      <c r="F23" s="128"/>
+      <c r="G23" s="128"/>
+      <c r="H23" s="128"/>
+      <c r="I23" s="128"/>
+      <c r="J23" s="128"/>
+      <c r="K23" s="128"/>
+      <c r="L23" s="129"/>
+      <c r="M23" s="114"/>
+      <c r="N23" s="115"/>
+      <c r="O23" s="121"/>
+      <c r="P23" s="122"/>
+      <c r="Q23" s="122"/>
+      <c r="R23" s="123"/>
+    </row>
+    <row r="24" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="89"/>
+      <c r="B24" s="90"/>
+      <c r="C24" s="90"/>
+      <c r="D24" s="130"/>
+      <c r="E24" s="128"/>
+      <c r="F24" s="128"/>
+      <c r="G24" s="128"/>
+      <c r="H24" s="128"/>
+      <c r="I24" s="128"/>
+      <c r="J24" s="128"/>
+      <c r="K24" s="128"/>
+      <c r="L24" s="129"/>
+      <c r="M24" s="114"/>
+      <c r="N24" s="115"/>
+      <c r="O24" s="121"/>
+      <c r="P24" s="122"/>
+      <c r="Q24" s="122"/>
+      <c r="R24" s="123"/>
+    </row>
+    <row r="25" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="89"/>
+      <c r="B25" s="90"/>
+      <c r="C25" s="90"/>
+      <c r="D25" s="130"/>
+      <c r="E25" s="128"/>
+      <c r="F25" s="128"/>
+      <c r="G25" s="128"/>
+      <c r="H25" s="128"/>
+      <c r="I25" s="128"/>
+      <c r="J25" s="128"/>
+      <c r="K25" s="128"/>
+      <c r="L25" s="129"/>
+      <c r="M25" s="114"/>
+      <c r="N25" s="115"/>
+      <c r="O25" s="121"/>
+      <c r="P25" s="122"/>
+      <c r="Q25" s="122"/>
+      <c r="R25" s="123"/>
+    </row>
+    <row r="26" spans="1:18" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="89"/>
+      <c r="B26" s="90"/>
+      <c r="C26" s="90"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="14"/>
+      <c r="K26" s="14"/>
+      <c r="L26" s="15"/>
+      <c r="M26" s="114"/>
+      <c r="N26" s="115"/>
+      <c r="O26" s="121"/>
+      <c r="P26" s="122"/>
+      <c r="Q26" s="122"/>
+      <c r="R26" s="123"/>
+    </row>
+    <row r="27" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="89"/>
+      <c r="B27" s="90"/>
+      <c r="C27" s="90"/>
+      <c r="D27" s="16"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="18"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="19"/>
+      <c r="L27" s="20"/>
+      <c r="M27" s="114"/>
+      <c r="N27" s="115"/>
+      <c r="O27" s="121"/>
+      <c r="P27" s="122"/>
+      <c r="Q27" s="122"/>
+      <c r="R27" s="123"/>
+    </row>
+    <row r="28" spans="1:18" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A28" s="97"/>
+      <c r="B28" s="98"/>
+      <c r="C28" s="98"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="22"/>
+      <c r="H28" s="22"/>
+      <c r="I28" s="22"/>
+      <c r="J28" s="22"/>
+      <c r="K28" s="22"/>
+      <c r="L28" s="23"/>
+      <c r="M28" s="116"/>
+      <c r="N28" s="117"/>
+      <c r="O28" s="124"/>
+      <c r="P28" s="125"/>
+      <c r="Q28" s="125"/>
+      <c r="R28" s="126"/>
+    </row>
+    <row r="29" spans="1:18" ht="12.75" thickTop="1" x14ac:dyDescent="0.4"/>
+    <row r="30" spans="1:18" ht="12.75" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="31" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="108" t="s">
+        <v>6</v>
+      </c>
+      <c r="B31" s="109"/>
+      <c r="C31" s="109"/>
+      <c r="D31" s="131"/>
+      <c r="E31" s="131"/>
+      <c r="F31" s="131"/>
+      <c r="G31" s="131"/>
+      <c r="H31" s="131"/>
+      <c r="I31" s="131"/>
+      <c r="J31" s="109" t="s">
+        <v>7</v>
+      </c>
+      <c r="K31" s="109"/>
+      <c r="L31" s="109"/>
+      <c r="M31" s="131"/>
+      <c r="N31" s="131"/>
+      <c r="O31" s="131"/>
+      <c r="P31" s="131"/>
+      <c r="Q31" s="131"/>
+      <c r="R31" s="133"/>
+    </row>
+    <row r="32" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="89"/>
+      <c r="B32" s="90"/>
+      <c r="C32" s="90"/>
+      <c r="D32" s="132"/>
+      <c r="E32" s="132"/>
+      <c r="F32" s="132"/>
+      <c r="G32" s="132"/>
+      <c r="H32" s="132"/>
+      <c r="I32" s="132"/>
+      <c r="J32" s="90"/>
+      <c r="K32" s="90"/>
+      <c r="L32" s="90"/>
+      <c r="M32" s="132"/>
+      <c r="N32" s="132"/>
+      <c r="O32" s="132"/>
+      <c r="P32" s="132"/>
+      <c r="Q32" s="132"/>
+      <c r="R32" s="134"/>
+    </row>
+    <row r="33" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="89" t="s">
+        <v>8</v>
+      </c>
+      <c r="B33" s="90"/>
+      <c r="C33" s="90"/>
+      <c r="D33" s="91"/>
+      <c r="E33" s="92"/>
+      <c r="F33" s="92"/>
+      <c r="G33" s="92"/>
+      <c r="H33" s="92"/>
+      <c r="I33" s="92"/>
+      <c r="J33" s="92"/>
+      <c r="K33" s="92"/>
+      <c r="L33" s="92"/>
+      <c r="M33" s="92"/>
+      <c r="N33" s="92"/>
+      <c r="O33" s="92"/>
+      <c r="P33" s="92"/>
+      <c r="Q33" s="92"/>
+      <c r="R33" s="93"/>
+    </row>
+    <row r="34" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="89"/>
+      <c r="B34" s="90"/>
+      <c r="C34" s="90"/>
+      <c r="D34" s="94"/>
+      <c r="E34" s="95"/>
+      <c r="F34" s="95"/>
+      <c r="G34" s="95"/>
+      <c r="H34" s="95"/>
+      <c r="I34" s="95"/>
+      <c r="J34" s="95"/>
+      <c r="K34" s="95"/>
+      <c r="L34" s="95"/>
+      <c r="M34" s="95"/>
+      <c r="N34" s="95"/>
+      <c r="O34" s="95"/>
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="96"/>
+    </row>
+    <row r="35" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="89" t="s">
+        <v>9</v>
+      </c>
+      <c r="B35" s="90"/>
+      <c r="C35" s="90"/>
+      <c r="D35" s="99"/>
+      <c r="E35" s="100"/>
+      <c r="F35" s="100"/>
+      <c r="G35" s="100"/>
+      <c r="H35" s="100"/>
+      <c r="I35" s="100"/>
+      <c r="J35" s="100"/>
+      <c r="K35" s="100"/>
+      <c r="L35" s="100"/>
+      <c r="M35" s="100"/>
+      <c r="N35" s="100"/>
+      <c r="O35" s="100"/>
+      <c r="P35" s="100"/>
+      <c r="Q35" s="100"/>
+      <c r="R35" s="101"/>
+    </row>
+    <row r="36" spans="1:18" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A36" s="97"/>
+      <c r="B36" s="98"/>
+      <c r="C36" s="98"/>
+      <c r="D36" s="102"/>
+      <c r="E36" s="103"/>
+      <c r="F36" s="103"/>
+      <c r="G36" s="103"/>
+      <c r="H36" s="103"/>
+      <c r="I36" s="103"/>
+      <c r="J36" s="103"/>
+      <c r="K36" s="103"/>
+      <c r="L36" s="103"/>
+      <c r="M36" s="103"/>
+      <c r="N36" s="103"/>
+      <c r="O36" s="103"/>
+      <c r="P36" s="103"/>
+      <c r="Q36" s="103"/>
+      <c r="R36" s="104"/>
+    </row>
+    <row r="37" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="105"/>
+      <c r="B37" s="106"/>
+      <c r="C37" s="106"/>
+      <c r="D37" s="106"/>
+      <c r="E37" s="106"/>
+      <c r="F37" s="106"/>
+      <c r="G37" s="106"/>
+      <c r="H37" s="106"/>
+      <c r="I37" s="106"/>
+      <c r="J37" s="106"/>
+      <c r="K37" s="106"/>
+      <c r="L37" s="106"/>
+      <c r="M37" s="106"/>
+      <c r="N37" s="106"/>
+      <c r="O37" s="106"/>
+      <c r="P37" s="106"/>
+      <c r="Q37" s="106"/>
+      <c r="R37" s="106"/>
+    </row>
+    <row r="38" spans="1:18" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A38" s="107"/>
+      <c r="B38" s="107"/>
+      <c r="C38" s="107"/>
+      <c r="D38" s="107"/>
+      <c r="E38" s="107"/>
+      <c r="F38" s="107"/>
+      <c r="G38" s="107"/>
+      <c r="H38" s="107"/>
+      <c r="I38" s="107"/>
+      <c r="J38" s="107"/>
+      <c r="K38" s="107"/>
+      <c r="L38" s="107"/>
+      <c r="M38" s="107"/>
+      <c r="N38" s="107"/>
+      <c r="O38" s="107"/>
+      <c r="P38" s="107"/>
+      <c r="Q38" s="107"/>
+      <c r="R38" s="107"/>
+    </row>
+    <row r="39" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="108" t="s">
+        <v>10</v>
+      </c>
+      <c r="B39" s="109"/>
+      <c r="C39" s="109"/>
+      <c r="D39" s="109" t="s">
+        <v>11</v>
+      </c>
+      <c r="E39" s="109"/>
+      <c r="F39" s="109"/>
+      <c r="G39" s="110"/>
+      <c r="H39" s="109" t="s">
+        <v>10</v>
+      </c>
+      <c r="I39" s="109"/>
+      <c r="J39" s="109"/>
+      <c r="K39" s="109" t="s">
+        <v>11</v>
+      </c>
+      <c r="L39" s="109"/>
+      <c r="M39" s="109"/>
+      <c r="N39" s="110"/>
+      <c r="O39" s="109" t="s">
+        <v>35</v>
+      </c>
+      <c r="P39" s="109"/>
+      <c r="Q39" s="109"/>
+      <c r="R39" s="112"/>
+    </row>
+    <row r="40" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="89"/>
+      <c r="B40" s="90"/>
+      <c r="C40" s="90"/>
+      <c r="D40" s="90"/>
+      <c r="E40" s="90"/>
+      <c r="F40" s="90"/>
+      <c r="G40" s="111"/>
+      <c r="H40" s="90"/>
+      <c r="I40" s="90"/>
+      <c r="J40" s="90"/>
+      <c r="K40" s="90"/>
+      <c r="L40" s="90"/>
+      <c r="M40" s="90"/>
+      <c r="N40" s="111"/>
+      <c r="O40" s="90"/>
+      <c r="P40" s="90"/>
+      <c r="Q40" s="90"/>
+      <c r="R40" s="113"/>
+    </row>
+    <row r="41" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A41" s="64" t="s">
+        <v>13</v>
+      </c>
+      <c r="B41" s="65"/>
+      <c r="C41" s="66"/>
+      <c r="D41" s="70"/>
+      <c r="E41" s="71"/>
+      <c r="F41" s="71"/>
+      <c r="G41" s="72"/>
+      <c r="H41" s="76" t="s">
+        <v>14</v>
+      </c>
+      <c r="I41" s="77"/>
+      <c r="J41" s="78"/>
+      <c r="K41" s="70"/>
+      <c r="L41" s="71"/>
+      <c r="M41" s="71"/>
+      <c r="N41" s="72"/>
+      <c r="O41" s="82"/>
+      <c r="P41" s="82"/>
+      <c r="Q41" s="82"/>
+      <c r="R41" s="83"/>
+    </row>
+    <row r="42" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A42" s="67"/>
+      <c r="B42" s="68"/>
+      <c r="C42" s="69"/>
+      <c r="D42" s="73"/>
+      <c r="E42" s="74"/>
+      <c r="F42" s="74"/>
+      <c r="G42" s="75"/>
+      <c r="H42" s="79"/>
+      <c r="I42" s="80"/>
+      <c r="J42" s="81"/>
+      <c r="K42" s="73"/>
+      <c r="L42" s="74"/>
+      <c r="M42" s="74"/>
+      <c r="N42" s="75"/>
+      <c r="O42" s="82"/>
+      <c r="P42" s="82"/>
+      <c r="Q42" s="82"/>
+      <c r="R42" s="83"/>
+    </row>
+    <row r="43" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A43" s="64" t="s">
+        <v>15</v>
+      </c>
+      <c r="B43" s="65"/>
+      <c r="C43" s="66"/>
+      <c r="D43" s="70"/>
+      <c r="E43" s="71"/>
+      <c r="F43" s="71"/>
+      <c r="G43" s="72"/>
+      <c r="H43" s="86" t="s">
+        <v>16</v>
+      </c>
+      <c r="I43" s="65"/>
+      <c r="J43" s="66"/>
+      <c r="K43" s="70"/>
+      <c r="L43" s="71"/>
+      <c r="M43" s="71"/>
+      <c r="N43" s="72"/>
+      <c r="O43" s="82"/>
+      <c r="P43" s="82"/>
+      <c r="Q43" s="82"/>
+      <c r="R43" s="83"/>
+    </row>
+    <row r="44" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="67"/>
+      <c r="B44" s="68"/>
+      <c r="C44" s="69"/>
+      <c r="D44" s="73"/>
+      <c r="E44" s="74"/>
+      <c r="F44" s="74"/>
+      <c r="G44" s="75"/>
+      <c r="H44" s="87"/>
+      <c r="I44" s="68"/>
+      <c r="J44" s="69"/>
+      <c r="K44" s="73"/>
+      <c r="L44" s="74"/>
+      <c r="M44" s="74"/>
+      <c r="N44" s="75"/>
+      <c r="O44" s="82"/>
+      <c r="P44" s="82"/>
+      <c r="Q44" s="82"/>
+      <c r="R44" s="83"/>
+    </row>
+    <row r="45" spans="1:18" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A45" s="88" t="s">
+        <v>17</v>
+      </c>
+      <c r="B45" s="60"/>
+      <c r="C45" s="60"/>
+      <c r="D45" s="58"/>
+      <c r="E45" s="58"/>
+      <c r="F45" s="58"/>
+      <c r="G45" s="59"/>
+      <c r="H45" s="60" t="s">
+        <v>17</v>
+      </c>
+      <c r="I45" s="60"/>
+      <c r="J45" s="60"/>
+      <c r="K45" s="58"/>
+      <c r="L45" s="58"/>
+      <c r="M45" s="58"/>
+      <c r="N45" s="59"/>
+      <c r="O45" s="84"/>
+      <c r="P45" s="84"/>
+      <c r="Q45" s="84"/>
+      <c r="R45" s="85"/>
+    </row>
+    <row r="46" spans="1:18" ht="20.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.4"/>
+    <row r="47" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="48" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A48" s="24"/>
+      <c r="B48" s="61" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48" s="61"/>
+      <c r="D48" s="61"/>
+      <c r="E48" s="61"/>
+      <c r="F48" s="25"/>
+      <c r="G48" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="H48" s="53"/>
+      <c r="I48" s="54"/>
+      <c r="J48" s="24"/>
+      <c r="K48" s="61" t="s">
+        <v>20</v>
+      </c>
+      <c r="L48" s="61"/>
+      <c r="M48" s="61"/>
+      <c r="N48" s="61"/>
+      <c r="O48" s="25"/>
+      <c r="P48" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q48" s="53"/>
+      <c r="R48" s="54"/>
+    </row>
+    <row r="49" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A49" s="26"/>
+      <c r="B49" s="147" t="s">
+        <v>21</v>
+      </c>
+      <c r="C49" s="147"/>
+      <c r="D49" s="147"/>
+      <c r="E49" s="148"/>
+      <c r="G49" s="48"/>
+      <c r="H49" s="51"/>
+      <c r="I49" s="50"/>
+      <c r="J49" s="29"/>
+      <c r="K49" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="L49" s="56"/>
+      <c r="M49" s="56"/>
+      <c r="N49" s="57"/>
+      <c r="O49" s="30"/>
+      <c r="P49" s="48"/>
+      <c r="Q49" s="51"/>
+      <c r="R49" s="50"/>
+    </row>
+    <row r="50" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A50" s="27"/>
+      <c r="B50" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="C50" s="46"/>
+      <c r="D50" s="46"/>
+      <c r="E50" s="146"/>
+      <c r="F50" s="28"/>
+      <c r="G50" s="48"/>
+      <c r="H50" s="51"/>
+      <c r="I50" s="50"/>
+      <c r="J50" s="29"/>
+      <c r="K50" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="L50" s="46"/>
+      <c r="M50" s="46"/>
+      <c r="N50" s="46"/>
+      <c r="O50" s="30"/>
+      <c r="P50" s="48"/>
+      <c r="Q50" s="51"/>
+      <c r="R50" s="50"/>
+    </row>
+    <row r="51" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A51" s="27"/>
+      <c r="B51" s="46" t="s">
+        <v>25</v>
+      </c>
+      <c r="C51" s="46"/>
+      <c r="D51" s="46"/>
+      <c r="E51" s="146"/>
+      <c r="F51" s="28"/>
+      <c r="G51" s="48"/>
+      <c r="H51" s="51"/>
+      <c r="I51" s="50"/>
+      <c r="J51" s="29"/>
+      <c r="K51" s="46" t="s">
+        <v>26</v>
+      </c>
+      <c r="L51" s="46"/>
+      <c r="M51" s="46"/>
+      <c r="N51" s="46"/>
+      <c r="O51" s="30"/>
+      <c r="P51" s="48"/>
+      <c r="Q51" s="51"/>
+      <c r="R51" s="50"/>
+    </row>
+    <row r="52" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A52" s="27"/>
+      <c r="B52" s="46" t="s">
+        <v>27</v>
+      </c>
+      <c r="C52" s="46"/>
+      <c r="D52" s="46"/>
+      <c r="E52" s="146"/>
+      <c r="F52" s="28"/>
+      <c r="G52" s="48"/>
+      <c r="H52" s="51"/>
+      <c r="I52" s="50"/>
+      <c r="J52" s="29"/>
+      <c r="K52" s="46" t="s">
+        <v>28</v>
+      </c>
+      <c r="L52" s="46"/>
+      <c r="M52" s="46"/>
+      <c r="N52" s="46"/>
+      <c r="O52" s="30"/>
+      <c r="P52" s="48"/>
+      <c r="Q52" s="51"/>
+      <c r="R52" s="50"/>
+    </row>
+    <row r="53" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A53" s="27"/>
+      <c r="B53" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="C53" s="46"/>
+      <c r="D53" s="46"/>
+      <c r="E53" s="146"/>
+      <c r="F53" s="28"/>
+      <c r="G53" s="48"/>
+      <c r="H53" s="51"/>
+      <c r="I53" s="50"/>
+      <c r="J53" s="29"/>
+      <c r="K53" s="46" t="s">
+        <v>30</v>
+      </c>
+      <c r="L53" s="46"/>
+      <c r="M53" s="46"/>
+      <c r="N53" s="46"/>
+      <c r="O53" s="30"/>
+      <c r="P53" s="48"/>
+      <c r="Q53" s="51"/>
+      <c r="R53" s="50"/>
+    </row>
+    <row r="54" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A54" s="27"/>
+      <c r="B54" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="C54" s="46"/>
+      <c r="D54" s="46"/>
+      <c r="E54" s="146"/>
+      <c r="F54" s="28"/>
+      <c r="G54" s="48"/>
+      <c r="H54" s="51"/>
+      <c r="I54" s="50"/>
+      <c r="J54" s="31"/>
+      <c r="K54" s="32"/>
+      <c r="L54" s="32"/>
+      <c r="M54" s="32"/>
+      <c r="N54" s="32"/>
+      <c r="O54" s="32"/>
+      <c r="P54" s="32"/>
+      <c r="Q54" s="32"/>
+      <c r="R54" s="33"/>
+    </row>
+    <row r="55" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A55" s="27"/>
+      <c r="B55" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="C55" s="46"/>
+      <c r="D55" s="46"/>
+      <c r="E55" s="146"/>
+      <c r="F55" s="28"/>
+      <c r="G55" s="48"/>
+      <c r="H55" s="51"/>
+      <c r="I55" s="50"/>
+      <c r="J55" s="34"/>
+      <c r="K55" s="35"/>
+      <c r="L55" s="35"/>
+      <c r="M55" s="35"/>
+      <c r="N55" s="35"/>
+      <c r="O55" s="35"/>
+      <c r="P55" s="35"/>
+      <c r="Q55" s="35"/>
+      <c r="R55" s="36"/>
+    </row>
+    <row r="56" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A56" s="27"/>
+      <c r="B56" s="46" t="s">
+        <v>33</v>
+      </c>
+      <c r="C56" s="46"/>
+      <c r="D56" s="46"/>
+      <c r="E56" s="146"/>
+      <c r="F56" s="28"/>
+      <c r="G56" s="48"/>
+      <c r="H56" s="51"/>
+      <c r="I56" s="50"/>
+      <c r="J56" s="34"/>
+      <c r="K56" s="35"/>
+      <c r="L56" s="35"/>
+      <c r="M56" s="35"/>
+      <c r="N56" s="35"/>
+      <c r="O56" s="35"/>
+      <c r="P56" s="35"/>
+      <c r="Q56" s="35"/>
+      <c r="R56" s="36"/>
+    </row>
+    <row r="57" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A57" s="27"/>
+      <c r="B57" s="46" t="s">
+        <v>34</v>
+      </c>
+      <c r="C57" s="46"/>
+      <c r="D57" s="46"/>
+      <c r="E57" s="146"/>
+      <c r="F57" s="28"/>
+      <c r="G57" s="48"/>
+      <c r="H57" s="51"/>
       <c r="I57" s="50"/>
       <c r="J57" s="37"/>
       <c r="K57" s="38"/>
@@ -4326,1009 +5316,9 @@
   </mergeCells>
   <phoneticPr fontId="3"/>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.47244094488188981" right="0.47244094488188981" top="0.44" bottom="0.55118110236220474" header="0.25" footer="0.31496062992125984"/>
+  <pageMargins left="0.47244094488188981" right="0.47244094488188981" top="0.43307086614173229" bottom="0.55118110236220474" header="0.23622047244094491" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="95" orientation="portrait" r:id="rId1"/>
-  <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;R&amp;"ＭＳ Ｐ明朝,標準"&amp;7 Ver.3-12.03-01</oddFooter>
-  </headerFooter>
-  <colBreaks count="1" manualBreakCount="1">
-    <brk id="18" max="1048575" man="1"/>
-  </colBreaks>
-  <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F598854D-5A4C-4289-91C2-F1136C69061F}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:R57"/>
-  <sheetFormatPr defaultColWidth="5" defaultRowHeight="12" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="16384" width="5" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="O1" s="135"/>
-      <c r="P1" s="135"/>
-      <c r="Q1" s="135"/>
-      <c r="R1" s="135"/>
-    </row>
-    <row r="2" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
-    </row>
-    <row r="3" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A3" s="3"/>
-      <c r="O3" s="145"/>
-      <c r="P3" s="145"/>
-      <c r="Q3" s="145"/>
-      <c r="R3" s="145"/>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="O4" s="145"/>
-      <c r="P4" s="145"/>
-      <c r="Q4" s="145"/>
-      <c r="R4" s="145"/>
-    </row>
-    <row r="5" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="N5" s="4"/>
-      <c r="O5" s="4"/>
-      <c r="P5" s="4"/>
-      <c r="Q5" s="4"/>
-      <c r="R5" s="5"/>
-    </row>
-    <row r="6" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="N6" s="4"/>
-      <c r="O6" s="4"/>
-      <c r="P6" s="4"/>
-      <c r="Q6" s="4"/>
-      <c r="R6" s="5"/>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="R7" s="5"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="R8" s="5"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="6"/>
-      <c r="O9" s="6"/>
-      <c r="P9" s="6"/>
-      <c r="Q9" s="6"/>
-      <c r="R9" s="7"/>
-    </row>
-    <row r="10" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="6"/>
-      <c r="O10" s="6"/>
-      <c r="P10" s="6"/>
-      <c r="Q10" s="6"/>
-      <c r="R10" s="8"/>
-    </row>
-    <row r="11" spans="1:18" ht="21" x14ac:dyDescent="0.4">
-      <c r="A11" s="136" t="s">
-        <v>0</v>
-      </c>
-      <c r="B11" s="136"/>
-      <c r="C11" s="136"/>
-      <c r="D11" s="136"/>
-      <c r="E11" s="136"/>
-      <c r="F11" s="136"/>
-      <c r="G11" s="136"/>
-      <c r="H11" s="136"/>
-      <c r="I11" s="136"/>
-      <c r="J11" s="136"/>
-      <c r="K11" s="136"/>
-      <c r="L11" s="136"/>
-      <c r="M11" s="136"/>
-      <c r="N11" s="136"/>
-      <c r="O11" s="136"/>
-      <c r="P11" s="136"/>
-      <c r="Q11" s="136"/>
-      <c r="R11" s="136"/>
-    </row>
-    <row r="14" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="15" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A15" s="137" t="s">
-        <v>1</v>
-      </c>
-      <c r="B15" s="137"/>
-      <c r="C15" s="137"/>
-      <c r="D15" s="137"/>
-      <c r="E15" s="137"/>
-      <c r="F15" s="137"/>
-      <c r="G15" s="137"/>
-      <c r="H15" s="137"/>
-      <c r="I15" s="137"/>
-      <c r="J15" s="137"/>
-      <c r="K15" s="137"/>
-      <c r="L15" s="137"/>
-      <c r="M15" s="137"/>
-      <c r="N15" s="137"/>
-      <c r="O15" s="137"/>
-      <c r="P15" s="137"/>
-      <c r="Q15" s="137"/>
-      <c r="R15" s="137"/>
-    </row>
-    <row r="18" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A18" s="138" t="s">
-        <v>2</v>
-      </c>
-      <c r="B18" s="138"/>
-      <c r="C18" s="138"/>
-      <c r="D18" s="138"/>
-      <c r="E18" s="138"/>
-      <c r="F18" s="138"/>
-      <c r="G18" s="138"/>
-      <c r="H18" s="138"/>
-      <c r="I18" s="138"/>
-      <c r="J18" s="138"/>
-      <c r="K18" s="138"/>
-      <c r="L18" s="138"/>
-      <c r="M18" s="138"/>
-      <c r="N18" s="138"/>
-      <c r="O18" s="138"/>
-      <c r="P18" s="138"/>
-      <c r="Q18" s="138"/>
-      <c r="R18" s="138"/>
-    </row>
-    <row r="19" spans="1:18" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
-    <row r="20" spans="1:18" ht="12.75" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="89" t="s">
-        <v>3</v>
-      </c>
-      <c r="B20" s="90"/>
-      <c r="C20" s="90"/>
-      <c r="D20" s="139"/>
-      <c r="E20" s="140"/>
-      <c r="F20" s="140"/>
-      <c r="G20" s="140"/>
-      <c r="H20" s="140"/>
-      <c r="I20" s="140"/>
-      <c r="J20" s="140"/>
-      <c r="K20" s="140"/>
-      <c r="L20" s="140"/>
-      <c r="M20" s="140"/>
-      <c r="N20" s="140"/>
-      <c r="O20" s="140"/>
-      <c r="P20" s="140"/>
-      <c r="Q20" s="140"/>
-      <c r="R20" s="141"/>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A21" s="91"/>
-      <c r="B21" s="92"/>
-      <c r="C21" s="92"/>
-      <c r="D21" s="142"/>
-      <c r="E21" s="143"/>
-      <c r="F21" s="143"/>
-      <c r="G21" s="143"/>
-      <c r="H21" s="143"/>
-      <c r="I21" s="143"/>
-      <c r="J21" s="143"/>
-      <c r="K21" s="143"/>
-      <c r="L21" s="143"/>
-      <c r="M21" s="143"/>
-      <c r="N21" s="143"/>
-      <c r="O21" s="143"/>
-      <c r="P21" s="143"/>
-      <c r="Q21" s="143"/>
-      <c r="R21" s="144"/>
-    </row>
-    <row r="22" spans="1:18" ht="5.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="91" t="s">
-        <v>4</v>
-      </c>
-      <c r="B22" s="92"/>
-      <c r="C22" s="92"/>
-      <c r="D22" s="9"/>
-      <c r="L22" s="10"/>
-      <c r="M22" s="114" t="s">
-        <v>5</v>
-      </c>
-      <c r="N22" s="115"/>
-      <c r="O22" s="118"/>
-      <c r="P22" s="119"/>
-      <c r="Q22" s="119"/>
-      <c r="R22" s="120"/>
-    </row>
-    <row r="23" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="91"/>
-      <c r="B23" s="92"/>
-      <c r="C23" s="92"/>
-      <c r="D23" s="127"/>
-      <c r="E23" s="128"/>
-      <c r="F23" s="128"/>
-      <c r="G23" s="128"/>
-      <c r="H23" s="128"/>
-      <c r="I23" s="128"/>
-      <c r="J23" s="128"/>
-      <c r="K23" s="128"/>
-      <c r="L23" s="129"/>
-      <c r="M23" s="114"/>
-      <c r="N23" s="115"/>
-      <c r="O23" s="121"/>
-      <c r="P23" s="122"/>
-      <c r="Q23" s="122"/>
-      <c r="R23" s="123"/>
-    </row>
-    <row r="24" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="91"/>
-      <c r="B24" s="92"/>
-      <c r="C24" s="92"/>
-      <c r="D24" s="130"/>
-      <c r="E24" s="128"/>
-      <c r="F24" s="128"/>
-      <c r="G24" s="128"/>
-      <c r="H24" s="128"/>
-      <c r="I24" s="128"/>
-      <c r="J24" s="128"/>
-      <c r="K24" s="128"/>
-      <c r="L24" s="129"/>
-      <c r="M24" s="114"/>
-      <c r="N24" s="115"/>
-      <c r="O24" s="121"/>
-      <c r="P24" s="122"/>
-      <c r="Q24" s="122"/>
-      <c r="R24" s="123"/>
-    </row>
-    <row r="25" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="91"/>
-      <c r="B25" s="92"/>
-      <c r="C25" s="92"/>
-      <c r="D25" s="130"/>
-      <c r="E25" s="128"/>
-      <c r="F25" s="128"/>
-      <c r="G25" s="128"/>
-      <c r="H25" s="128"/>
-      <c r="I25" s="128"/>
-      <c r="J25" s="128"/>
-      <c r="K25" s="128"/>
-      <c r="L25" s="129"/>
-      <c r="M25" s="114"/>
-      <c r="N25" s="115"/>
-      <c r="O25" s="121"/>
-      <c r="P25" s="122"/>
-      <c r="Q25" s="122"/>
-      <c r="R25" s="123"/>
-    </row>
-    <row r="26" spans="1:18" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="91"/>
-      <c r="B26" s="92"/>
-      <c r="C26" s="92"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="14"/>
-      <c r="J26" s="14"/>
-      <c r="K26" s="14"/>
-      <c r="L26" s="15"/>
-      <c r="M26" s="114"/>
-      <c r="N26" s="115"/>
-      <c r="O26" s="121"/>
-      <c r="P26" s="122"/>
-      <c r="Q26" s="122"/>
-      <c r="R26" s="123"/>
-    </row>
-    <row r="27" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="91"/>
-      <c r="B27" s="92"/>
-      <c r="C27" s="92"/>
-      <c r="D27" s="16"/>
-      <c r="F27" s="17"/>
-      <c r="G27" s="18"/>
-      <c r="H27" s="17"/>
-      <c r="I27" s="19"/>
-      <c r="J27" s="19"/>
-      <c r="L27" s="20"/>
-      <c r="M27" s="114"/>
-      <c r="N27" s="115"/>
-      <c r="O27" s="121"/>
-      <c r="P27" s="122"/>
-      <c r="Q27" s="122"/>
-      <c r="R27" s="123"/>
-    </row>
-    <row r="28" spans="1:18" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="97"/>
-      <c r="B28" s="98"/>
-      <c r="C28" s="98"/>
-      <c r="D28" s="21"/>
-      <c r="E28" s="22"/>
-      <c r="F28" s="22"/>
-      <c r="G28" s="22"/>
-      <c r="H28" s="22"/>
-      <c r="I28" s="22"/>
-      <c r="J28" s="22"/>
-      <c r="K28" s="22"/>
-      <c r="L28" s="23"/>
-      <c r="M28" s="116"/>
-      <c r="N28" s="117"/>
-      <c r="O28" s="124"/>
-      <c r="P28" s="125"/>
-      <c r="Q28" s="125"/>
-      <c r="R28" s="126"/>
-    </row>
-    <row r="29" spans="1:18" ht="12.75" thickTop="1" x14ac:dyDescent="0.4"/>
-    <row r="30" spans="1:18" ht="12.75" thickBot="1" x14ac:dyDescent="0.45"/>
-    <row r="31" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="89" t="s">
-        <v>6</v>
-      </c>
-      <c r="B31" s="90"/>
-      <c r="C31" s="90"/>
-      <c r="D31" s="131"/>
-      <c r="E31" s="131"/>
-      <c r="F31" s="131"/>
-      <c r="G31" s="131"/>
-      <c r="H31" s="131"/>
-      <c r="I31" s="131"/>
-      <c r="J31" s="90" t="s">
-        <v>7</v>
-      </c>
-      <c r="K31" s="90"/>
-      <c r="L31" s="90"/>
-      <c r="M31" s="131"/>
-      <c r="N31" s="131"/>
-      <c r="O31" s="131"/>
-      <c r="P31" s="131"/>
-      <c r="Q31" s="131"/>
-      <c r="R31" s="133"/>
-    </row>
-    <row r="32" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="91"/>
-      <c r="B32" s="92"/>
-      <c r="C32" s="92"/>
-      <c r="D32" s="132"/>
-      <c r="E32" s="132"/>
-      <c r="F32" s="132"/>
-      <c r="G32" s="132"/>
-      <c r="H32" s="132"/>
-      <c r="I32" s="132"/>
-      <c r="J32" s="92"/>
-      <c r="K32" s="92"/>
-      <c r="L32" s="92"/>
-      <c r="M32" s="132"/>
-      <c r="N32" s="132"/>
-      <c r="O32" s="132"/>
-      <c r="P32" s="132"/>
-      <c r="Q32" s="132"/>
-      <c r="R32" s="134"/>
-    </row>
-    <row r="33" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="91" t="s">
-        <v>8</v>
-      </c>
-      <c r="B33" s="92"/>
-      <c r="C33" s="92"/>
-      <c r="D33" s="105"/>
-      <c r="E33" s="106"/>
-      <c r="F33" s="106"/>
-      <c r="G33" s="106"/>
-      <c r="H33" s="106"/>
-      <c r="I33" s="106"/>
-      <c r="J33" s="106"/>
-      <c r="K33" s="106"/>
-      <c r="L33" s="106"/>
-      <c r="M33" s="106"/>
-      <c r="N33" s="106"/>
-      <c r="O33" s="106"/>
-      <c r="P33" s="106"/>
-      <c r="Q33" s="106"/>
-      <c r="R33" s="107"/>
-    </row>
-    <row r="34" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="91"/>
-      <c r="B34" s="92"/>
-      <c r="C34" s="92"/>
-      <c r="D34" s="108"/>
-      <c r="E34" s="109"/>
-      <c r="F34" s="109"/>
-      <c r="G34" s="109"/>
-      <c r="H34" s="109"/>
-      <c r="I34" s="109"/>
-      <c r="J34" s="109"/>
-      <c r="K34" s="109"/>
-      <c r="L34" s="109"/>
-      <c r="M34" s="109"/>
-      <c r="N34" s="109"/>
-      <c r="O34" s="109"/>
-      <c r="P34" s="109"/>
-      <c r="Q34" s="109"/>
-      <c r="R34" s="110"/>
-    </row>
-    <row r="35" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="91" t="s">
-        <v>9</v>
-      </c>
-      <c r="B35" s="92"/>
-      <c r="C35" s="92"/>
-      <c r="D35" s="99"/>
-      <c r="E35" s="100"/>
-      <c r="F35" s="100"/>
-      <c r="G35" s="100"/>
-      <c r="H35" s="100"/>
-      <c r="I35" s="100"/>
-      <c r="J35" s="100"/>
-      <c r="K35" s="100"/>
-      <c r="L35" s="100"/>
-      <c r="M35" s="100"/>
-      <c r="N35" s="100"/>
-      <c r="O35" s="100"/>
-      <c r="P35" s="100"/>
-      <c r="Q35" s="100"/>
-      <c r="R35" s="101"/>
-    </row>
-    <row r="36" spans="1:18" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="97"/>
-      <c r="B36" s="98"/>
-      <c r="C36" s="98"/>
-      <c r="D36" s="102"/>
-      <c r="E36" s="103"/>
-      <c r="F36" s="103"/>
-      <c r="G36" s="103"/>
-      <c r="H36" s="103"/>
-      <c r="I36" s="103"/>
-      <c r="J36" s="103"/>
-      <c r="K36" s="103"/>
-      <c r="L36" s="103"/>
-      <c r="M36" s="103"/>
-      <c r="N36" s="103"/>
-      <c r="O36" s="103"/>
-      <c r="P36" s="103"/>
-      <c r="Q36" s="103"/>
-      <c r="R36" s="104"/>
-    </row>
-    <row r="37" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="111"/>
-      <c r="B37" s="112"/>
-      <c r="C37" s="112"/>
-      <c r="D37" s="112"/>
-      <c r="E37" s="112"/>
-      <c r="F37" s="112"/>
-      <c r="G37" s="112"/>
-      <c r="H37" s="112"/>
-      <c r="I37" s="112"/>
-      <c r="J37" s="112"/>
-      <c r="K37" s="112"/>
-      <c r="L37" s="112"/>
-      <c r="M37" s="112"/>
-      <c r="N37" s="112"/>
-      <c r="O37" s="112"/>
-      <c r="P37" s="112"/>
-      <c r="Q37" s="112"/>
-      <c r="R37" s="112"/>
-    </row>
-    <row r="38" spans="1:18" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="113"/>
-      <c r="B38" s="113"/>
-      <c r="C38" s="113"/>
-      <c r="D38" s="113"/>
-      <c r="E38" s="113"/>
-      <c r="F38" s="113"/>
-      <c r="G38" s="113"/>
-      <c r="H38" s="113"/>
-      <c r="I38" s="113"/>
-      <c r="J38" s="113"/>
-      <c r="K38" s="113"/>
-      <c r="L38" s="113"/>
-      <c r="M38" s="113"/>
-      <c r="N38" s="113"/>
-      <c r="O38" s="113"/>
-      <c r="P38" s="113"/>
-      <c r="Q38" s="113"/>
-      <c r="R38" s="113"/>
-    </row>
-    <row r="39" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="89" t="s">
-        <v>10</v>
-      </c>
-      <c r="B39" s="90"/>
-      <c r="C39" s="90"/>
-      <c r="D39" s="90" t="s">
-        <v>11</v>
-      </c>
-      <c r="E39" s="90"/>
-      <c r="F39" s="90"/>
-      <c r="G39" s="93"/>
-      <c r="H39" s="90" t="s">
-        <v>10</v>
-      </c>
-      <c r="I39" s="90"/>
-      <c r="J39" s="90"/>
-      <c r="K39" s="90" t="s">
-        <v>11</v>
-      </c>
-      <c r="L39" s="90"/>
-      <c r="M39" s="90"/>
-      <c r="N39" s="93"/>
-      <c r="O39" s="90" t="s">
-        <v>35</v>
-      </c>
-      <c r="P39" s="90"/>
-      <c r="Q39" s="90"/>
-      <c r="R39" s="95"/>
-    </row>
-    <row r="40" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="91"/>
-      <c r="B40" s="92"/>
-      <c r="C40" s="92"/>
-      <c r="D40" s="92"/>
-      <c r="E40" s="92"/>
-      <c r="F40" s="92"/>
-      <c r="G40" s="94"/>
-      <c r="H40" s="92"/>
-      <c r="I40" s="92"/>
-      <c r="J40" s="92"/>
-      <c r="K40" s="92"/>
-      <c r="L40" s="92"/>
-      <c r="M40" s="92"/>
-      <c r="N40" s="94"/>
-      <c r="O40" s="92"/>
-      <c r="P40" s="92"/>
-      <c r="Q40" s="92"/>
-      <c r="R40" s="96"/>
-    </row>
-    <row r="41" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="64" t="s">
-        <v>13</v>
-      </c>
-      <c r="B41" s="65"/>
-      <c r="C41" s="66"/>
-      <c r="D41" s="70"/>
-      <c r="E41" s="71"/>
-      <c r="F41" s="71"/>
-      <c r="G41" s="72"/>
-      <c r="H41" s="76" t="s">
-        <v>14</v>
-      </c>
-      <c r="I41" s="77"/>
-      <c r="J41" s="78"/>
-      <c r="K41" s="70"/>
-      <c r="L41" s="71"/>
-      <c r="M41" s="71"/>
-      <c r="N41" s="72"/>
-      <c r="O41" s="82"/>
-      <c r="P41" s="82"/>
-      <c r="Q41" s="82"/>
-      <c r="R41" s="83"/>
-    </row>
-    <row r="42" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="67"/>
-      <c r="B42" s="68"/>
-      <c r="C42" s="69"/>
-      <c r="D42" s="73"/>
-      <c r="E42" s="74"/>
-      <c r="F42" s="74"/>
-      <c r="G42" s="75"/>
-      <c r="H42" s="79"/>
-      <c r="I42" s="80"/>
-      <c r="J42" s="81"/>
-      <c r="K42" s="73"/>
-      <c r="L42" s="74"/>
-      <c r="M42" s="74"/>
-      <c r="N42" s="75"/>
-      <c r="O42" s="82"/>
-      <c r="P42" s="82"/>
-      <c r="Q42" s="82"/>
-      <c r="R42" s="83"/>
-    </row>
-    <row r="43" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="64" t="s">
-        <v>15</v>
-      </c>
-      <c r="B43" s="65"/>
-      <c r="C43" s="66"/>
-      <c r="D43" s="70"/>
-      <c r="E43" s="71"/>
-      <c r="F43" s="71"/>
-      <c r="G43" s="72"/>
-      <c r="H43" s="86" t="s">
-        <v>16</v>
-      </c>
-      <c r="I43" s="65"/>
-      <c r="J43" s="66"/>
-      <c r="K43" s="70"/>
-      <c r="L43" s="71"/>
-      <c r="M43" s="71"/>
-      <c r="N43" s="72"/>
-      <c r="O43" s="82"/>
-      <c r="P43" s="82"/>
-      <c r="Q43" s="82"/>
-      <c r="R43" s="83"/>
-    </row>
-    <row r="44" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="67"/>
-      <c r="B44" s="68"/>
-      <c r="C44" s="69"/>
-      <c r="D44" s="73"/>
-      <c r="E44" s="74"/>
-      <c r="F44" s="74"/>
-      <c r="G44" s="75"/>
-      <c r="H44" s="87"/>
-      <c r="I44" s="68"/>
-      <c r="J44" s="69"/>
-      <c r="K44" s="73"/>
-      <c r="L44" s="74"/>
-      <c r="M44" s="74"/>
-      <c r="N44" s="75"/>
-      <c r="O44" s="82"/>
-      <c r="P44" s="82"/>
-      <c r="Q44" s="82"/>
-      <c r="R44" s="83"/>
-    </row>
-    <row r="45" spans="1:18" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A45" s="88" t="s">
-        <v>17</v>
-      </c>
-      <c r="B45" s="54"/>
-      <c r="C45" s="54"/>
-      <c r="D45" s="52"/>
-      <c r="E45" s="52"/>
-      <c r="F45" s="52"/>
-      <c r="G45" s="53"/>
-      <c r="H45" s="54" t="s">
-        <v>17</v>
-      </c>
-      <c r="I45" s="54"/>
-      <c r="J45" s="54"/>
-      <c r="K45" s="52"/>
-      <c r="L45" s="52"/>
-      <c r="M45" s="52"/>
-      <c r="N45" s="53"/>
-      <c r="O45" s="84"/>
-      <c r="P45" s="84"/>
-      <c r="Q45" s="84"/>
-      <c r="R45" s="85"/>
-    </row>
-    <row r="46" spans="1:18" ht="20.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.4"/>
-    <row r="47" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="48" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="24"/>
-      <c r="B48" s="55" t="s">
-        <v>18</v>
-      </c>
-      <c r="C48" s="55"/>
-      <c r="D48" s="55"/>
-      <c r="E48" s="55"/>
-      <c r="F48" s="25"/>
-      <c r="G48" s="56" t="s">
-        <v>36</v>
-      </c>
-      <c r="H48" s="59"/>
-      <c r="I48" s="60"/>
-      <c r="J48" s="24"/>
-      <c r="K48" s="55" t="s">
-        <v>20</v>
-      </c>
-      <c r="L48" s="55"/>
-      <c r="M48" s="55"/>
-      <c r="N48" s="55"/>
-      <c r="O48" s="25"/>
-      <c r="P48" s="56" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q48" s="59"/>
-      <c r="R48" s="60"/>
-    </row>
-    <row r="49" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="26"/>
-      <c r="B49" s="147" t="s">
-        <v>21</v>
-      </c>
-      <c r="C49" s="147"/>
-      <c r="D49" s="147"/>
-      <c r="E49" s="148"/>
-      <c r="G49" s="48"/>
-      <c r="H49" s="51"/>
-      <c r="I49" s="50"/>
-      <c r="J49" s="29"/>
-      <c r="K49" s="61" t="s">
-        <v>22</v>
-      </c>
-      <c r="L49" s="62"/>
-      <c r="M49" s="62"/>
-      <c r="N49" s="63"/>
-      <c r="O49" s="30"/>
-      <c r="P49" s="48"/>
-      <c r="Q49" s="51"/>
-      <c r="R49" s="50"/>
-    </row>
-    <row r="50" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="27"/>
-      <c r="B50" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="C50" s="46"/>
-      <c r="D50" s="46"/>
-      <c r="E50" s="146"/>
-      <c r="F50" s="28"/>
-      <c r="G50" s="48"/>
-      <c r="H50" s="51"/>
-      <c r="I50" s="50"/>
-      <c r="J50" s="29"/>
-      <c r="K50" s="46" t="s">
-        <v>24</v>
-      </c>
-      <c r="L50" s="46"/>
-      <c r="M50" s="46"/>
-      <c r="N50" s="46"/>
-      <c r="O50" s="30"/>
-      <c r="P50" s="48"/>
-      <c r="Q50" s="51"/>
-      <c r="R50" s="50"/>
-    </row>
-    <row r="51" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="27"/>
-      <c r="B51" s="46" t="s">
-        <v>25</v>
-      </c>
-      <c r="C51" s="46"/>
-      <c r="D51" s="46"/>
-      <c r="E51" s="146"/>
-      <c r="F51" s="28"/>
-      <c r="G51" s="48"/>
-      <c r="H51" s="51"/>
-      <c r="I51" s="50"/>
-      <c r="J51" s="29"/>
-      <c r="K51" s="46" t="s">
-        <v>26</v>
-      </c>
-      <c r="L51" s="46"/>
-      <c r="M51" s="46"/>
-      <c r="N51" s="46"/>
-      <c r="O51" s="30"/>
-      <c r="P51" s="48"/>
-      <c r="Q51" s="51"/>
-      <c r="R51" s="50"/>
-    </row>
-    <row r="52" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="27"/>
-      <c r="B52" s="46" t="s">
-        <v>27</v>
-      </c>
-      <c r="C52" s="46"/>
-      <c r="D52" s="46"/>
-      <c r="E52" s="146"/>
-      <c r="F52" s="28"/>
-      <c r="G52" s="48"/>
-      <c r="H52" s="51"/>
-      <c r="I52" s="50"/>
-      <c r="J52" s="29"/>
-      <c r="K52" s="46" t="s">
-        <v>28</v>
-      </c>
-      <c r="L52" s="46"/>
-      <c r="M52" s="46"/>
-      <c r="N52" s="46"/>
-      <c r="O52" s="30"/>
-      <c r="P52" s="48"/>
-      <c r="Q52" s="51"/>
-      <c r="R52" s="50"/>
-    </row>
-    <row r="53" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="27"/>
-      <c r="B53" s="46" t="s">
-        <v>29</v>
-      </c>
-      <c r="C53" s="46"/>
-      <c r="D53" s="46"/>
-      <c r="E53" s="146"/>
-      <c r="F53" s="28"/>
-      <c r="G53" s="48"/>
-      <c r="H53" s="51"/>
-      <c r="I53" s="50"/>
-      <c r="J53" s="29"/>
-      <c r="K53" s="46" t="s">
-        <v>30</v>
-      </c>
-      <c r="L53" s="46"/>
-      <c r="M53" s="46"/>
-      <c r="N53" s="46"/>
-      <c r="O53" s="30"/>
-      <c r="P53" s="48"/>
-      <c r="Q53" s="51"/>
-      <c r="R53" s="50"/>
-    </row>
-    <row r="54" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="27"/>
-      <c r="B54" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="C54" s="46"/>
-      <c r="D54" s="46"/>
-      <c r="E54" s="146"/>
-      <c r="F54" s="28"/>
-      <c r="G54" s="48"/>
-      <c r="H54" s="51"/>
-      <c r="I54" s="50"/>
-      <c r="J54" s="31"/>
-      <c r="K54" s="32"/>
-      <c r="L54" s="32"/>
-      <c r="M54" s="32"/>
-      <c r="N54" s="32"/>
-      <c r="O54" s="32"/>
-      <c r="P54" s="32"/>
-      <c r="Q54" s="32"/>
-      <c r="R54" s="33"/>
-    </row>
-    <row r="55" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="27"/>
-      <c r="B55" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="C55" s="46"/>
-      <c r="D55" s="46"/>
-      <c r="E55" s="146"/>
-      <c r="F55" s="28"/>
-      <c r="G55" s="48"/>
-      <c r="H55" s="51"/>
-      <c r="I55" s="50"/>
-      <c r="J55" s="34"/>
-      <c r="K55" s="35"/>
-      <c r="L55" s="35"/>
-      <c r="M55" s="35"/>
-      <c r="N55" s="35"/>
-      <c r="O55" s="35"/>
-      <c r="P55" s="35"/>
-      <c r="Q55" s="35"/>
-      <c r="R55" s="36"/>
-    </row>
-    <row r="56" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A56" s="27"/>
-      <c r="B56" s="46" t="s">
-        <v>33</v>
-      </c>
-      <c r="C56" s="46"/>
-      <c r="D56" s="46"/>
-      <c r="E56" s="146"/>
-      <c r="F56" s="28"/>
-      <c r="G56" s="48"/>
-      <c r="H56" s="51"/>
-      <c r="I56" s="50"/>
-      <c r="J56" s="34"/>
-      <c r="K56" s="35"/>
-      <c r="L56" s="35"/>
-      <c r="M56" s="35"/>
-      <c r="N56" s="35"/>
-      <c r="O56" s="35"/>
-      <c r="P56" s="35"/>
-      <c r="Q56" s="35"/>
-      <c r="R56" s="36"/>
-    </row>
-    <row r="57" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="27"/>
-      <c r="B57" s="46" t="s">
-        <v>34</v>
-      </c>
-      <c r="C57" s="46"/>
-      <c r="D57" s="46"/>
-      <c r="E57" s="146"/>
-      <c r="F57" s="28"/>
-      <c r="G57" s="48"/>
-      <c r="H57" s="51"/>
-      <c r="I57" s="50"/>
-      <c r="J57" s="37"/>
-      <c r="K57" s="38"/>
-      <c r="L57" s="38"/>
-      <c r="M57" s="38"/>
-      <c r="N57" s="38"/>
-      <c r="O57" s="38"/>
-      <c r="P57" s="38"/>
-      <c r="Q57" s="38"/>
-      <c r="R57" s="39"/>
-    </row>
-  </sheetData>
-  <sheetProtection formatCells="0"/>
-  <mergeCells count="70">
-    <mergeCell ref="O1:R1"/>
-    <mergeCell ref="A11:R11"/>
-    <mergeCell ref="A15:R15"/>
-    <mergeCell ref="A18:R18"/>
-    <mergeCell ref="A20:C21"/>
-    <mergeCell ref="D20:R21"/>
-    <mergeCell ref="O3:R4"/>
-    <mergeCell ref="A22:C28"/>
-    <mergeCell ref="M22:N28"/>
-    <mergeCell ref="O22:R28"/>
-    <mergeCell ref="D23:L25"/>
-    <mergeCell ref="A31:C32"/>
-    <mergeCell ref="D31:I32"/>
-    <mergeCell ref="J31:L32"/>
-    <mergeCell ref="M31:R32"/>
-    <mergeCell ref="A33:C34"/>
-    <mergeCell ref="A35:C36"/>
-    <mergeCell ref="D35:R36"/>
-    <mergeCell ref="D33:R34"/>
-    <mergeCell ref="A37:R38"/>
-    <mergeCell ref="A39:C40"/>
-    <mergeCell ref="D39:G40"/>
-    <mergeCell ref="H39:J40"/>
-    <mergeCell ref="K39:N40"/>
-    <mergeCell ref="O39:R40"/>
-    <mergeCell ref="A41:C42"/>
-    <mergeCell ref="D41:G42"/>
-    <mergeCell ref="H41:J42"/>
-    <mergeCell ref="K41:N42"/>
-    <mergeCell ref="O41:R45"/>
-    <mergeCell ref="A43:C44"/>
-    <mergeCell ref="D43:G44"/>
-    <mergeCell ref="H43:J44"/>
-    <mergeCell ref="K43:N44"/>
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="B50:E50"/>
-    <mergeCell ref="G50:I50"/>
-    <mergeCell ref="K50:N50"/>
-    <mergeCell ref="P50:R50"/>
-    <mergeCell ref="D45:G45"/>
-    <mergeCell ref="H45:J45"/>
-    <mergeCell ref="K45:N45"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="G48:I48"/>
-    <mergeCell ref="K48:N48"/>
-    <mergeCell ref="P48:R48"/>
-    <mergeCell ref="B49:E49"/>
-    <mergeCell ref="G49:I49"/>
-    <mergeCell ref="K49:N49"/>
-    <mergeCell ref="P49:R49"/>
-    <mergeCell ref="B51:E51"/>
-    <mergeCell ref="G51:I51"/>
-    <mergeCell ref="K51:N51"/>
-    <mergeCell ref="P51:R51"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="G52:I52"/>
-    <mergeCell ref="K52:N52"/>
-    <mergeCell ref="P52:R52"/>
-    <mergeCell ref="B53:E53"/>
-    <mergeCell ref="G53:I53"/>
-    <mergeCell ref="K53:N53"/>
-    <mergeCell ref="P53:R53"/>
-    <mergeCell ref="B54:E54"/>
-    <mergeCell ref="G54:I54"/>
-    <mergeCell ref="B55:E55"/>
-    <mergeCell ref="G55:I55"/>
-    <mergeCell ref="B56:E56"/>
-    <mergeCell ref="G56:I56"/>
-    <mergeCell ref="B57:E57"/>
-    <mergeCell ref="G57:I57"/>
-  </mergeCells>
-  <phoneticPr fontId="3"/>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.47244094488188981" right="0.47244094488188981" top="0.44" bottom="0.55118110236220474" header="0.25" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="95" orientation="portrait" r:id="rId1"/>
-  <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;R&amp;"ＭＳ Ｐ明朝,標準"&amp;7 Ver.3-12.03-01</oddFooter>
-  </headerFooter>
+  <headerFooter alignWithMargins="0"/>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="18" max="1048575" man="1"/>
   </colBreaks>
@@ -5361,16 +5351,16 @@
     </row>
     <row r="3" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A3" s="3"/>
-      <c r="O3" s="145"/>
-      <c r="P3" s="145"/>
-      <c r="Q3" s="145"/>
-      <c r="R3" s="145"/>
+      <c r="O3" s="136"/>
+      <c r="P3" s="136"/>
+      <c r="Q3" s="136"/>
+      <c r="R3" s="136"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="O4" s="145"/>
-      <c r="P4" s="145"/>
-      <c r="Q4" s="145"/>
-      <c r="R4" s="145"/>
+      <c r="O4" s="136"/>
+      <c r="P4" s="136"/>
+      <c r="Q4" s="136"/>
+      <c r="R4" s="136"/>
     </row>
     <row r="5" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="N5" s="4"/>
@@ -5433,121 +5423,121 @@
       <c r="R10" s="8"/>
     </row>
     <row r="11" spans="1:18" ht="21" x14ac:dyDescent="0.4">
-      <c r="A11" s="136" t="s">
+      <c r="A11" s="137" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="136"/>
-      <c r="C11" s="136"/>
-      <c r="D11" s="136"/>
-      <c r="E11" s="136"/>
-      <c r="F11" s="136"/>
-      <c r="G11" s="136"/>
-      <c r="H11" s="136"/>
-      <c r="I11" s="136"/>
-      <c r="J11" s="136"/>
-      <c r="K11" s="136"/>
-      <c r="L11" s="136"/>
-      <c r="M11" s="136"/>
-      <c r="N11" s="136"/>
-      <c r="O11" s="136"/>
-      <c r="P11" s="136"/>
-      <c r="Q11" s="136"/>
-      <c r="R11" s="136"/>
+      <c r="B11" s="137"/>
+      <c r="C11" s="137"/>
+      <c r="D11" s="137"/>
+      <c r="E11" s="137"/>
+      <c r="F11" s="137"/>
+      <c r="G11" s="137"/>
+      <c r="H11" s="137"/>
+      <c r="I11" s="137"/>
+      <c r="J11" s="137"/>
+      <c r="K11" s="137"/>
+      <c r="L11" s="137"/>
+      <c r="M11" s="137"/>
+      <c r="N11" s="137"/>
+      <c r="O11" s="137"/>
+      <c r="P11" s="137"/>
+      <c r="Q11" s="137"/>
+      <c r="R11" s="137"/>
     </row>
     <row r="14" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="15" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A15" s="137" t="s">
+      <c r="A15" s="138" t="s">
         <v>1</v>
       </c>
-      <c r="B15" s="137"/>
-      <c r="C15" s="137"/>
-      <c r="D15" s="137"/>
-      <c r="E15" s="137"/>
-      <c r="F15" s="137"/>
-      <c r="G15" s="137"/>
-      <c r="H15" s="137"/>
-      <c r="I15" s="137"/>
-      <c r="J15" s="137"/>
-      <c r="K15" s="137"/>
-      <c r="L15" s="137"/>
-      <c r="M15" s="137"/>
-      <c r="N15" s="137"/>
-      <c r="O15" s="137"/>
-      <c r="P15" s="137"/>
-      <c r="Q15" s="137"/>
-      <c r="R15" s="137"/>
+      <c r="B15" s="138"/>
+      <c r="C15" s="138"/>
+      <c r="D15" s="138"/>
+      <c r="E15" s="138"/>
+      <c r="F15" s="138"/>
+      <c r="G15" s="138"/>
+      <c r="H15" s="138"/>
+      <c r="I15" s="138"/>
+      <c r="J15" s="138"/>
+      <c r="K15" s="138"/>
+      <c r="L15" s="138"/>
+      <c r="M15" s="138"/>
+      <c r="N15" s="138"/>
+      <c r="O15" s="138"/>
+      <c r="P15" s="138"/>
+      <c r="Q15" s="138"/>
+      <c r="R15" s="138"/>
     </row>
     <row r="18" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A18" s="138" t="s">
+      <c r="A18" s="139" t="s">
         <v>2</v>
       </c>
-      <c r="B18" s="138"/>
-      <c r="C18" s="138"/>
-      <c r="D18" s="138"/>
-      <c r="E18" s="138"/>
-      <c r="F18" s="138"/>
-      <c r="G18" s="138"/>
-      <c r="H18" s="138"/>
-      <c r="I18" s="138"/>
-      <c r="J18" s="138"/>
-      <c r="K18" s="138"/>
-      <c r="L18" s="138"/>
-      <c r="M18" s="138"/>
-      <c r="N18" s="138"/>
-      <c r="O18" s="138"/>
-      <c r="P18" s="138"/>
-      <c r="Q18" s="138"/>
-      <c r="R18" s="138"/>
+      <c r="B18" s="139"/>
+      <c r="C18" s="139"/>
+      <c r="D18" s="139"/>
+      <c r="E18" s="139"/>
+      <c r="F18" s="139"/>
+      <c r="G18" s="139"/>
+      <c r="H18" s="139"/>
+      <c r="I18" s="139"/>
+      <c r="J18" s="139"/>
+      <c r="K18" s="139"/>
+      <c r="L18" s="139"/>
+      <c r="M18" s="139"/>
+      <c r="N18" s="139"/>
+      <c r="O18" s="139"/>
+      <c r="P18" s="139"/>
+      <c r="Q18" s="139"/>
+      <c r="R18" s="139"/>
     </row>
     <row r="19" spans="1:18" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="20" spans="1:18" ht="12.75" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="89" t="s">
+      <c r="A20" s="108" t="s">
         <v>3</v>
       </c>
-      <c r="B20" s="90"/>
-      <c r="C20" s="90"/>
-      <c r="D20" s="139"/>
-      <c r="E20" s="140"/>
-      <c r="F20" s="140"/>
-      <c r="G20" s="140"/>
-      <c r="H20" s="140"/>
-      <c r="I20" s="140"/>
-      <c r="J20" s="140"/>
-      <c r="K20" s="140"/>
-      <c r="L20" s="140"/>
-      <c r="M20" s="140"/>
-      <c r="N20" s="140"/>
-      <c r="O20" s="140"/>
-      <c r="P20" s="140"/>
-      <c r="Q20" s="140"/>
-      <c r="R20" s="141"/>
+      <c r="B20" s="109"/>
+      <c r="C20" s="109"/>
+      <c r="D20" s="140"/>
+      <c r="E20" s="141"/>
+      <c r="F20" s="141"/>
+      <c r="G20" s="141"/>
+      <c r="H20" s="141"/>
+      <c r="I20" s="141"/>
+      <c r="J20" s="141"/>
+      <c r="K20" s="141"/>
+      <c r="L20" s="141"/>
+      <c r="M20" s="141"/>
+      <c r="N20" s="141"/>
+      <c r="O20" s="141"/>
+      <c r="P20" s="141"/>
+      <c r="Q20" s="141"/>
+      <c r="R20" s="142"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A21" s="91"/>
-      <c r="B21" s="92"/>
-      <c r="C21" s="92"/>
-      <c r="D21" s="142"/>
-      <c r="E21" s="143"/>
-      <c r="F21" s="143"/>
-      <c r="G21" s="143"/>
-      <c r="H21" s="143"/>
-      <c r="I21" s="143"/>
-      <c r="J21" s="143"/>
-      <c r="K21" s="143"/>
-      <c r="L21" s="143"/>
-      <c r="M21" s="143"/>
-      <c r="N21" s="143"/>
-      <c r="O21" s="143"/>
-      <c r="P21" s="143"/>
-      <c r="Q21" s="143"/>
-      <c r="R21" s="144"/>
+      <c r="A21" s="89"/>
+      <c r="B21" s="90"/>
+      <c r="C21" s="90"/>
+      <c r="D21" s="143"/>
+      <c r="E21" s="144"/>
+      <c r="F21" s="144"/>
+      <c r="G21" s="144"/>
+      <c r="H21" s="144"/>
+      <c r="I21" s="144"/>
+      <c r="J21" s="144"/>
+      <c r="K21" s="144"/>
+      <c r="L21" s="144"/>
+      <c r="M21" s="144"/>
+      <c r="N21" s="144"/>
+      <c r="O21" s="144"/>
+      <c r="P21" s="144"/>
+      <c r="Q21" s="144"/>
+      <c r="R21" s="145"/>
     </row>
     <row r="22" spans="1:18" ht="5.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="91" t="s">
+      <c r="A22" s="89" t="s">
         <v>4</v>
       </c>
-      <c r="B22" s="92"/>
-      <c r="C22" s="92"/>
+      <c r="B22" s="90"/>
+      <c r="C22" s="90"/>
       <c r="D22" s="9"/>
       <c r="L22" s="10"/>
       <c r="M22" s="114" t="s">
@@ -5560,9 +5550,9 @@
       <c r="R22" s="120"/>
     </row>
     <row r="23" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="91"/>
-      <c r="B23" s="92"/>
-      <c r="C23" s="92"/>
+      <c r="A23" s="89"/>
+      <c r="B23" s="90"/>
+      <c r="C23" s="90"/>
       <c r="D23" s="127"/>
       <c r="E23" s="128"/>
       <c r="F23" s="128"/>
@@ -5580,9 +5570,9 @@
       <c r="R23" s="123"/>
     </row>
     <row r="24" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="91"/>
-      <c r="B24" s="92"/>
-      <c r="C24" s="92"/>
+      <c r="A24" s="89"/>
+      <c r="B24" s="90"/>
+      <c r="C24" s="90"/>
       <c r="D24" s="130"/>
       <c r="E24" s="128"/>
       <c r="F24" s="128"/>
@@ -5600,9 +5590,9 @@
       <c r="R24" s="123"/>
     </row>
     <row r="25" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="91"/>
-      <c r="B25" s="92"/>
-      <c r="C25" s="92"/>
+      <c r="A25" s="89"/>
+      <c r="B25" s="90"/>
+      <c r="C25" s="90"/>
       <c r="D25" s="130"/>
       <c r="E25" s="128"/>
       <c r="F25" s="128"/>
@@ -5620,9 +5610,9 @@
       <c r="R25" s="123"/>
     </row>
     <row r="26" spans="1:18" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="91"/>
-      <c r="B26" s="92"/>
-      <c r="C26" s="92"/>
+      <c r="A26" s="89"/>
+      <c r="B26" s="90"/>
+      <c r="C26" s="90"/>
       <c r="D26" s="11"/>
       <c r="E26" s="12"/>
       <c r="F26" s="13"/>
@@ -5640,9 +5630,9 @@
       <c r="R26" s="123"/>
     </row>
     <row r="27" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="91"/>
-      <c r="B27" s="92"/>
-      <c r="C27" s="92"/>
+      <c r="A27" s="89"/>
+      <c r="B27" s="90"/>
+      <c r="C27" s="90"/>
       <c r="D27" s="16"/>
       <c r="F27" s="17"/>
       <c r="G27" s="18"/>
@@ -5680,22 +5670,22 @@
     <row r="29" spans="1:18" ht="12.75" thickTop="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="1:18" ht="12.75" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="31" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="89" t="s">
+      <c r="A31" s="108" t="s">
         <v>6</v>
       </c>
-      <c r="B31" s="90"/>
-      <c r="C31" s="90"/>
+      <c r="B31" s="109"/>
+      <c r="C31" s="109"/>
       <c r="D31" s="131"/>
       <c r="E31" s="131"/>
       <c r="F31" s="131"/>
       <c r="G31" s="131"/>
       <c r="H31" s="131"/>
       <c r="I31" s="131"/>
-      <c r="J31" s="90" t="s">
+      <c r="J31" s="109" t="s">
         <v>7</v>
       </c>
-      <c r="K31" s="90"/>
-      <c r="L31" s="90"/>
+      <c r="K31" s="109"/>
+      <c r="L31" s="109"/>
       <c r="M31" s="131"/>
       <c r="N31" s="131"/>
       <c r="O31" s="131"/>
@@ -5704,18 +5694,18 @@
       <c r="R31" s="133"/>
     </row>
     <row r="32" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="91"/>
-      <c r="B32" s="92"/>
-      <c r="C32" s="92"/>
+      <c r="A32" s="89"/>
+      <c r="B32" s="90"/>
+      <c r="C32" s="90"/>
       <c r="D32" s="132"/>
       <c r="E32" s="132"/>
       <c r="F32" s="132"/>
       <c r="G32" s="132"/>
       <c r="H32" s="132"/>
       <c r="I32" s="132"/>
-      <c r="J32" s="92"/>
-      <c r="K32" s="92"/>
-      <c r="L32" s="92"/>
+      <c r="J32" s="90"/>
+      <c r="K32" s="90"/>
+      <c r="L32" s="90"/>
       <c r="M32" s="132"/>
       <c r="N32" s="132"/>
       <c r="O32" s="132"/>
@@ -5724,53 +5714,53 @@
       <c r="R32" s="134"/>
     </row>
     <row r="33" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="91" t="s">
+      <c r="A33" s="89" t="s">
         <v>8</v>
       </c>
-      <c r="B33" s="92"/>
-      <c r="C33" s="92"/>
-      <c r="D33" s="105"/>
-      <c r="E33" s="106"/>
-      <c r="F33" s="106"/>
-      <c r="G33" s="106"/>
-      <c r="H33" s="106"/>
-      <c r="I33" s="106"/>
-      <c r="J33" s="106"/>
-      <c r="K33" s="106"/>
-      <c r="L33" s="106"/>
-      <c r="M33" s="106"/>
-      <c r="N33" s="106"/>
-      <c r="O33" s="106"/>
-      <c r="P33" s="106"/>
-      <c r="Q33" s="106"/>
-      <c r="R33" s="107"/>
+      <c r="B33" s="90"/>
+      <c r="C33" s="90"/>
+      <c r="D33" s="91"/>
+      <c r="E33" s="92"/>
+      <c r="F33" s="92"/>
+      <c r="G33" s="92"/>
+      <c r="H33" s="92"/>
+      <c r="I33" s="92"/>
+      <c r="J33" s="92"/>
+      <c r="K33" s="92"/>
+      <c r="L33" s="92"/>
+      <c r="M33" s="92"/>
+      <c r="N33" s="92"/>
+      <c r="O33" s="92"/>
+      <c r="P33" s="92"/>
+      <c r="Q33" s="92"/>
+      <c r="R33" s="93"/>
     </row>
     <row r="34" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="91"/>
-      <c r="B34" s="92"/>
-      <c r="C34" s="92"/>
-      <c r="D34" s="108"/>
-      <c r="E34" s="109"/>
-      <c r="F34" s="109"/>
-      <c r="G34" s="109"/>
-      <c r="H34" s="109"/>
-      <c r="I34" s="109"/>
-      <c r="J34" s="109"/>
-      <c r="K34" s="109"/>
-      <c r="L34" s="109"/>
-      <c r="M34" s="109"/>
-      <c r="N34" s="109"/>
-      <c r="O34" s="109"/>
-      <c r="P34" s="109"/>
-      <c r="Q34" s="109"/>
-      <c r="R34" s="110"/>
+      <c r="A34" s="89"/>
+      <c r="B34" s="90"/>
+      <c r="C34" s="90"/>
+      <c r="D34" s="94"/>
+      <c r="E34" s="95"/>
+      <c r="F34" s="95"/>
+      <c r="G34" s="95"/>
+      <c r="H34" s="95"/>
+      <c r="I34" s="95"/>
+      <c r="J34" s="95"/>
+      <c r="K34" s="95"/>
+      <c r="L34" s="95"/>
+      <c r="M34" s="95"/>
+      <c r="N34" s="95"/>
+      <c r="O34" s="95"/>
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="96"/>
     </row>
     <row r="35" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="91" t="s">
+      <c r="A35" s="89" t="s">
         <v>9</v>
       </c>
-      <c r="B35" s="92"/>
-      <c r="C35" s="92"/>
+      <c r="B35" s="90"/>
+      <c r="C35" s="90"/>
       <c r="D35" s="99"/>
       <c r="E35" s="100"/>
       <c r="F35" s="100"/>
@@ -5808,94 +5798,94 @@
       <c r="R36" s="104"/>
     </row>
     <row r="37" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="111"/>
-      <c r="B37" s="112"/>
-      <c r="C37" s="112"/>
-      <c r="D37" s="112"/>
-      <c r="E37" s="112"/>
-      <c r="F37" s="112"/>
-      <c r="G37" s="112"/>
-      <c r="H37" s="112"/>
-      <c r="I37" s="112"/>
-      <c r="J37" s="112"/>
-      <c r="K37" s="112"/>
-      <c r="L37" s="112"/>
-      <c r="M37" s="112"/>
-      <c r="N37" s="112"/>
-      <c r="O37" s="112"/>
-      <c r="P37" s="112"/>
-      <c r="Q37" s="112"/>
-      <c r="R37" s="112"/>
+      <c r="A37" s="105"/>
+      <c r="B37" s="106"/>
+      <c r="C37" s="106"/>
+      <c r="D37" s="106"/>
+      <c r="E37" s="106"/>
+      <c r="F37" s="106"/>
+      <c r="G37" s="106"/>
+      <c r="H37" s="106"/>
+      <c r="I37" s="106"/>
+      <c r="J37" s="106"/>
+      <c r="K37" s="106"/>
+      <c r="L37" s="106"/>
+      <c r="M37" s="106"/>
+      <c r="N37" s="106"/>
+      <c r="O37" s="106"/>
+      <c r="P37" s="106"/>
+      <c r="Q37" s="106"/>
+      <c r="R37" s="106"/>
     </row>
     <row r="38" spans="1:18" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="113"/>
-      <c r="B38" s="113"/>
-      <c r="C38" s="113"/>
-      <c r="D38" s="113"/>
-      <c r="E38" s="113"/>
-      <c r="F38" s="113"/>
-      <c r="G38" s="113"/>
-      <c r="H38" s="113"/>
-      <c r="I38" s="113"/>
-      <c r="J38" s="113"/>
-      <c r="K38" s="113"/>
-      <c r="L38" s="113"/>
-      <c r="M38" s="113"/>
-      <c r="N38" s="113"/>
-      <c r="O38" s="113"/>
-      <c r="P38" s="113"/>
-      <c r="Q38" s="113"/>
-      <c r="R38" s="113"/>
+      <c r="A38" s="107"/>
+      <c r="B38" s="107"/>
+      <c r="C38" s="107"/>
+      <c r="D38" s="107"/>
+      <c r="E38" s="107"/>
+      <c r="F38" s="107"/>
+      <c r="G38" s="107"/>
+      <c r="H38" s="107"/>
+      <c r="I38" s="107"/>
+      <c r="J38" s="107"/>
+      <c r="K38" s="107"/>
+      <c r="L38" s="107"/>
+      <c r="M38" s="107"/>
+      <c r="N38" s="107"/>
+      <c r="O38" s="107"/>
+      <c r="P38" s="107"/>
+      <c r="Q38" s="107"/>
+      <c r="R38" s="107"/>
     </row>
     <row r="39" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="89" t="s">
+      <c r="A39" s="108" t="s">
         <v>10</v>
       </c>
-      <c r="B39" s="90"/>
-      <c r="C39" s="90"/>
-      <c r="D39" s="90" t="s">
+      <c r="B39" s="109"/>
+      <c r="C39" s="109"/>
+      <c r="D39" s="109" t="s">
         <v>11</v>
       </c>
-      <c r="E39" s="90"/>
-      <c r="F39" s="90"/>
-      <c r="G39" s="93"/>
-      <c r="H39" s="90" t="s">
+      <c r="E39" s="109"/>
+      <c r="F39" s="109"/>
+      <c r="G39" s="110"/>
+      <c r="H39" s="109" t="s">
         <v>10</v>
       </c>
-      <c r="I39" s="90"/>
-      <c r="J39" s="90"/>
-      <c r="K39" s="90" t="s">
+      <c r="I39" s="109"/>
+      <c r="J39" s="109"/>
+      <c r="K39" s="109" t="s">
         <v>11</v>
       </c>
-      <c r="L39" s="90"/>
-      <c r="M39" s="90"/>
-      <c r="N39" s="93"/>
-      <c r="O39" s="90" t="s">
+      <c r="L39" s="109"/>
+      <c r="M39" s="109"/>
+      <c r="N39" s="110"/>
+      <c r="O39" s="109" t="s">
         <v>37</v>
       </c>
-      <c r="P39" s="90"/>
-      <c r="Q39" s="90"/>
-      <c r="R39" s="95"/>
+      <c r="P39" s="109"/>
+      <c r="Q39" s="109"/>
+      <c r="R39" s="112"/>
     </row>
     <row r="40" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="91"/>
-      <c r="B40" s="92"/>
-      <c r="C40" s="92"/>
-      <c r="D40" s="92"/>
-      <c r="E40" s="92"/>
-      <c r="F40" s="92"/>
-      <c r="G40" s="94"/>
-      <c r="H40" s="92"/>
-      <c r="I40" s="92"/>
-      <c r="J40" s="92"/>
-      <c r="K40" s="92"/>
-      <c r="L40" s="92"/>
-      <c r="M40" s="92"/>
-      <c r="N40" s="94"/>
-      <c r="O40" s="92"/>
-      <c r="P40" s="92"/>
-      <c r="Q40" s="92"/>
-      <c r="R40" s="96"/>
+      <c r="A40" s="89"/>
+      <c r="B40" s="90"/>
+      <c r="C40" s="90"/>
+      <c r="D40" s="90"/>
+      <c r="E40" s="90"/>
+      <c r="F40" s="90"/>
+      <c r="G40" s="111"/>
+      <c r="H40" s="90"/>
+      <c r="I40" s="90"/>
+      <c r="J40" s="90"/>
+      <c r="K40" s="90"/>
+      <c r="L40" s="90"/>
+      <c r="M40" s="90"/>
+      <c r="N40" s="111"/>
+      <c r="O40" s="90"/>
+      <c r="P40" s="90"/>
+      <c r="Q40" s="90"/>
+      <c r="R40" s="113"/>
     </row>
     <row r="41" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="64" t="s">
@@ -5991,21 +5981,21 @@
       <c r="A45" s="88" t="s">
         <v>17</v>
       </c>
-      <c r="B45" s="54"/>
-      <c r="C45" s="54"/>
-      <c r="D45" s="52"/>
-      <c r="E45" s="52"/>
-      <c r="F45" s="52"/>
-      <c r="G45" s="53"/>
-      <c r="H45" s="54" t="s">
+      <c r="B45" s="60"/>
+      <c r="C45" s="60"/>
+      <c r="D45" s="58"/>
+      <c r="E45" s="58"/>
+      <c r="F45" s="58"/>
+      <c r="G45" s="59"/>
+      <c r="H45" s="60" t="s">
         <v>17</v>
       </c>
-      <c r="I45" s="54"/>
-      <c r="J45" s="54"/>
-      <c r="K45" s="52"/>
-      <c r="L45" s="52"/>
-      <c r="M45" s="52"/>
-      <c r="N45" s="53"/>
+      <c r="I45" s="60"/>
+      <c r="J45" s="60"/>
+      <c r="K45" s="58"/>
+      <c r="L45" s="58"/>
+      <c r="M45" s="58"/>
+      <c r="N45" s="59"/>
       <c r="O45" s="163"/>
       <c r="P45" s="164"/>
       <c r="Q45" s="164"/>
@@ -6014,13 +6004,13 @@
     <row r="46" spans="1:18" ht="20.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.4"/>
     <row r="47" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="48" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="56" t="s">
+      <c r="A48" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="B48" s="59"/>
-      <c r="C48" s="59"/>
-      <c r="D48" s="59"/>
-      <c r="E48" s="60"/>
+      <c r="B48" s="53"/>
+      <c r="C48" s="53"/>
+      <c r="D48" s="53"/>
+      <c r="E48" s="54"/>
       <c r="F48" s="158" t="s">
         <v>39</v>
       </c>
@@ -6029,13 +6019,13 @@
         <v>40</v>
       </c>
       <c r="I48" s="157"/>
-      <c r="J48" s="56" t="s">
+      <c r="J48" s="52" t="s">
         <v>20</v>
       </c>
-      <c r="K48" s="59"/>
-      <c r="L48" s="59"/>
-      <c r="M48" s="59"/>
-      <c r="N48" s="60"/>
+      <c r="K48" s="53"/>
+      <c r="L48" s="53"/>
+      <c r="M48" s="53"/>
+      <c r="N48" s="54"/>
       <c r="O48" s="158" t="s">
         <v>39</v>
       </c>
@@ -6046,7 +6036,7 @@
       <c r="R48" s="157"/>
     </row>
     <row r="49" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="63" t="s">
+      <c r="A49" s="57" t="s">
         <v>21</v>
       </c>
       <c r="B49" s="149"/>
@@ -6057,7 +6047,7 @@
       <c r="G49" s="152"/>
       <c r="H49" s="153"/>
       <c r="I49" s="154"/>
-      <c r="J49" s="63" t="s">
+      <c r="J49" s="57" t="s">
         <v>22</v>
       </c>
       <c r="K49" s="149"/>
@@ -6070,7 +6060,7 @@
       <c r="R49" s="154"/>
     </row>
     <row r="50" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="63" t="s">
+      <c r="A50" s="57" t="s">
         <v>23</v>
       </c>
       <c r="B50" s="149"/>
@@ -6081,7 +6071,7 @@
       <c r="G50" s="152"/>
       <c r="H50" s="153"/>
       <c r="I50" s="154"/>
-      <c r="J50" s="63" t="s">
+      <c r="J50" s="57" t="s">
         <v>24</v>
       </c>
       <c r="K50" s="149"/>
@@ -6094,7 +6084,7 @@
       <c r="R50" s="154"/>
     </row>
     <row r="51" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="63" t="s">
+      <c r="A51" s="57" t="s">
         <v>25</v>
       </c>
       <c r="B51" s="149"/>
@@ -6105,20 +6095,20 @@
       <c r="G51" s="152"/>
       <c r="H51" s="153"/>
       <c r="I51" s="154"/>
-      <c r="J51" s="63" t="s">
+      <c r="J51" s="57" t="s">
         <v>26</v>
       </c>
       <c r="K51" s="46"/>
       <c r="L51" s="46"/>
       <c r="M51" s="46"/>
-      <c r="N51" s="61"/>
+      <c r="N51" s="55"/>
       <c r="O51" s="151"/>
       <c r="P51" s="152"/>
       <c r="Q51" s="153"/>
       <c r="R51" s="154"/>
     </row>
     <row r="52" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="63" t="s">
+      <c r="A52" s="57" t="s">
         <v>27</v>
       </c>
       <c r="B52" s="149"/>
@@ -6129,20 +6119,20 @@
       <c r="G52" s="152"/>
       <c r="H52" s="153"/>
       <c r="I52" s="154"/>
-      <c r="J52" s="63" t="s">
+      <c r="J52" s="57" t="s">
         <v>28</v>
       </c>
       <c r="K52" s="46"/>
       <c r="L52" s="46"/>
       <c r="M52" s="46"/>
-      <c r="N52" s="61"/>
+      <c r="N52" s="55"/>
       <c r="O52" s="48"/>
       <c r="P52" s="155"/>
       <c r="Q52" s="51"/>
       <c r="R52" s="50"/>
     </row>
     <row r="53" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="63" t="s">
+      <c r="A53" s="57" t="s">
         <v>29</v>
       </c>
       <c r="B53" s="149"/>
@@ -6153,7 +6143,7 @@
       <c r="G53" s="152"/>
       <c r="H53" s="153"/>
       <c r="I53" s="154"/>
-      <c r="J53" s="63" t="s">
+      <c r="J53" s="57" t="s">
         <v>30</v>
       </c>
       <c r="K53" s="149"/>
@@ -6166,7 +6156,7 @@
       <c r="R53" s="154"/>
     </row>
     <row r="54" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="63" t="s">
+      <c r="A54" s="57" t="s">
         <v>31</v>
       </c>
       <c r="B54" s="149"/>
@@ -6188,7 +6178,7 @@
       <c r="R54" s="33"/>
     </row>
     <row r="55" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="63" t="s">
+      <c r="A55" s="57" t="s">
         <v>32</v>
       </c>
       <c r="B55" s="149"/>
@@ -6210,7 +6200,7 @@
       <c r="R55" s="36"/>
     </row>
     <row r="56" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A56" s="63" t="s">
+      <c r="A56" s="57" t="s">
         <v>33</v>
       </c>
       <c r="B56" s="149"/>
@@ -6232,7 +6222,7 @@
       <c r="R56" s="36"/>
     </row>
     <row r="57" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="63" t="s">
+      <c r="A57" s="57" t="s">
         <v>34</v>
       </c>
       <c r="B57" s="149"/>
@@ -6349,9 +6339,7 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.47244094488188981" right="0.47244094488188981" top="0.44" bottom="0.55118110236220474" header="0.25" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="95" orientation="portrait" r:id="rId1"/>
-  <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;R&amp;"ＭＳ Ｐ明朝,標準"&amp;7Ver.3-12.03-01</oddFooter>
-  </headerFooter>
+  <headerFooter alignWithMargins="0"/>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="18" max="1048575" man="1"/>
   </colBreaks>
@@ -6384,16 +6372,16 @@
     </row>
     <row r="3" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A3" s="3"/>
-      <c r="O3" s="145"/>
-      <c r="P3" s="145"/>
-      <c r="Q3" s="145"/>
-      <c r="R3" s="145"/>
+      <c r="O3" s="136"/>
+      <c r="P3" s="136"/>
+      <c r="Q3" s="136"/>
+      <c r="R3" s="136"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="O4" s="145"/>
-      <c r="P4" s="145"/>
-      <c r="Q4" s="145"/>
-      <c r="R4" s="145"/>
+      <c r="O4" s="136"/>
+      <c r="P4" s="136"/>
+      <c r="Q4" s="136"/>
+      <c r="R4" s="136"/>
     </row>
     <row r="5" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="N5" s="4"/>
@@ -6529,41 +6517,41 @@
       </c>
       <c r="B20" s="229"/>
       <c r="C20" s="230"/>
-      <c r="D20" s="139"/>
-      <c r="E20" s="140"/>
-      <c r="F20" s="140"/>
-      <c r="G20" s="140"/>
-      <c r="H20" s="140"/>
-      <c r="I20" s="140"/>
-      <c r="J20" s="140"/>
-      <c r="K20" s="140"/>
-      <c r="L20" s="140"/>
-      <c r="M20" s="140"/>
-      <c r="N20" s="140"/>
-      <c r="O20" s="140"/>
-      <c r="P20" s="140"/>
-      <c r="Q20" s="140"/>
-      <c r="R20" s="141"/>
+      <c r="D20" s="140"/>
+      <c r="E20" s="141"/>
+      <c r="F20" s="141"/>
+      <c r="G20" s="141"/>
+      <c r="H20" s="141"/>
+      <c r="I20" s="141"/>
+      <c r="J20" s="141"/>
+      <c r="K20" s="141"/>
+      <c r="L20" s="141"/>
+      <c r="M20" s="141"/>
+      <c r="N20" s="141"/>
+      <c r="O20" s="141"/>
+      <c r="P20" s="141"/>
+      <c r="Q20" s="141"/>
+      <c r="R20" s="142"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A21" s="231"/>
       <c r="B21" s="232"/>
       <c r="C21" s="233"/>
-      <c r="D21" s="142"/>
-      <c r="E21" s="143"/>
-      <c r="F21" s="143"/>
-      <c r="G21" s="143"/>
-      <c r="H21" s="143"/>
-      <c r="I21" s="143"/>
-      <c r="J21" s="143"/>
-      <c r="K21" s="143"/>
-      <c r="L21" s="143"/>
-      <c r="M21" s="143"/>
-      <c r="N21" s="143"/>
-      <c r="O21" s="143"/>
-      <c r="P21" s="143"/>
-      <c r="Q21" s="143"/>
-      <c r="R21" s="144"/>
+      <c r="D21" s="143"/>
+      <c r="E21" s="144"/>
+      <c r="F21" s="144"/>
+      <c r="G21" s="144"/>
+      <c r="H21" s="144"/>
+      <c r="I21" s="144"/>
+      <c r="J21" s="144"/>
+      <c r="K21" s="144"/>
+      <c r="L21" s="144"/>
+      <c r="M21" s="144"/>
+      <c r="N21" s="144"/>
+      <c r="O21" s="144"/>
+      <c r="P21" s="144"/>
+      <c r="Q21" s="144"/>
+      <c r="R21" s="145"/>
     </row>
     <row r="22" spans="1:18" ht="5.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="240" t="s">
@@ -6747,46 +6735,46 @@
       <c r="R32" s="255"/>
     </row>
     <row r="33" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="91" t="s">
+      <c r="A33" s="89" t="s">
         <v>8</v>
       </c>
-      <c r="B33" s="92"/>
-      <c r="C33" s="92"/>
-      <c r="D33" s="105"/>
-      <c r="E33" s="106"/>
-      <c r="F33" s="106"/>
-      <c r="G33" s="106"/>
-      <c r="H33" s="106"/>
-      <c r="I33" s="106"/>
-      <c r="J33" s="106"/>
-      <c r="K33" s="106"/>
-      <c r="L33" s="106"/>
-      <c r="M33" s="106"/>
-      <c r="N33" s="106"/>
-      <c r="O33" s="106"/>
-      <c r="P33" s="106"/>
-      <c r="Q33" s="106"/>
-      <c r="R33" s="107"/>
+      <c r="B33" s="90"/>
+      <c r="C33" s="90"/>
+      <c r="D33" s="91"/>
+      <c r="E33" s="92"/>
+      <c r="F33" s="92"/>
+      <c r="G33" s="92"/>
+      <c r="H33" s="92"/>
+      <c r="I33" s="92"/>
+      <c r="J33" s="92"/>
+      <c r="K33" s="92"/>
+      <c r="L33" s="92"/>
+      <c r="M33" s="92"/>
+      <c r="N33" s="92"/>
+      <c r="O33" s="92"/>
+      <c r="P33" s="92"/>
+      <c r="Q33" s="92"/>
+      <c r="R33" s="93"/>
     </row>
     <row r="34" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="91"/>
-      <c r="B34" s="92"/>
-      <c r="C34" s="92"/>
-      <c r="D34" s="108"/>
-      <c r="E34" s="109"/>
-      <c r="F34" s="109"/>
-      <c r="G34" s="109"/>
-      <c r="H34" s="109"/>
-      <c r="I34" s="109"/>
-      <c r="J34" s="109"/>
-      <c r="K34" s="109"/>
-      <c r="L34" s="109"/>
-      <c r="M34" s="109"/>
-      <c r="N34" s="109"/>
-      <c r="O34" s="109"/>
-      <c r="P34" s="109"/>
-      <c r="Q34" s="109"/>
-      <c r="R34" s="110"/>
+      <c r="A34" s="89"/>
+      <c r="B34" s="90"/>
+      <c r="C34" s="90"/>
+      <c r="D34" s="94"/>
+      <c r="E34" s="95"/>
+      <c r="F34" s="95"/>
+      <c r="G34" s="95"/>
+      <c r="H34" s="95"/>
+      <c r="I34" s="95"/>
+      <c r="J34" s="95"/>
+      <c r="K34" s="95"/>
+      <c r="L34" s="95"/>
+      <c r="M34" s="95"/>
+      <c r="N34" s="95"/>
+      <c r="O34" s="95"/>
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="96"/>
     </row>
     <row r="35" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="240" t="s">
@@ -6831,44 +6819,44 @@
       <c r="R36" s="104"/>
     </row>
     <row r="37" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="111"/>
-      <c r="B37" s="112"/>
-      <c r="C37" s="112"/>
-      <c r="D37" s="112"/>
-      <c r="E37" s="112"/>
-      <c r="F37" s="112"/>
-      <c r="G37" s="112"/>
-      <c r="H37" s="112"/>
-      <c r="I37" s="112"/>
-      <c r="J37" s="112"/>
-      <c r="K37" s="112"/>
-      <c r="L37" s="112"/>
-      <c r="M37" s="112"/>
-      <c r="N37" s="112"/>
-      <c r="O37" s="112"/>
-      <c r="P37" s="112"/>
-      <c r="Q37" s="112"/>
-      <c r="R37" s="112"/>
+      <c r="A37" s="105"/>
+      <c r="B37" s="106"/>
+      <c r="C37" s="106"/>
+      <c r="D37" s="106"/>
+      <c r="E37" s="106"/>
+      <c r="F37" s="106"/>
+      <c r="G37" s="106"/>
+      <c r="H37" s="106"/>
+      <c r="I37" s="106"/>
+      <c r="J37" s="106"/>
+      <c r="K37" s="106"/>
+      <c r="L37" s="106"/>
+      <c r="M37" s="106"/>
+      <c r="N37" s="106"/>
+      <c r="O37" s="106"/>
+      <c r="P37" s="106"/>
+      <c r="Q37" s="106"/>
+      <c r="R37" s="106"/>
     </row>
     <row r="38" spans="1:18" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="113"/>
-      <c r="B38" s="113"/>
-      <c r="C38" s="113"/>
-      <c r="D38" s="113"/>
-      <c r="E38" s="113"/>
-      <c r="F38" s="113"/>
-      <c r="G38" s="113"/>
-      <c r="H38" s="113"/>
-      <c r="I38" s="113"/>
-      <c r="J38" s="113"/>
-      <c r="K38" s="113"/>
-      <c r="L38" s="113"/>
-      <c r="M38" s="113"/>
-      <c r="N38" s="113"/>
-      <c r="O38" s="113"/>
-      <c r="P38" s="113"/>
-      <c r="Q38" s="113"/>
-      <c r="R38" s="113"/>
+      <c r="A38" s="107"/>
+      <c r="B38" s="107"/>
+      <c r="C38" s="107"/>
+      <c r="D38" s="107"/>
+      <c r="E38" s="107"/>
+      <c r="F38" s="107"/>
+      <c r="G38" s="107"/>
+      <c r="H38" s="107"/>
+      <c r="I38" s="107"/>
+      <c r="J38" s="107"/>
+      <c r="K38" s="107"/>
+      <c r="L38" s="107"/>
+      <c r="M38" s="107"/>
+      <c r="N38" s="107"/>
+      <c r="O38" s="107"/>
+      <c r="P38" s="107"/>
+      <c r="Q38" s="107"/>
+      <c r="R38" s="107"/>
     </row>
     <row r="39" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="A39" s="228" t="s">
@@ -7233,9 +7221,7 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.47244094488188981" right="0.47244094488188981" top="0.44" bottom="0.55118110236220474" header="0.25" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="95" orientation="portrait" r:id="rId1"/>
-  <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;R&amp;"ＭＳ Ｐ明朝,標準"&amp;7Ver.3-12.03-01</oddFooter>
-  </headerFooter>
+  <headerFooter alignWithMargins="0"/>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="18" max="1048575" man="1"/>
   </colBreaks>
@@ -7268,16 +7254,16 @@
     </row>
     <row r="3" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A3" s="3"/>
-      <c r="O3" s="145"/>
-      <c r="P3" s="145"/>
-      <c r="Q3" s="145"/>
-      <c r="R3" s="145"/>
+      <c r="O3" s="136"/>
+      <c r="P3" s="136"/>
+      <c r="Q3" s="136"/>
+      <c r="R3" s="136"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="O4" s="145"/>
-      <c r="P4" s="145"/>
-      <c r="Q4" s="145"/>
-      <c r="R4" s="145"/>
+      <c r="O4" s="136"/>
+      <c r="P4" s="136"/>
+      <c r="Q4" s="136"/>
+      <c r="R4" s="136"/>
     </row>
     <row r="5" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="N5" s="4"/>
@@ -7340,121 +7326,121 @@
       <c r="R10" s="8"/>
     </row>
     <row r="11" spans="1:18" ht="21" x14ac:dyDescent="0.4">
-      <c r="A11" s="136" t="s">
+      <c r="A11" s="137" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="136"/>
-      <c r="C11" s="136"/>
-      <c r="D11" s="136"/>
-      <c r="E11" s="136"/>
-      <c r="F11" s="136"/>
-      <c r="G11" s="136"/>
-      <c r="H11" s="136"/>
-      <c r="I11" s="136"/>
-      <c r="J11" s="136"/>
-      <c r="K11" s="136"/>
-      <c r="L11" s="136"/>
-      <c r="M11" s="136"/>
-      <c r="N11" s="136"/>
-      <c r="O11" s="136"/>
-      <c r="P11" s="136"/>
-      <c r="Q11" s="136"/>
-      <c r="R11" s="136"/>
+      <c r="B11" s="137"/>
+      <c r="C11" s="137"/>
+      <c r="D11" s="137"/>
+      <c r="E11" s="137"/>
+      <c r="F11" s="137"/>
+      <c r="G11" s="137"/>
+      <c r="H11" s="137"/>
+      <c r="I11" s="137"/>
+      <c r="J11" s="137"/>
+      <c r="K11" s="137"/>
+      <c r="L11" s="137"/>
+      <c r="M11" s="137"/>
+      <c r="N11" s="137"/>
+      <c r="O11" s="137"/>
+      <c r="P11" s="137"/>
+      <c r="Q11" s="137"/>
+      <c r="R11" s="137"/>
     </row>
     <row r="14" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="15" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A15" s="137" t="s">
+      <c r="A15" s="138" t="s">
         <v>1</v>
       </c>
-      <c r="B15" s="137"/>
-      <c r="C15" s="137"/>
-      <c r="D15" s="137"/>
-      <c r="E15" s="137"/>
-      <c r="F15" s="137"/>
-      <c r="G15" s="137"/>
-      <c r="H15" s="137"/>
-      <c r="I15" s="137"/>
-      <c r="J15" s="137"/>
-      <c r="K15" s="137"/>
-      <c r="L15" s="137"/>
-      <c r="M15" s="137"/>
-      <c r="N15" s="137"/>
-      <c r="O15" s="137"/>
-      <c r="P15" s="137"/>
-      <c r="Q15" s="137"/>
-      <c r="R15" s="137"/>
+      <c r="B15" s="138"/>
+      <c r="C15" s="138"/>
+      <c r="D15" s="138"/>
+      <c r="E15" s="138"/>
+      <c r="F15" s="138"/>
+      <c r="G15" s="138"/>
+      <c r="H15" s="138"/>
+      <c r="I15" s="138"/>
+      <c r="J15" s="138"/>
+      <c r="K15" s="138"/>
+      <c r="L15" s="138"/>
+      <c r="M15" s="138"/>
+      <c r="N15" s="138"/>
+      <c r="O15" s="138"/>
+      <c r="P15" s="138"/>
+      <c r="Q15" s="138"/>
+      <c r="R15" s="138"/>
     </row>
     <row r="18" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A18" s="138" t="s">
+      <c r="A18" s="139" t="s">
         <v>2</v>
       </c>
-      <c r="B18" s="138"/>
-      <c r="C18" s="138"/>
-      <c r="D18" s="138"/>
-      <c r="E18" s="138"/>
-      <c r="F18" s="138"/>
-      <c r="G18" s="138"/>
-      <c r="H18" s="138"/>
-      <c r="I18" s="138"/>
-      <c r="J18" s="138"/>
-      <c r="K18" s="138"/>
-      <c r="L18" s="138"/>
-      <c r="M18" s="138"/>
-      <c r="N18" s="138"/>
-      <c r="O18" s="138"/>
-      <c r="P18" s="138"/>
-      <c r="Q18" s="138"/>
-      <c r="R18" s="138"/>
+      <c r="B18" s="139"/>
+      <c r="C18" s="139"/>
+      <c r="D18" s="139"/>
+      <c r="E18" s="139"/>
+      <c r="F18" s="139"/>
+      <c r="G18" s="139"/>
+      <c r="H18" s="139"/>
+      <c r="I18" s="139"/>
+      <c r="J18" s="139"/>
+      <c r="K18" s="139"/>
+      <c r="L18" s="139"/>
+      <c r="M18" s="139"/>
+      <c r="N18" s="139"/>
+      <c r="O18" s="139"/>
+      <c r="P18" s="139"/>
+      <c r="Q18" s="139"/>
+      <c r="R18" s="139"/>
     </row>
     <row r="19" spans="1:18" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="20" spans="1:18" ht="12.75" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="89" t="s">
+      <c r="A20" s="108" t="s">
         <v>3</v>
       </c>
-      <c r="B20" s="90"/>
-      <c r="C20" s="90"/>
-      <c r="D20" s="139"/>
-      <c r="E20" s="140"/>
-      <c r="F20" s="140"/>
-      <c r="G20" s="140"/>
-      <c r="H20" s="140"/>
-      <c r="I20" s="140"/>
-      <c r="J20" s="140"/>
-      <c r="K20" s="140"/>
-      <c r="L20" s="140"/>
-      <c r="M20" s="140"/>
-      <c r="N20" s="140"/>
-      <c r="O20" s="140"/>
-      <c r="P20" s="140"/>
-      <c r="Q20" s="140"/>
-      <c r="R20" s="141"/>
+      <c r="B20" s="109"/>
+      <c r="C20" s="109"/>
+      <c r="D20" s="140"/>
+      <c r="E20" s="141"/>
+      <c r="F20" s="141"/>
+      <c r="G20" s="141"/>
+      <c r="H20" s="141"/>
+      <c r="I20" s="141"/>
+      <c r="J20" s="141"/>
+      <c r="K20" s="141"/>
+      <c r="L20" s="141"/>
+      <c r="M20" s="141"/>
+      <c r="N20" s="141"/>
+      <c r="O20" s="141"/>
+      <c r="P20" s="141"/>
+      <c r="Q20" s="141"/>
+      <c r="R20" s="142"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A21" s="91"/>
-      <c r="B21" s="92"/>
-      <c r="C21" s="92"/>
-      <c r="D21" s="142"/>
-      <c r="E21" s="143"/>
-      <c r="F21" s="143"/>
-      <c r="G21" s="143"/>
-      <c r="H21" s="143"/>
-      <c r="I21" s="143"/>
-      <c r="J21" s="143"/>
-      <c r="K21" s="143"/>
-      <c r="L21" s="143"/>
-      <c r="M21" s="143"/>
-      <c r="N21" s="143"/>
-      <c r="O21" s="143"/>
-      <c r="P21" s="143"/>
-      <c r="Q21" s="143"/>
-      <c r="R21" s="144"/>
+      <c r="A21" s="89"/>
+      <c r="B21" s="90"/>
+      <c r="C21" s="90"/>
+      <c r="D21" s="143"/>
+      <c r="E21" s="144"/>
+      <c r="F21" s="144"/>
+      <c r="G21" s="144"/>
+      <c r="H21" s="144"/>
+      <c r="I21" s="144"/>
+      <c r="J21" s="144"/>
+      <c r="K21" s="144"/>
+      <c r="L21" s="144"/>
+      <c r="M21" s="144"/>
+      <c r="N21" s="144"/>
+      <c r="O21" s="144"/>
+      <c r="P21" s="144"/>
+      <c r="Q21" s="144"/>
+      <c r="R21" s="145"/>
     </row>
     <row r="22" spans="1:18" ht="5.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="91" t="s">
+      <c r="A22" s="89" t="s">
         <v>4</v>
       </c>
-      <c r="B22" s="92"/>
-      <c r="C22" s="92"/>
+      <c r="B22" s="90"/>
+      <c r="C22" s="90"/>
       <c r="D22" s="9"/>
       <c r="L22" s="10"/>
       <c r="M22" s="114" t="s">
@@ -7467,9 +7453,9 @@
       <c r="R22" s="120"/>
     </row>
     <row r="23" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="91"/>
-      <c r="B23" s="92"/>
-      <c r="C23" s="92"/>
+      <c r="A23" s="89"/>
+      <c r="B23" s="90"/>
+      <c r="C23" s="90"/>
       <c r="D23" s="127"/>
       <c r="E23" s="128"/>
       <c r="F23" s="128"/>
@@ -7487,9 +7473,9 @@
       <c r="R23" s="123"/>
     </row>
     <row r="24" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="91"/>
-      <c r="B24" s="92"/>
-      <c r="C24" s="92"/>
+      <c r="A24" s="89"/>
+      <c r="B24" s="90"/>
+      <c r="C24" s="90"/>
       <c r="D24" s="130"/>
       <c r="E24" s="128"/>
       <c r="F24" s="128"/>
@@ -7507,9 +7493,9 @@
       <c r="R24" s="123"/>
     </row>
     <row r="25" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="91"/>
-      <c r="B25" s="92"/>
-      <c r="C25" s="92"/>
+      <c r="A25" s="89"/>
+      <c r="B25" s="90"/>
+      <c r="C25" s="90"/>
       <c r="D25" s="130"/>
       <c r="E25" s="128"/>
       <c r="F25" s="128"/>
@@ -7527,9 +7513,9 @@
       <c r="R25" s="123"/>
     </row>
     <row r="26" spans="1:18" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="91"/>
-      <c r="B26" s="92"/>
-      <c r="C26" s="92"/>
+      <c r="A26" s="89"/>
+      <c r="B26" s="90"/>
+      <c r="C26" s="90"/>
       <c r="D26" s="11"/>
       <c r="E26" s="12"/>
       <c r="F26" s="13"/>
@@ -7547,9 +7533,9 @@
       <c r="R26" s="123"/>
     </row>
     <row r="27" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="91"/>
-      <c r="B27" s="92"/>
-      <c r="C27" s="92"/>
+      <c r="A27" s="89"/>
+      <c r="B27" s="90"/>
+      <c r="C27" s="90"/>
       <c r="D27" s="16"/>
       <c r="F27" s="17"/>
       <c r="G27" s="18"/>
@@ -7587,22 +7573,22 @@
     <row r="29" spans="1:18" ht="12.75" thickTop="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="1:18" ht="12.75" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="31" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="89" t="s">
+      <c r="A31" s="108" t="s">
         <v>6</v>
       </c>
-      <c r="B31" s="90"/>
-      <c r="C31" s="90"/>
+      <c r="B31" s="109"/>
+      <c r="C31" s="109"/>
       <c r="D31" s="131"/>
       <c r="E31" s="131"/>
       <c r="F31" s="131"/>
       <c r="G31" s="131"/>
       <c r="H31" s="131"/>
       <c r="I31" s="131"/>
-      <c r="J31" s="90" t="s">
+      <c r="J31" s="109" t="s">
         <v>7</v>
       </c>
-      <c r="K31" s="90"/>
-      <c r="L31" s="90"/>
+      <c r="K31" s="109"/>
+      <c r="L31" s="109"/>
       <c r="M31" s="131"/>
       <c r="N31" s="131"/>
       <c r="O31" s="131"/>
@@ -7611,18 +7597,18 @@
       <c r="R31" s="133"/>
     </row>
     <row r="32" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="91"/>
-      <c r="B32" s="92"/>
-      <c r="C32" s="92"/>
+      <c r="A32" s="89"/>
+      <c r="B32" s="90"/>
+      <c r="C32" s="90"/>
       <c r="D32" s="132"/>
       <c r="E32" s="132"/>
       <c r="F32" s="132"/>
       <c r="G32" s="132"/>
       <c r="H32" s="132"/>
       <c r="I32" s="132"/>
-      <c r="J32" s="92"/>
-      <c r="K32" s="92"/>
-      <c r="L32" s="92"/>
+      <c r="J32" s="90"/>
+      <c r="K32" s="90"/>
+      <c r="L32" s="90"/>
       <c r="M32" s="132"/>
       <c r="N32" s="132"/>
       <c r="O32" s="132"/>
@@ -7631,53 +7617,53 @@
       <c r="R32" s="134"/>
     </row>
     <row r="33" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="91" t="s">
+      <c r="A33" s="89" t="s">
         <v>8</v>
       </c>
-      <c r="B33" s="92"/>
-      <c r="C33" s="92"/>
-      <c r="D33" s="105"/>
-      <c r="E33" s="106"/>
-      <c r="F33" s="106"/>
-      <c r="G33" s="106"/>
-      <c r="H33" s="106"/>
-      <c r="I33" s="106"/>
-      <c r="J33" s="106"/>
-      <c r="K33" s="106"/>
-      <c r="L33" s="106"/>
-      <c r="M33" s="106"/>
-      <c r="N33" s="106"/>
-      <c r="O33" s="106"/>
-      <c r="P33" s="106"/>
-      <c r="Q33" s="106"/>
-      <c r="R33" s="107"/>
+      <c r="B33" s="90"/>
+      <c r="C33" s="90"/>
+      <c r="D33" s="91"/>
+      <c r="E33" s="92"/>
+      <c r="F33" s="92"/>
+      <c r="G33" s="92"/>
+      <c r="H33" s="92"/>
+      <c r="I33" s="92"/>
+      <c r="J33" s="92"/>
+      <c r="K33" s="92"/>
+      <c r="L33" s="92"/>
+      <c r="M33" s="92"/>
+      <c r="N33" s="92"/>
+      <c r="O33" s="92"/>
+      <c r="P33" s="92"/>
+      <c r="Q33" s="92"/>
+      <c r="R33" s="93"/>
     </row>
     <row r="34" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="91"/>
-      <c r="B34" s="92"/>
-      <c r="C34" s="92"/>
-      <c r="D34" s="108"/>
-      <c r="E34" s="109"/>
-      <c r="F34" s="109"/>
-      <c r="G34" s="109"/>
-      <c r="H34" s="109"/>
-      <c r="I34" s="109"/>
-      <c r="J34" s="109"/>
-      <c r="K34" s="109"/>
-      <c r="L34" s="109"/>
-      <c r="M34" s="109"/>
-      <c r="N34" s="109"/>
-      <c r="O34" s="109"/>
-      <c r="P34" s="109"/>
-      <c r="Q34" s="109"/>
-      <c r="R34" s="110"/>
+      <c r="A34" s="89"/>
+      <c r="B34" s="90"/>
+      <c r="C34" s="90"/>
+      <c r="D34" s="94"/>
+      <c r="E34" s="95"/>
+      <c r="F34" s="95"/>
+      <c r="G34" s="95"/>
+      <c r="H34" s="95"/>
+      <c r="I34" s="95"/>
+      <c r="J34" s="95"/>
+      <c r="K34" s="95"/>
+      <c r="L34" s="95"/>
+      <c r="M34" s="95"/>
+      <c r="N34" s="95"/>
+      <c r="O34" s="95"/>
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="96"/>
     </row>
     <row r="35" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="91" t="s">
+      <c r="A35" s="89" t="s">
         <v>9</v>
       </c>
-      <c r="B35" s="92"/>
-      <c r="C35" s="92"/>
+      <c r="B35" s="90"/>
+      <c r="C35" s="90"/>
       <c r="D35" s="99"/>
       <c r="E35" s="100"/>
       <c r="F35" s="100"/>
@@ -7715,94 +7701,94 @@
       <c r="R36" s="104"/>
     </row>
     <row r="37" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="111"/>
-      <c r="B37" s="112"/>
-      <c r="C37" s="112"/>
-      <c r="D37" s="112"/>
-      <c r="E37" s="112"/>
-      <c r="F37" s="112"/>
-      <c r="G37" s="112"/>
-      <c r="H37" s="112"/>
-      <c r="I37" s="112"/>
-      <c r="J37" s="112"/>
-      <c r="K37" s="112"/>
-      <c r="L37" s="112"/>
-      <c r="M37" s="112"/>
-      <c r="N37" s="112"/>
-      <c r="O37" s="112"/>
-      <c r="P37" s="112"/>
-      <c r="Q37" s="112"/>
-      <c r="R37" s="112"/>
+      <c r="A37" s="105"/>
+      <c r="B37" s="106"/>
+      <c r="C37" s="106"/>
+      <c r="D37" s="106"/>
+      <c r="E37" s="106"/>
+      <c r="F37" s="106"/>
+      <c r="G37" s="106"/>
+      <c r="H37" s="106"/>
+      <c r="I37" s="106"/>
+      <c r="J37" s="106"/>
+      <c r="K37" s="106"/>
+      <c r="L37" s="106"/>
+      <c r="M37" s="106"/>
+      <c r="N37" s="106"/>
+      <c r="O37" s="106"/>
+      <c r="P37" s="106"/>
+      <c r="Q37" s="106"/>
+      <c r="R37" s="106"/>
     </row>
     <row r="38" spans="1:18" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="113"/>
-      <c r="B38" s="113"/>
-      <c r="C38" s="113"/>
-      <c r="D38" s="113"/>
-      <c r="E38" s="113"/>
-      <c r="F38" s="113"/>
-      <c r="G38" s="113"/>
-      <c r="H38" s="113"/>
-      <c r="I38" s="113"/>
-      <c r="J38" s="113"/>
-      <c r="K38" s="113"/>
-      <c r="L38" s="113"/>
-      <c r="M38" s="113"/>
-      <c r="N38" s="113"/>
-      <c r="O38" s="113"/>
-      <c r="P38" s="113"/>
-      <c r="Q38" s="113"/>
-      <c r="R38" s="113"/>
+      <c r="A38" s="107"/>
+      <c r="B38" s="107"/>
+      <c r="C38" s="107"/>
+      <c r="D38" s="107"/>
+      <c r="E38" s="107"/>
+      <c r="F38" s="107"/>
+      <c r="G38" s="107"/>
+      <c r="H38" s="107"/>
+      <c r="I38" s="107"/>
+      <c r="J38" s="107"/>
+      <c r="K38" s="107"/>
+      <c r="L38" s="107"/>
+      <c r="M38" s="107"/>
+      <c r="N38" s="107"/>
+      <c r="O38" s="107"/>
+      <c r="P38" s="107"/>
+      <c r="Q38" s="107"/>
+      <c r="R38" s="107"/>
     </row>
     <row r="39" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="89" t="s">
+      <c r="A39" s="108" t="s">
         <v>10</v>
       </c>
-      <c r="B39" s="90"/>
-      <c r="C39" s="90"/>
-      <c r="D39" s="90" t="s">
+      <c r="B39" s="109"/>
+      <c r="C39" s="109"/>
+      <c r="D39" s="109" t="s">
         <v>11</v>
       </c>
-      <c r="E39" s="90"/>
-      <c r="F39" s="90"/>
-      <c r="G39" s="93"/>
-      <c r="H39" s="90" t="s">
+      <c r="E39" s="109"/>
+      <c r="F39" s="109"/>
+      <c r="G39" s="110"/>
+      <c r="H39" s="109" t="s">
         <v>10</v>
       </c>
-      <c r="I39" s="90"/>
-      <c r="J39" s="90"/>
-      <c r="K39" s="90" t="s">
+      <c r="I39" s="109"/>
+      <c r="J39" s="109"/>
+      <c r="K39" s="109" t="s">
         <v>11</v>
       </c>
-      <c r="L39" s="90"/>
-      <c r="M39" s="90"/>
-      <c r="N39" s="93"/>
-      <c r="O39" s="90" t="s">
+      <c r="L39" s="109"/>
+      <c r="M39" s="109"/>
+      <c r="N39" s="110"/>
+      <c r="O39" s="109" t="s">
         <v>35</v>
       </c>
-      <c r="P39" s="90"/>
-      <c r="Q39" s="90"/>
-      <c r="R39" s="95"/>
+      <c r="P39" s="109"/>
+      <c r="Q39" s="109"/>
+      <c r="R39" s="112"/>
     </row>
     <row r="40" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="91"/>
-      <c r="B40" s="92"/>
-      <c r="C40" s="92"/>
-      <c r="D40" s="92"/>
-      <c r="E40" s="92"/>
-      <c r="F40" s="92"/>
-      <c r="G40" s="94"/>
-      <c r="H40" s="92"/>
-      <c r="I40" s="92"/>
-      <c r="J40" s="92"/>
-      <c r="K40" s="92"/>
-      <c r="L40" s="92"/>
-      <c r="M40" s="92"/>
-      <c r="N40" s="94"/>
-      <c r="O40" s="92"/>
-      <c r="P40" s="92"/>
-      <c r="Q40" s="92"/>
-      <c r="R40" s="96"/>
+      <c r="A40" s="89"/>
+      <c r="B40" s="90"/>
+      <c r="C40" s="90"/>
+      <c r="D40" s="90"/>
+      <c r="E40" s="90"/>
+      <c r="F40" s="90"/>
+      <c r="G40" s="111"/>
+      <c r="H40" s="90"/>
+      <c r="I40" s="90"/>
+      <c r="J40" s="90"/>
+      <c r="K40" s="90"/>
+      <c r="L40" s="90"/>
+      <c r="M40" s="90"/>
+      <c r="N40" s="111"/>
+      <c r="O40" s="90"/>
+      <c r="P40" s="90"/>
+      <c r="Q40" s="90"/>
+      <c r="R40" s="113"/>
     </row>
     <row r="41" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="64" t="s">
@@ -7896,21 +7882,21 @@
       <c r="A45" s="88" t="s">
         <v>17</v>
       </c>
-      <c r="B45" s="54"/>
-      <c r="C45" s="54"/>
-      <c r="D45" s="52"/>
-      <c r="E45" s="52"/>
-      <c r="F45" s="52"/>
-      <c r="G45" s="53"/>
-      <c r="H45" s="54" t="s">
+      <c r="B45" s="60"/>
+      <c r="C45" s="60"/>
+      <c r="D45" s="58"/>
+      <c r="E45" s="58"/>
+      <c r="F45" s="58"/>
+      <c r="G45" s="59"/>
+      <c r="H45" s="60" t="s">
         <v>17</v>
       </c>
-      <c r="I45" s="54"/>
-      <c r="J45" s="54"/>
-      <c r="K45" s="52"/>
-      <c r="L45" s="52"/>
-      <c r="M45" s="52"/>
-      <c r="N45" s="53"/>
+      <c r="I45" s="60"/>
+      <c r="J45" s="60"/>
+      <c r="K45" s="58"/>
+      <c r="L45" s="58"/>
+      <c r="M45" s="58"/>
+      <c r="N45" s="59"/>
       <c r="O45" s="84"/>
       <c r="P45" s="84"/>
       <c r="Q45" s="84"/>
@@ -8117,9 +8103,7 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.47244094488188981" right="0.47244094488188981" top="0.44" bottom="0.55118110236220474" header="0.25" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="95" orientation="portrait" r:id="rId1"/>
-  <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;R&amp;"ＭＳ Ｐ明朝,標準"&amp;7Ver.3-12.03-01</oddFooter>
-  </headerFooter>
+  <headerFooter alignWithMargins="0"/>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="18" max="1048575" man="1"/>
   </colBreaks>
@@ -8152,16 +8136,16 @@
     </row>
     <row r="3" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A3" s="3"/>
-      <c r="O3" s="145"/>
-      <c r="P3" s="145"/>
-      <c r="Q3" s="145"/>
-      <c r="R3" s="145"/>
+      <c r="O3" s="136"/>
+      <c r="P3" s="136"/>
+      <c r="Q3" s="136"/>
+      <c r="R3" s="136"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="O4" s="145"/>
-      <c r="P4" s="145"/>
-      <c r="Q4" s="145"/>
-      <c r="R4" s="145"/>
+      <c r="O4" s="136"/>
+      <c r="P4" s="136"/>
+      <c r="Q4" s="136"/>
+      <c r="R4" s="136"/>
     </row>
     <row r="5" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="N5" s="4"/>
@@ -8224,121 +8208,121 @@
       <c r="R10" s="8"/>
     </row>
     <row r="11" spans="1:18" ht="21" x14ac:dyDescent="0.4">
-      <c r="A11" s="136" t="s">
+      <c r="A11" s="137" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="136"/>
-      <c r="C11" s="136"/>
-      <c r="D11" s="136"/>
-      <c r="E11" s="136"/>
-      <c r="F11" s="136"/>
-      <c r="G11" s="136"/>
-      <c r="H11" s="136"/>
-      <c r="I11" s="136"/>
-      <c r="J11" s="136"/>
-      <c r="K11" s="136"/>
-      <c r="L11" s="136"/>
-      <c r="M11" s="136"/>
-      <c r="N11" s="136"/>
-      <c r="O11" s="136"/>
-      <c r="P11" s="136"/>
-      <c r="Q11" s="136"/>
-      <c r="R11" s="136"/>
+      <c r="B11" s="137"/>
+      <c r="C11" s="137"/>
+      <c r="D11" s="137"/>
+      <c r="E11" s="137"/>
+      <c r="F11" s="137"/>
+      <c r="G11" s="137"/>
+      <c r="H11" s="137"/>
+      <c r="I11" s="137"/>
+      <c r="J11" s="137"/>
+      <c r="K11" s="137"/>
+      <c r="L11" s="137"/>
+      <c r="M11" s="137"/>
+      <c r="N11" s="137"/>
+      <c r="O11" s="137"/>
+      <c r="P11" s="137"/>
+      <c r="Q11" s="137"/>
+      <c r="R11" s="137"/>
     </row>
     <row r="14" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="15" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A15" s="137" t="s">
+      <c r="A15" s="138" t="s">
         <v>1</v>
       </c>
-      <c r="B15" s="137"/>
-      <c r="C15" s="137"/>
-      <c r="D15" s="137"/>
-      <c r="E15" s="137"/>
-      <c r="F15" s="137"/>
-      <c r="G15" s="137"/>
-      <c r="H15" s="137"/>
-      <c r="I15" s="137"/>
-      <c r="J15" s="137"/>
-      <c r="K15" s="137"/>
-      <c r="L15" s="137"/>
-      <c r="M15" s="137"/>
-      <c r="N15" s="137"/>
-      <c r="O15" s="137"/>
-      <c r="P15" s="137"/>
-      <c r="Q15" s="137"/>
-      <c r="R15" s="137"/>
+      <c r="B15" s="138"/>
+      <c r="C15" s="138"/>
+      <c r="D15" s="138"/>
+      <c r="E15" s="138"/>
+      <c r="F15" s="138"/>
+      <c r="G15" s="138"/>
+      <c r="H15" s="138"/>
+      <c r="I15" s="138"/>
+      <c r="J15" s="138"/>
+      <c r="K15" s="138"/>
+      <c r="L15" s="138"/>
+      <c r="M15" s="138"/>
+      <c r="N15" s="138"/>
+      <c r="O15" s="138"/>
+      <c r="P15" s="138"/>
+      <c r="Q15" s="138"/>
+      <c r="R15" s="138"/>
     </row>
     <row r="18" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A18" s="138" t="s">
+      <c r="A18" s="139" t="s">
         <v>2</v>
       </c>
-      <c r="B18" s="138"/>
-      <c r="C18" s="138"/>
-      <c r="D18" s="138"/>
-      <c r="E18" s="138"/>
-      <c r="F18" s="138"/>
-      <c r="G18" s="138"/>
-      <c r="H18" s="138"/>
-      <c r="I18" s="138"/>
-      <c r="J18" s="138"/>
-      <c r="K18" s="138"/>
-      <c r="L18" s="138"/>
-      <c r="M18" s="138"/>
-      <c r="N18" s="138"/>
-      <c r="O18" s="138"/>
-      <c r="P18" s="138"/>
-      <c r="Q18" s="138"/>
-      <c r="R18" s="138"/>
+      <c r="B18" s="139"/>
+      <c r="C18" s="139"/>
+      <c r="D18" s="139"/>
+      <c r="E18" s="139"/>
+      <c r="F18" s="139"/>
+      <c r="G18" s="139"/>
+      <c r="H18" s="139"/>
+      <c r="I18" s="139"/>
+      <c r="J18" s="139"/>
+      <c r="K18" s="139"/>
+      <c r="L18" s="139"/>
+      <c r="M18" s="139"/>
+      <c r="N18" s="139"/>
+      <c r="O18" s="139"/>
+      <c r="P18" s="139"/>
+      <c r="Q18" s="139"/>
+      <c r="R18" s="139"/>
     </row>
     <row r="19" spans="1:18" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="20" spans="1:18" ht="12.75" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="89" t="s">
+      <c r="A20" s="108" t="s">
         <v>3</v>
       </c>
-      <c r="B20" s="90"/>
-      <c r="C20" s="90"/>
-      <c r="D20" s="139"/>
-      <c r="E20" s="140"/>
-      <c r="F20" s="140"/>
-      <c r="G20" s="140"/>
-      <c r="H20" s="140"/>
-      <c r="I20" s="140"/>
-      <c r="J20" s="140"/>
-      <c r="K20" s="140"/>
-      <c r="L20" s="140"/>
-      <c r="M20" s="140"/>
-      <c r="N20" s="140"/>
-      <c r="O20" s="140"/>
-      <c r="P20" s="140"/>
-      <c r="Q20" s="140"/>
-      <c r="R20" s="141"/>
+      <c r="B20" s="109"/>
+      <c r="C20" s="109"/>
+      <c r="D20" s="140"/>
+      <c r="E20" s="141"/>
+      <c r="F20" s="141"/>
+      <c r="G20" s="141"/>
+      <c r="H20" s="141"/>
+      <c r="I20" s="141"/>
+      <c r="J20" s="141"/>
+      <c r="K20" s="141"/>
+      <c r="L20" s="141"/>
+      <c r="M20" s="141"/>
+      <c r="N20" s="141"/>
+      <c r="O20" s="141"/>
+      <c r="P20" s="141"/>
+      <c r="Q20" s="141"/>
+      <c r="R20" s="142"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A21" s="91"/>
-      <c r="B21" s="92"/>
-      <c r="C21" s="92"/>
-      <c r="D21" s="142"/>
-      <c r="E21" s="143"/>
-      <c r="F21" s="143"/>
-      <c r="G21" s="143"/>
-      <c r="H21" s="143"/>
-      <c r="I21" s="143"/>
-      <c r="J21" s="143"/>
-      <c r="K21" s="143"/>
-      <c r="L21" s="143"/>
-      <c r="M21" s="143"/>
-      <c r="N21" s="143"/>
-      <c r="O21" s="143"/>
-      <c r="P21" s="143"/>
-      <c r="Q21" s="143"/>
-      <c r="R21" s="144"/>
+      <c r="A21" s="89"/>
+      <c r="B21" s="90"/>
+      <c r="C21" s="90"/>
+      <c r="D21" s="143"/>
+      <c r="E21" s="144"/>
+      <c r="F21" s="144"/>
+      <c r="G21" s="144"/>
+      <c r="H21" s="144"/>
+      <c r="I21" s="144"/>
+      <c r="J21" s="144"/>
+      <c r="K21" s="144"/>
+      <c r="L21" s="144"/>
+      <c r="M21" s="144"/>
+      <c r="N21" s="144"/>
+      <c r="O21" s="144"/>
+      <c r="P21" s="144"/>
+      <c r="Q21" s="144"/>
+      <c r="R21" s="145"/>
     </row>
     <row r="22" spans="1:18" ht="5.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="91" t="s">
+      <c r="A22" s="89" t="s">
         <v>4</v>
       </c>
-      <c r="B22" s="92"/>
-      <c r="C22" s="92"/>
+      <c r="B22" s="90"/>
+      <c r="C22" s="90"/>
       <c r="D22" s="9"/>
       <c r="L22" s="10"/>
       <c r="M22" s="114" t="s">
@@ -8351,9 +8335,9 @@
       <c r="R22" s="120"/>
     </row>
     <row r="23" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="91"/>
-      <c r="B23" s="92"/>
-      <c r="C23" s="92"/>
+      <c r="A23" s="89"/>
+      <c r="B23" s="90"/>
+      <c r="C23" s="90"/>
       <c r="D23" s="127"/>
       <c r="E23" s="128"/>
       <c r="F23" s="128"/>
@@ -8371,9 +8355,9 @@
       <c r="R23" s="123"/>
     </row>
     <row r="24" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="91"/>
-      <c r="B24" s="92"/>
-      <c r="C24" s="92"/>
+      <c r="A24" s="89"/>
+      <c r="B24" s="90"/>
+      <c r="C24" s="90"/>
       <c r="D24" s="130"/>
       <c r="E24" s="128"/>
       <c r="F24" s="128"/>
@@ -8391,9 +8375,9 @@
       <c r="R24" s="123"/>
     </row>
     <row r="25" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="91"/>
-      <c r="B25" s="92"/>
-      <c r="C25" s="92"/>
+      <c r="A25" s="89"/>
+      <c r="B25" s="90"/>
+      <c r="C25" s="90"/>
       <c r="D25" s="130"/>
       <c r="E25" s="128"/>
       <c r="F25" s="128"/>
@@ -8411,9 +8395,9 @@
       <c r="R25" s="123"/>
     </row>
     <row r="26" spans="1:18" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="91"/>
-      <c r="B26" s="92"/>
-      <c r="C26" s="92"/>
+      <c r="A26" s="89"/>
+      <c r="B26" s="90"/>
+      <c r="C26" s="90"/>
       <c r="D26" s="11"/>
       <c r="E26" s="12"/>
       <c r="F26" s="13"/>
@@ -8431,9 +8415,9 @@
       <c r="R26" s="123"/>
     </row>
     <row r="27" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="91"/>
-      <c r="B27" s="92"/>
-      <c r="C27" s="92"/>
+      <c r="A27" s="89"/>
+      <c r="B27" s="90"/>
+      <c r="C27" s="90"/>
       <c r="D27" s="16"/>
       <c r="F27" s="17"/>
       <c r="G27" s="18"/>
@@ -8471,22 +8455,22 @@
     <row r="29" spans="1:18" ht="12.75" thickTop="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="1:18" ht="12.75" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="31" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="89" t="s">
+      <c r="A31" s="108" t="s">
         <v>6</v>
       </c>
-      <c r="B31" s="90"/>
-      <c r="C31" s="90"/>
+      <c r="B31" s="109"/>
+      <c r="C31" s="109"/>
       <c r="D31" s="131"/>
       <c r="E31" s="131"/>
       <c r="F31" s="131"/>
       <c r="G31" s="131"/>
       <c r="H31" s="131"/>
       <c r="I31" s="131"/>
-      <c r="J31" s="90" t="s">
+      <c r="J31" s="109" t="s">
         <v>7</v>
       </c>
-      <c r="K31" s="90"/>
-      <c r="L31" s="90"/>
+      <c r="K31" s="109"/>
+      <c r="L31" s="109"/>
       <c r="M31" s="131"/>
       <c r="N31" s="131"/>
       <c r="O31" s="131"/>
@@ -8495,18 +8479,18 @@
       <c r="R31" s="133"/>
     </row>
     <row r="32" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="91"/>
-      <c r="B32" s="92"/>
-      <c r="C32" s="92"/>
+      <c r="A32" s="89"/>
+      <c r="B32" s="90"/>
+      <c r="C32" s="90"/>
       <c r="D32" s="132"/>
       <c r="E32" s="132"/>
       <c r="F32" s="132"/>
       <c r="G32" s="132"/>
       <c r="H32" s="132"/>
       <c r="I32" s="132"/>
-      <c r="J32" s="92"/>
-      <c r="K32" s="92"/>
-      <c r="L32" s="92"/>
+      <c r="J32" s="90"/>
+      <c r="K32" s="90"/>
+      <c r="L32" s="90"/>
       <c r="M32" s="132"/>
       <c r="N32" s="132"/>
       <c r="O32" s="132"/>
@@ -8515,53 +8499,53 @@
       <c r="R32" s="134"/>
     </row>
     <row r="33" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="91" t="s">
+      <c r="A33" s="89" t="s">
         <v>8</v>
       </c>
-      <c r="B33" s="92"/>
-      <c r="C33" s="92"/>
-      <c r="D33" s="105"/>
-      <c r="E33" s="106"/>
-      <c r="F33" s="106"/>
-      <c r="G33" s="106"/>
-      <c r="H33" s="106"/>
-      <c r="I33" s="106"/>
-      <c r="J33" s="106"/>
-      <c r="K33" s="106"/>
-      <c r="L33" s="106"/>
-      <c r="M33" s="106"/>
-      <c r="N33" s="106"/>
-      <c r="O33" s="106"/>
-      <c r="P33" s="106"/>
-      <c r="Q33" s="106"/>
-      <c r="R33" s="107"/>
+      <c r="B33" s="90"/>
+      <c r="C33" s="90"/>
+      <c r="D33" s="91"/>
+      <c r="E33" s="92"/>
+      <c r="F33" s="92"/>
+      <c r="G33" s="92"/>
+      <c r="H33" s="92"/>
+      <c r="I33" s="92"/>
+      <c r="J33" s="92"/>
+      <c r="K33" s="92"/>
+      <c r="L33" s="92"/>
+      <c r="M33" s="92"/>
+      <c r="N33" s="92"/>
+      <c r="O33" s="92"/>
+      <c r="P33" s="92"/>
+      <c r="Q33" s="92"/>
+      <c r="R33" s="93"/>
     </row>
     <row r="34" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="91"/>
-      <c r="B34" s="92"/>
-      <c r="C34" s="92"/>
-      <c r="D34" s="108"/>
-      <c r="E34" s="109"/>
-      <c r="F34" s="109"/>
-      <c r="G34" s="109"/>
-      <c r="H34" s="109"/>
-      <c r="I34" s="109"/>
-      <c r="J34" s="109"/>
-      <c r="K34" s="109"/>
-      <c r="L34" s="109"/>
-      <c r="M34" s="109"/>
-      <c r="N34" s="109"/>
-      <c r="O34" s="109"/>
-      <c r="P34" s="109"/>
-      <c r="Q34" s="109"/>
-      <c r="R34" s="110"/>
+      <c r="A34" s="89"/>
+      <c r="B34" s="90"/>
+      <c r="C34" s="90"/>
+      <c r="D34" s="94"/>
+      <c r="E34" s="95"/>
+      <c r="F34" s="95"/>
+      <c r="G34" s="95"/>
+      <c r="H34" s="95"/>
+      <c r="I34" s="95"/>
+      <c r="J34" s="95"/>
+      <c r="K34" s="95"/>
+      <c r="L34" s="95"/>
+      <c r="M34" s="95"/>
+      <c r="N34" s="95"/>
+      <c r="O34" s="95"/>
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="96"/>
     </row>
     <row r="35" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="91" t="s">
+      <c r="A35" s="89" t="s">
         <v>9</v>
       </c>
-      <c r="B35" s="92"/>
-      <c r="C35" s="92"/>
+      <c r="B35" s="90"/>
+      <c r="C35" s="90"/>
       <c r="D35" s="99"/>
       <c r="E35" s="100"/>
       <c r="F35" s="100"/>
@@ -8599,94 +8583,94 @@
       <c r="R36" s="104"/>
     </row>
     <row r="37" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="111"/>
-      <c r="B37" s="112"/>
-      <c r="C37" s="112"/>
-      <c r="D37" s="112"/>
-      <c r="E37" s="112"/>
-      <c r="F37" s="112"/>
-      <c r="G37" s="112"/>
-      <c r="H37" s="112"/>
-      <c r="I37" s="112"/>
-      <c r="J37" s="112"/>
-      <c r="K37" s="112"/>
-      <c r="L37" s="112"/>
-      <c r="M37" s="112"/>
-      <c r="N37" s="112"/>
-      <c r="O37" s="112"/>
-      <c r="P37" s="112"/>
-      <c r="Q37" s="112"/>
-      <c r="R37" s="112"/>
+      <c r="A37" s="105"/>
+      <c r="B37" s="106"/>
+      <c r="C37" s="106"/>
+      <c r="D37" s="106"/>
+      <c r="E37" s="106"/>
+      <c r="F37" s="106"/>
+      <c r="G37" s="106"/>
+      <c r="H37" s="106"/>
+      <c r="I37" s="106"/>
+      <c r="J37" s="106"/>
+      <c r="K37" s="106"/>
+      <c r="L37" s="106"/>
+      <c r="M37" s="106"/>
+      <c r="N37" s="106"/>
+      <c r="O37" s="106"/>
+      <c r="P37" s="106"/>
+      <c r="Q37" s="106"/>
+      <c r="R37" s="106"/>
     </row>
     <row r="38" spans="1:18" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="113"/>
-      <c r="B38" s="113"/>
-      <c r="C38" s="113"/>
-      <c r="D38" s="113"/>
-      <c r="E38" s="113"/>
-      <c r="F38" s="113"/>
-      <c r="G38" s="113"/>
-      <c r="H38" s="113"/>
-      <c r="I38" s="113"/>
-      <c r="J38" s="113"/>
-      <c r="K38" s="113"/>
-      <c r="L38" s="113"/>
-      <c r="M38" s="113"/>
-      <c r="N38" s="113"/>
-      <c r="O38" s="113"/>
-      <c r="P38" s="113"/>
-      <c r="Q38" s="113"/>
-      <c r="R38" s="113"/>
+      <c r="A38" s="107"/>
+      <c r="B38" s="107"/>
+      <c r="C38" s="107"/>
+      <c r="D38" s="107"/>
+      <c r="E38" s="107"/>
+      <c r="F38" s="107"/>
+      <c r="G38" s="107"/>
+      <c r="H38" s="107"/>
+      <c r="I38" s="107"/>
+      <c r="J38" s="107"/>
+      <c r="K38" s="107"/>
+      <c r="L38" s="107"/>
+      <c r="M38" s="107"/>
+      <c r="N38" s="107"/>
+      <c r="O38" s="107"/>
+      <c r="P38" s="107"/>
+      <c r="Q38" s="107"/>
+      <c r="R38" s="107"/>
     </row>
     <row r="39" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="89" t="s">
+      <c r="A39" s="108" t="s">
         <v>10</v>
       </c>
-      <c r="B39" s="90"/>
-      <c r="C39" s="90"/>
-      <c r="D39" s="90" t="s">
+      <c r="B39" s="109"/>
+      <c r="C39" s="109"/>
+      <c r="D39" s="109" t="s">
         <v>11</v>
       </c>
-      <c r="E39" s="90"/>
-      <c r="F39" s="90"/>
-      <c r="G39" s="93"/>
-      <c r="H39" s="90" t="s">
+      <c r="E39" s="109"/>
+      <c r="F39" s="109"/>
+      <c r="G39" s="110"/>
+      <c r="H39" s="109" t="s">
         <v>10</v>
       </c>
-      <c r="I39" s="90"/>
-      <c r="J39" s="90"/>
-      <c r="K39" s="90" t="s">
+      <c r="I39" s="109"/>
+      <c r="J39" s="109"/>
+      <c r="K39" s="109" t="s">
         <v>11</v>
       </c>
-      <c r="L39" s="90"/>
-      <c r="M39" s="90"/>
-      <c r="N39" s="93"/>
-      <c r="O39" s="90" t="s">
+      <c r="L39" s="109"/>
+      <c r="M39" s="109"/>
+      <c r="N39" s="110"/>
+      <c r="O39" s="109" t="s">
         <v>37</v>
       </c>
-      <c r="P39" s="90"/>
-      <c r="Q39" s="90"/>
-      <c r="R39" s="95"/>
+      <c r="P39" s="109"/>
+      <c r="Q39" s="109"/>
+      <c r="R39" s="112"/>
     </row>
     <row r="40" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="91"/>
-      <c r="B40" s="92"/>
-      <c r="C40" s="92"/>
-      <c r="D40" s="92"/>
-      <c r="E40" s="92"/>
-      <c r="F40" s="92"/>
-      <c r="G40" s="94"/>
-      <c r="H40" s="92"/>
-      <c r="I40" s="92"/>
-      <c r="J40" s="92"/>
-      <c r="K40" s="92"/>
-      <c r="L40" s="92"/>
-      <c r="M40" s="92"/>
-      <c r="N40" s="94"/>
-      <c r="O40" s="92"/>
-      <c r="P40" s="92"/>
-      <c r="Q40" s="92"/>
-      <c r="R40" s="96"/>
+      <c r="A40" s="89"/>
+      <c r="B40" s="90"/>
+      <c r="C40" s="90"/>
+      <c r="D40" s="90"/>
+      <c r="E40" s="90"/>
+      <c r="F40" s="90"/>
+      <c r="G40" s="111"/>
+      <c r="H40" s="90"/>
+      <c r="I40" s="90"/>
+      <c r="J40" s="90"/>
+      <c r="K40" s="90"/>
+      <c r="L40" s="90"/>
+      <c r="M40" s="90"/>
+      <c r="N40" s="111"/>
+      <c r="O40" s="90"/>
+      <c r="P40" s="90"/>
+      <c r="Q40" s="90"/>
+      <c r="R40" s="113"/>
     </row>
     <row r="41" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="64" t="s">
@@ -8782,21 +8766,21 @@
       <c r="A45" s="88" t="s">
         <v>17</v>
       </c>
-      <c r="B45" s="54"/>
-      <c r="C45" s="54"/>
-      <c r="D45" s="52"/>
-      <c r="E45" s="52"/>
-      <c r="F45" s="52"/>
-      <c r="G45" s="53"/>
-      <c r="H45" s="54" t="s">
+      <c r="B45" s="60"/>
+      <c r="C45" s="60"/>
+      <c r="D45" s="58"/>
+      <c r="E45" s="58"/>
+      <c r="F45" s="58"/>
+      <c r="G45" s="59"/>
+      <c r="H45" s="60" t="s">
         <v>17</v>
       </c>
-      <c r="I45" s="54"/>
-      <c r="J45" s="54"/>
-      <c r="K45" s="52"/>
-      <c r="L45" s="52"/>
-      <c r="M45" s="52"/>
-      <c r="N45" s="53"/>
+      <c r="I45" s="60"/>
+      <c r="J45" s="60"/>
+      <c r="K45" s="58"/>
+      <c r="L45" s="58"/>
+      <c r="M45" s="58"/>
+      <c r="N45" s="59"/>
       <c r="O45" s="163"/>
       <c r="P45" s="164"/>
       <c r="Q45" s="164"/>
@@ -9066,9 +9050,7 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.47244094488188981" right="0.47244094488188981" top="0.44" bottom="0.55118110236220474" header="0.25" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="93" orientation="portrait" r:id="rId1"/>
-  <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;R&amp;"ＭＳ Ｐ明朝,標準"&amp;7Ver.3-12.03-01</oddFooter>
-  </headerFooter>
+  <headerFooter alignWithMargins="0"/>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="18" max="1048575" man="1"/>
   </colBreaks>
@@ -9101,16 +9083,16 @@
     </row>
     <row r="3" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A3" s="3"/>
-      <c r="O3" s="145"/>
-      <c r="P3" s="145"/>
-      <c r="Q3" s="145"/>
-      <c r="R3" s="145"/>
+      <c r="O3" s="136"/>
+      <c r="P3" s="136"/>
+      <c r="Q3" s="136"/>
+      <c r="R3" s="136"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="O4" s="145"/>
-      <c r="P4" s="145"/>
-      <c r="Q4" s="145"/>
-      <c r="R4" s="145"/>
+      <c r="O4" s="136"/>
+      <c r="P4" s="136"/>
+      <c r="Q4" s="136"/>
+      <c r="R4" s="136"/>
     </row>
     <row r="5" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="N5" s="4"/>
@@ -9241,53 +9223,53 @@
     </row>
     <row r="19" spans="1:18" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="20" spans="1:18" ht="12.75" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="89" t="s">
+      <c r="A20" s="108" t="s">
         <v>3</v>
       </c>
-      <c r="B20" s="90"/>
-      <c r="C20" s="90"/>
-      <c r="D20" s="139"/>
-      <c r="E20" s="140"/>
-      <c r="F20" s="140"/>
-      <c r="G20" s="140"/>
-      <c r="H20" s="140"/>
-      <c r="I20" s="140"/>
-      <c r="J20" s="140"/>
-      <c r="K20" s="140"/>
-      <c r="L20" s="140"/>
-      <c r="M20" s="140"/>
-      <c r="N20" s="140"/>
-      <c r="O20" s="140"/>
-      <c r="P20" s="140"/>
-      <c r="Q20" s="140"/>
-      <c r="R20" s="141"/>
+      <c r="B20" s="109"/>
+      <c r="C20" s="109"/>
+      <c r="D20" s="140"/>
+      <c r="E20" s="141"/>
+      <c r="F20" s="141"/>
+      <c r="G20" s="141"/>
+      <c r="H20" s="141"/>
+      <c r="I20" s="141"/>
+      <c r="J20" s="141"/>
+      <c r="K20" s="141"/>
+      <c r="L20" s="141"/>
+      <c r="M20" s="141"/>
+      <c r="N20" s="141"/>
+      <c r="O20" s="141"/>
+      <c r="P20" s="141"/>
+      <c r="Q20" s="141"/>
+      <c r="R20" s="142"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A21" s="91"/>
-      <c r="B21" s="92"/>
-      <c r="C21" s="92"/>
-      <c r="D21" s="142"/>
-      <c r="E21" s="143"/>
-      <c r="F21" s="143"/>
-      <c r="G21" s="143"/>
-      <c r="H21" s="143"/>
-      <c r="I21" s="143"/>
-      <c r="J21" s="143"/>
-      <c r="K21" s="143"/>
-      <c r="L21" s="143"/>
-      <c r="M21" s="143"/>
-      <c r="N21" s="143"/>
-      <c r="O21" s="143"/>
-      <c r="P21" s="143"/>
-      <c r="Q21" s="143"/>
-      <c r="R21" s="144"/>
+      <c r="A21" s="89"/>
+      <c r="B21" s="90"/>
+      <c r="C21" s="90"/>
+      <c r="D21" s="143"/>
+      <c r="E21" s="144"/>
+      <c r="F21" s="144"/>
+      <c r="G21" s="144"/>
+      <c r="H21" s="144"/>
+      <c r="I21" s="144"/>
+      <c r="J21" s="144"/>
+      <c r="K21" s="144"/>
+      <c r="L21" s="144"/>
+      <c r="M21" s="144"/>
+      <c r="N21" s="144"/>
+      <c r="O21" s="144"/>
+      <c r="P21" s="144"/>
+      <c r="Q21" s="144"/>
+      <c r="R21" s="145"/>
     </row>
     <row r="22" spans="1:18" ht="5.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="91" t="s">
+      <c r="A22" s="89" t="s">
         <v>4</v>
       </c>
-      <c r="B22" s="92"/>
-      <c r="C22" s="92"/>
+      <c r="B22" s="90"/>
+      <c r="C22" s="90"/>
       <c r="D22" s="9"/>
       <c r="L22" s="10"/>
       <c r="M22" s="114" t="s">
@@ -9300,9 +9282,9 @@
       <c r="R22" s="120"/>
     </row>
     <row r="23" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="91"/>
-      <c r="B23" s="92"/>
-      <c r="C23" s="92"/>
+      <c r="A23" s="89"/>
+      <c r="B23" s="90"/>
+      <c r="C23" s="90"/>
       <c r="D23" s="127"/>
       <c r="E23" s="128"/>
       <c r="F23" s="128"/>
@@ -9320,9 +9302,9 @@
       <c r="R23" s="123"/>
     </row>
     <row r="24" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="91"/>
-      <c r="B24" s="92"/>
-      <c r="C24" s="92"/>
+      <c r="A24" s="89"/>
+      <c r="B24" s="90"/>
+      <c r="C24" s="90"/>
       <c r="D24" s="130"/>
       <c r="E24" s="128"/>
       <c r="F24" s="128"/>
@@ -9340,9 +9322,9 @@
       <c r="R24" s="123"/>
     </row>
     <row r="25" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="91"/>
-      <c r="B25" s="92"/>
-      <c r="C25" s="92"/>
+      <c r="A25" s="89"/>
+      <c r="B25" s="90"/>
+      <c r="C25" s="90"/>
       <c r="D25" s="130"/>
       <c r="E25" s="128"/>
       <c r="F25" s="128"/>
@@ -9360,9 +9342,9 @@
       <c r="R25" s="123"/>
     </row>
     <row r="26" spans="1:18" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="91"/>
-      <c r="B26" s="92"/>
-      <c r="C26" s="92"/>
+      <c r="A26" s="89"/>
+      <c r="B26" s="90"/>
+      <c r="C26" s="90"/>
       <c r="D26" s="11"/>
       <c r="E26" s="12"/>
       <c r="F26" s="13"/>
@@ -9380,9 +9362,9 @@
       <c r="R26" s="123"/>
     </row>
     <row r="27" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="91"/>
-      <c r="B27" s="92"/>
-      <c r="C27" s="92"/>
+      <c r="A27" s="89"/>
+      <c r="B27" s="90"/>
+      <c r="C27" s="90"/>
       <c r="D27" s="16"/>
       <c r="F27" s="17"/>
       <c r="G27" s="18"/>
@@ -9420,22 +9402,22 @@
     <row r="29" spans="1:18" ht="12.75" thickTop="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="1:18" ht="12.75" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="31" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="89" t="s">
+      <c r="A31" s="108" t="s">
         <v>6</v>
       </c>
-      <c r="B31" s="90"/>
-      <c r="C31" s="90"/>
+      <c r="B31" s="109"/>
+      <c r="C31" s="109"/>
       <c r="D31" s="131"/>
       <c r="E31" s="131"/>
       <c r="F31" s="131"/>
       <c r="G31" s="131"/>
       <c r="H31" s="131"/>
       <c r="I31" s="131"/>
-      <c r="J31" s="90" t="s">
+      <c r="J31" s="109" t="s">
         <v>7</v>
       </c>
-      <c r="K31" s="90"/>
-      <c r="L31" s="90"/>
+      <c r="K31" s="109"/>
+      <c r="L31" s="109"/>
       <c r="M31" s="131"/>
       <c r="N31" s="131"/>
       <c r="O31" s="131"/>
@@ -9444,18 +9426,18 @@
       <c r="R31" s="133"/>
     </row>
     <row r="32" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="91"/>
-      <c r="B32" s="92"/>
-      <c r="C32" s="92"/>
+      <c r="A32" s="89"/>
+      <c r="B32" s="90"/>
+      <c r="C32" s="90"/>
       <c r="D32" s="132"/>
       <c r="E32" s="132"/>
       <c r="F32" s="132"/>
       <c r="G32" s="132"/>
       <c r="H32" s="132"/>
       <c r="I32" s="132"/>
-      <c r="J32" s="92"/>
-      <c r="K32" s="92"/>
-      <c r="L32" s="92"/>
+      <c r="J32" s="90"/>
+      <c r="K32" s="90"/>
+      <c r="L32" s="90"/>
       <c r="M32" s="132"/>
       <c r="N32" s="132"/>
       <c r="O32" s="132"/>
@@ -9464,53 +9446,53 @@
       <c r="R32" s="134"/>
     </row>
     <row r="33" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="91" t="s">
+      <c r="A33" s="89" t="s">
         <v>8</v>
       </c>
-      <c r="B33" s="92"/>
-      <c r="C33" s="92"/>
-      <c r="D33" s="105"/>
-      <c r="E33" s="106"/>
-      <c r="F33" s="106"/>
-      <c r="G33" s="106"/>
-      <c r="H33" s="106"/>
-      <c r="I33" s="106"/>
-      <c r="J33" s="106"/>
-      <c r="K33" s="106"/>
-      <c r="L33" s="106"/>
-      <c r="M33" s="106"/>
-      <c r="N33" s="106"/>
-      <c r="O33" s="106"/>
-      <c r="P33" s="106"/>
-      <c r="Q33" s="106"/>
-      <c r="R33" s="107"/>
+      <c r="B33" s="90"/>
+      <c r="C33" s="90"/>
+      <c r="D33" s="91"/>
+      <c r="E33" s="92"/>
+      <c r="F33" s="92"/>
+      <c r="G33" s="92"/>
+      <c r="H33" s="92"/>
+      <c r="I33" s="92"/>
+      <c r="J33" s="92"/>
+      <c r="K33" s="92"/>
+      <c r="L33" s="92"/>
+      <c r="M33" s="92"/>
+      <c r="N33" s="92"/>
+      <c r="O33" s="92"/>
+      <c r="P33" s="92"/>
+      <c r="Q33" s="92"/>
+      <c r="R33" s="93"/>
     </row>
     <row r="34" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="91"/>
-      <c r="B34" s="92"/>
-      <c r="C34" s="92"/>
-      <c r="D34" s="108"/>
-      <c r="E34" s="109"/>
-      <c r="F34" s="109"/>
-      <c r="G34" s="109"/>
-      <c r="H34" s="109"/>
-      <c r="I34" s="109"/>
-      <c r="J34" s="109"/>
-      <c r="K34" s="109"/>
-      <c r="L34" s="109"/>
-      <c r="M34" s="109"/>
-      <c r="N34" s="109"/>
-      <c r="O34" s="109"/>
-      <c r="P34" s="109"/>
-      <c r="Q34" s="109"/>
-      <c r="R34" s="110"/>
+      <c r="A34" s="89"/>
+      <c r="B34" s="90"/>
+      <c r="C34" s="90"/>
+      <c r="D34" s="94"/>
+      <c r="E34" s="95"/>
+      <c r="F34" s="95"/>
+      <c r="G34" s="95"/>
+      <c r="H34" s="95"/>
+      <c r="I34" s="95"/>
+      <c r="J34" s="95"/>
+      <c r="K34" s="95"/>
+      <c r="L34" s="95"/>
+      <c r="M34" s="95"/>
+      <c r="N34" s="95"/>
+      <c r="O34" s="95"/>
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="96"/>
     </row>
     <row r="35" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="91" t="s">
+      <c r="A35" s="89" t="s">
         <v>9</v>
       </c>
-      <c r="B35" s="92"/>
-      <c r="C35" s="92"/>
+      <c r="B35" s="90"/>
+      <c r="C35" s="90"/>
       <c r="D35" s="99"/>
       <c r="E35" s="100"/>
       <c r="F35" s="100"/>
@@ -9548,94 +9530,94 @@
       <c r="R36" s="104"/>
     </row>
     <row r="37" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="111"/>
-      <c r="B37" s="112"/>
-      <c r="C37" s="112"/>
-      <c r="D37" s="112"/>
-      <c r="E37" s="112"/>
-      <c r="F37" s="112"/>
-      <c r="G37" s="112"/>
-      <c r="H37" s="112"/>
-      <c r="I37" s="112"/>
-      <c r="J37" s="112"/>
-      <c r="K37" s="112"/>
-      <c r="L37" s="112"/>
-      <c r="M37" s="112"/>
-      <c r="N37" s="112"/>
-      <c r="O37" s="112"/>
-      <c r="P37" s="112"/>
-      <c r="Q37" s="112"/>
-      <c r="R37" s="112"/>
+      <c r="A37" s="105"/>
+      <c r="B37" s="106"/>
+      <c r="C37" s="106"/>
+      <c r="D37" s="106"/>
+      <c r="E37" s="106"/>
+      <c r="F37" s="106"/>
+      <c r="G37" s="106"/>
+      <c r="H37" s="106"/>
+      <c r="I37" s="106"/>
+      <c r="J37" s="106"/>
+      <c r="K37" s="106"/>
+      <c r="L37" s="106"/>
+      <c r="M37" s="106"/>
+      <c r="N37" s="106"/>
+      <c r="O37" s="106"/>
+      <c r="P37" s="106"/>
+      <c r="Q37" s="106"/>
+      <c r="R37" s="106"/>
     </row>
     <row r="38" spans="1:18" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="113"/>
-      <c r="B38" s="113"/>
-      <c r="C38" s="113"/>
-      <c r="D38" s="113"/>
-      <c r="E38" s="113"/>
-      <c r="F38" s="113"/>
-      <c r="G38" s="113"/>
-      <c r="H38" s="113"/>
-      <c r="I38" s="113"/>
-      <c r="J38" s="113"/>
-      <c r="K38" s="113"/>
-      <c r="L38" s="113"/>
-      <c r="M38" s="113"/>
-      <c r="N38" s="113"/>
-      <c r="O38" s="113"/>
-      <c r="P38" s="113"/>
-      <c r="Q38" s="113"/>
-      <c r="R38" s="113"/>
+      <c r="A38" s="107"/>
+      <c r="B38" s="107"/>
+      <c r="C38" s="107"/>
+      <c r="D38" s="107"/>
+      <c r="E38" s="107"/>
+      <c r="F38" s="107"/>
+      <c r="G38" s="107"/>
+      <c r="H38" s="107"/>
+      <c r="I38" s="107"/>
+      <c r="J38" s="107"/>
+      <c r="K38" s="107"/>
+      <c r="L38" s="107"/>
+      <c r="M38" s="107"/>
+      <c r="N38" s="107"/>
+      <c r="O38" s="107"/>
+      <c r="P38" s="107"/>
+      <c r="Q38" s="107"/>
+      <c r="R38" s="107"/>
     </row>
     <row r="39" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="89" t="s">
+      <c r="A39" s="108" t="s">
         <v>10</v>
       </c>
-      <c r="B39" s="90"/>
-      <c r="C39" s="90"/>
-      <c r="D39" s="90" t="s">
+      <c r="B39" s="109"/>
+      <c r="C39" s="109"/>
+      <c r="D39" s="109" t="s">
         <v>11</v>
       </c>
-      <c r="E39" s="90"/>
-      <c r="F39" s="90"/>
-      <c r="G39" s="93"/>
-      <c r="H39" s="90" t="s">
+      <c r="E39" s="109"/>
+      <c r="F39" s="109"/>
+      <c r="G39" s="110"/>
+      <c r="H39" s="109" t="s">
         <v>10</v>
       </c>
-      <c r="I39" s="90"/>
-      <c r="J39" s="90"/>
-      <c r="K39" s="90" t="s">
+      <c r="I39" s="109"/>
+      <c r="J39" s="109"/>
+      <c r="K39" s="109" t="s">
         <v>11</v>
       </c>
-      <c r="L39" s="90"/>
-      <c r="M39" s="90"/>
-      <c r="N39" s="93"/>
-      <c r="O39" s="90" t="s">
+      <c r="L39" s="109"/>
+      <c r="M39" s="109"/>
+      <c r="N39" s="110"/>
+      <c r="O39" s="109" t="s">
         <v>12</v>
       </c>
-      <c r="P39" s="90"/>
-      <c r="Q39" s="90"/>
-      <c r="R39" s="95"/>
+      <c r="P39" s="109"/>
+      <c r="Q39" s="109"/>
+      <c r="R39" s="112"/>
     </row>
     <row r="40" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="91"/>
-      <c r="B40" s="92"/>
-      <c r="C40" s="92"/>
-      <c r="D40" s="92"/>
-      <c r="E40" s="92"/>
-      <c r="F40" s="92"/>
-      <c r="G40" s="94"/>
-      <c r="H40" s="92"/>
-      <c r="I40" s="92"/>
-      <c r="J40" s="92"/>
-      <c r="K40" s="92"/>
-      <c r="L40" s="92"/>
-      <c r="M40" s="92"/>
-      <c r="N40" s="94"/>
-      <c r="O40" s="92"/>
-      <c r="P40" s="92"/>
-      <c r="Q40" s="92"/>
-      <c r="R40" s="96"/>
+      <c r="A40" s="89"/>
+      <c r="B40" s="90"/>
+      <c r="C40" s="90"/>
+      <c r="D40" s="90"/>
+      <c r="E40" s="90"/>
+      <c r="F40" s="90"/>
+      <c r="G40" s="111"/>
+      <c r="H40" s="90"/>
+      <c r="I40" s="90"/>
+      <c r="J40" s="90"/>
+      <c r="K40" s="90"/>
+      <c r="L40" s="90"/>
+      <c r="M40" s="90"/>
+      <c r="N40" s="111"/>
+      <c r="O40" s="90"/>
+      <c r="P40" s="90"/>
+      <c r="Q40" s="90"/>
+      <c r="R40" s="113"/>
     </row>
     <row r="41" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="64" t="s">
@@ -9729,21 +9711,21 @@
       <c r="A45" s="88" t="s">
         <v>17</v>
       </c>
-      <c r="B45" s="54"/>
-      <c r="C45" s="54"/>
-      <c r="D45" s="52"/>
-      <c r="E45" s="52"/>
-      <c r="F45" s="52"/>
-      <c r="G45" s="53"/>
-      <c r="H45" s="54" t="s">
+      <c r="B45" s="60"/>
+      <c r="C45" s="60"/>
+      <c r="D45" s="58"/>
+      <c r="E45" s="58"/>
+      <c r="F45" s="58"/>
+      <c r="G45" s="59"/>
+      <c r="H45" s="60" t="s">
         <v>17</v>
       </c>
-      <c r="I45" s="54"/>
-      <c r="J45" s="54"/>
-      <c r="K45" s="52"/>
-      <c r="L45" s="52"/>
-      <c r="M45" s="52"/>
-      <c r="N45" s="53"/>
+      <c r="I45" s="60"/>
+      <c r="J45" s="60"/>
+      <c r="K45" s="58"/>
+      <c r="L45" s="58"/>
+      <c r="M45" s="58"/>
+      <c r="N45" s="59"/>
       <c r="O45" s="84"/>
       <c r="P45" s="84"/>
       <c r="Q45" s="84"/>
@@ -10079,9 +10061,7 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.47244094488188981" right="0.47244094488188981" top="0.44" bottom="0.55118110236220474" header="0.25" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="93" orientation="portrait" r:id="rId1"/>
-  <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;R&amp;"ＭＳ Ｐ明朝,標準"&amp;7Ver.3-12.03-01</oddFooter>
-  </headerFooter>
+  <headerFooter alignWithMargins="0"/>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="18" max="1048575" man="1"/>
   </colBreaks>
@@ -10114,16 +10094,16 @@
     </row>
     <row r="3" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A3" s="3"/>
-      <c r="O3" s="145"/>
-      <c r="P3" s="145"/>
-      <c r="Q3" s="145"/>
-      <c r="R3" s="145"/>
+      <c r="O3" s="136"/>
+      <c r="P3" s="136"/>
+      <c r="Q3" s="136"/>
+      <c r="R3" s="136"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="O4" s="145"/>
-      <c r="P4" s="145"/>
-      <c r="Q4" s="145"/>
-      <c r="R4" s="145"/>
+      <c r="O4" s="136"/>
+      <c r="P4" s="136"/>
+      <c r="Q4" s="136"/>
+      <c r="R4" s="136"/>
     </row>
     <row r="5" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="N5" s="4"/>
@@ -10254,53 +10234,53 @@
     </row>
     <row r="19" spans="1:18" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="20" spans="1:18" ht="12.75" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="89" t="s">
+      <c r="A20" s="108" t="s">
         <v>3</v>
       </c>
-      <c r="B20" s="90"/>
-      <c r="C20" s="90"/>
-      <c r="D20" s="139"/>
-      <c r="E20" s="140"/>
-      <c r="F20" s="140"/>
-      <c r="G20" s="140"/>
-      <c r="H20" s="140"/>
-      <c r="I20" s="140"/>
-      <c r="J20" s="140"/>
-      <c r="K20" s="140"/>
-      <c r="L20" s="140"/>
-      <c r="M20" s="140"/>
-      <c r="N20" s="140"/>
-      <c r="O20" s="140"/>
-      <c r="P20" s="140"/>
-      <c r="Q20" s="140"/>
-      <c r="R20" s="141"/>
+      <c r="B20" s="109"/>
+      <c r="C20" s="109"/>
+      <c r="D20" s="140"/>
+      <c r="E20" s="141"/>
+      <c r="F20" s="141"/>
+      <c r="G20" s="141"/>
+      <c r="H20" s="141"/>
+      <c r="I20" s="141"/>
+      <c r="J20" s="141"/>
+      <c r="K20" s="141"/>
+      <c r="L20" s="141"/>
+      <c r="M20" s="141"/>
+      <c r="N20" s="141"/>
+      <c r="O20" s="141"/>
+      <c r="P20" s="141"/>
+      <c r="Q20" s="141"/>
+      <c r="R20" s="142"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A21" s="91"/>
-      <c r="B21" s="92"/>
-      <c r="C21" s="92"/>
-      <c r="D21" s="142"/>
-      <c r="E21" s="143"/>
-      <c r="F21" s="143"/>
-      <c r="G21" s="143"/>
-      <c r="H21" s="143"/>
-      <c r="I21" s="143"/>
-      <c r="J21" s="143"/>
-      <c r="K21" s="143"/>
-      <c r="L21" s="143"/>
-      <c r="M21" s="143"/>
-      <c r="N21" s="143"/>
-      <c r="O21" s="143"/>
-      <c r="P21" s="143"/>
-      <c r="Q21" s="143"/>
-      <c r="R21" s="144"/>
+      <c r="A21" s="89"/>
+      <c r="B21" s="90"/>
+      <c r="C21" s="90"/>
+      <c r="D21" s="143"/>
+      <c r="E21" s="144"/>
+      <c r="F21" s="144"/>
+      <c r="G21" s="144"/>
+      <c r="H21" s="144"/>
+      <c r="I21" s="144"/>
+      <c r="J21" s="144"/>
+      <c r="K21" s="144"/>
+      <c r="L21" s="144"/>
+      <c r="M21" s="144"/>
+      <c r="N21" s="144"/>
+      <c r="O21" s="144"/>
+      <c r="P21" s="144"/>
+      <c r="Q21" s="144"/>
+      <c r="R21" s="145"/>
     </row>
     <row r="22" spans="1:18" ht="5.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="91" t="s">
+      <c r="A22" s="89" t="s">
         <v>4</v>
       </c>
-      <c r="B22" s="92"/>
-      <c r="C22" s="92"/>
+      <c r="B22" s="90"/>
+      <c r="C22" s="90"/>
       <c r="D22" s="9"/>
       <c r="L22" s="10"/>
       <c r="M22" s="114" t="s">
@@ -10313,9 +10293,9 @@
       <c r="R22" s="120"/>
     </row>
     <row r="23" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="91"/>
-      <c r="B23" s="92"/>
-      <c r="C23" s="92"/>
+      <c r="A23" s="89"/>
+      <c r="B23" s="90"/>
+      <c r="C23" s="90"/>
       <c r="D23" s="127"/>
       <c r="E23" s="128"/>
       <c r="F23" s="128"/>
@@ -10333,9 +10313,9 @@
       <c r="R23" s="123"/>
     </row>
     <row r="24" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="91"/>
-      <c r="B24" s="92"/>
-      <c r="C24" s="92"/>
+      <c r="A24" s="89"/>
+      <c r="B24" s="90"/>
+      <c r="C24" s="90"/>
       <c r="D24" s="130"/>
       <c r="E24" s="128"/>
       <c r="F24" s="128"/>
@@ -10353,9 +10333,9 @@
       <c r="R24" s="123"/>
     </row>
     <row r="25" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="91"/>
-      <c r="B25" s="92"/>
-      <c r="C25" s="92"/>
+      <c r="A25" s="89"/>
+      <c r="B25" s="90"/>
+      <c r="C25" s="90"/>
       <c r="D25" s="130"/>
       <c r="E25" s="128"/>
       <c r="F25" s="128"/>
@@ -10373,9 +10353,9 @@
       <c r="R25" s="123"/>
     </row>
     <row r="26" spans="1:18" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="91"/>
-      <c r="B26" s="92"/>
-      <c r="C26" s="92"/>
+      <c r="A26" s="89"/>
+      <c r="B26" s="90"/>
+      <c r="C26" s="90"/>
       <c r="D26" s="11"/>
       <c r="E26" s="12"/>
       <c r="F26" s="13"/>
@@ -10393,9 +10373,9 @@
       <c r="R26" s="123"/>
     </row>
     <row r="27" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="91"/>
-      <c r="B27" s="92"/>
-      <c r="C27" s="92"/>
+      <c r="A27" s="89"/>
+      <c r="B27" s="90"/>
+      <c r="C27" s="90"/>
       <c r="D27" s="16"/>
       <c r="F27" s="17"/>
       <c r="G27" s="18"/>
@@ -10433,22 +10413,22 @@
     <row r="29" spans="1:18" ht="12.75" thickTop="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="1:18" ht="12.75" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="31" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="89" t="s">
+      <c r="A31" s="108" t="s">
         <v>6</v>
       </c>
-      <c r="B31" s="90"/>
-      <c r="C31" s="90"/>
+      <c r="B31" s="109"/>
+      <c r="C31" s="109"/>
       <c r="D31" s="131"/>
       <c r="E31" s="131"/>
       <c r="F31" s="131"/>
       <c r="G31" s="131"/>
       <c r="H31" s="131"/>
       <c r="I31" s="131"/>
-      <c r="J31" s="90" t="s">
+      <c r="J31" s="109" t="s">
         <v>7</v>
       </c>
-      <c r="K31" s="90"/>
-      <c r="L31" s="90"/>
+      <c r="K31" s="109"/>
+      <c r="L31" s="109"/>
       <c r="M31" s="131"/>
       <c r="N31" s="131"/>
       <c r="O31" s="131"/>
@@ -10457,18 +10437,18 @@
       <c r="R31" s="133"/>
     </row>
     <row r="32" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="91"/>
-      <c r="B32" s="92"/>
-      <c r="C32" s="92"/>
+      <c r="A32" s="89"/>
+      <c r="B32" s="90"/>
+      <c r="C32" s="90"/>
       <c r="D32" s="132"/>
       <c r="E32" s="132"/>
       <c r="F32" s="132"/>
       <c r="G32" s="132"/>
       <c r="H32" s="132"/>
       <c r="I32" s="132"/>
-      <c r="J32" s="92"/>
-      <c r="K32" s="92"/>
-      <c r="L32" s="92"/>
+      <c r="J32" s="90"/>
+      <c r="K32" s="90"/>
+      <c r="L32" s="90"/>
       <c r="M32" s="132"/>
       <c r="N32" s="132"/>
       <c r="O32" s="132"/>
@@ -10477,53 +10457,53 @@
       <c r="R32" s="134"/>
     </row>
     <row r="33" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="91" t="s">
+      <c r="A33" s="89" t="s">
         <v>8</v>
       </c>
-      <c r="B33" s="92"/>
-      <c r="C33" s="92"/>
-      <c r="D33" s="105"/>
-      <c r="E33" s="106"/>
-      <c r="F33" s="106"/>
-      <c r="G33" s="106"/>
-      <c r="H33" s="106"/>
-      <c r="I33" s="106"/>
-      <c r="J33" s="106"/>
-      <c r="K33" s="106"/>
-      <c r="L33" s="106"/>
-      <c r="M33" s="106"/>
-      <c r="N33" s="106"/>
-      <c r="O33" s="106"/>
-      <c r="P33" s="106"/>
-      <c r="Q33" s="106"/>
-      <c r="R33" s="107"/>
+      <c r="B33" s="90"/>
+      <c r="C33" s="90"/>
+      <c r="D33" s="91"/>
+      <c r="E33" s="92"/>
+      <c r="F33" s="92"/>
+      <c r="G33" s="92"/>
+      <c r="H33" s="92"/>
+      <c r="I33" s="92"/>
+      <c r="J33" s="92"/>
+      <c r="K33" s="92"/>
+      <c r="L33" s="92"/>
+      <c r="M33" s="92"/>
+      <c r="N33" s="92"/>
+      <c r="O33" s="92"/>
+      <c r="P33" s="92"/>
+      <c r="Q33" s="92"/>
+      <c r="R33" s="93"/>
     </row>
     <row r="34" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="91"/>
-      <c r="B34" s="92"/>
-      <c r="C34" s="92"/>
-      <c r="D34" s="108"/>
-      <c r="E34" s="109"/>
-      <c r="F34" s="109"/>
-      <c r="G34" s="109"/>
-      <c r="H34" s="109"/>
-      <c r="I34" s="109"/>
-      <c r="J34" s="109"/>
-      <c r="K34" s="109"/>
-      <c r="L34" s="109"/>
-      <c r="M34" s="109"/>
-      <c r="N34" s="109"/>
-      <c r="O34" s="109"/>
-      <c r="P34" s="109"/>
-      <c r="Q34" s="109"/>
-      <c r="R34" s="110"/>
+      <c r="A34" s="89"/>
+      <c r="B34" s="90"/>
+      <c r="C34" s="90"/>
+      <c r="D34" s="94"/>
+      <c r="E34" s="95"/>
+      <c r="F34" s="95"/>
+      <c r="G34" s="95"/>
+      <c r="H34" s="95"/>
+      <c r="I34" s="95"/>
+      <c r="J34" s="95"/>
+      <c r="K34" s="95"/>
+      <c r="L34" s="95"/>
+      <c r="M34" s="95"/>
+      <c r="N34" s="95"/>
+      <c r="O34" s="95"/>
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="96"/>
     </row>
     <row r="35" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="91" t="s">
+      <c r="A35" s="89" t="s">
         <v>9</v>
       </c>
-      <c r="B35" s="92"/>
-      <c r="C35" s="92"/>
+      <c r="B35" s="90"/>
+      <c r="C35" s="90"/>
       <c r="D35" s="99"/>
       <c r="E35" s="100"/>
       <c r="F35" s="100"/>
@@ -10561,94 +10541,94 @@
       <c r="R36" s="104"/>
     </row>
     <row r="37" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="111"/>
-      <c r="B37" s="112"/>
-      <c r="C37" s="112"/>
-      <c r="D37" s="112"/>
-      <c r="E37" s="112"/>
-      <c r="F37" s="112"/>
-      <c r="G37" s="112"/>
-      <c r="H37" s="112"/>
-      <c r="I37" s="112"/>
-      <c r="J37" s="112"/>
-      <c r="K37" s="112"/>
-      <c r="L37" s="112"/>
-      <c r="M37" s="112"/>
-      <c r="N37" s="112"/>
-      <c r="O37" s="112"/>
-      <c r="P37" s="112"/>
-      <c r="Q37" s="112"/>
-      <c r="R37" s="112"/>
+      <c r="A37" s="105"/>
+      <c r="B37" s="106"/>
+      <c r="C37" s="106"/>
+      <c r="D37" s="106"/>
+      <c r="E37" s="106"/>
+      <c r="F37" s="106"/>
+      <c r="G37" s="106"/>
+      <c r="H37" s="106"/>
+      <c r="I37" s="106"/>
+      <c r="J37" s="106"/>
+      <c r="K37" s="106"/>
+      <c r="L37" s="106"/>
+      <c r="M37" s="106"/>
+      <c r="N37" s="106"/>
+      <c r="O37" s="106"/>
+      <c r="P37" s="106"/>
+      <c r="Q37" s="106"/>
+      <c r="R37" s="106"/>
     </row>
     <row r="38" spans="1:18" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="113"/>
-      <c r="B38" s="113"/>
-      <c r="C38" s="113"/>
-      <c r="D38" s="113"/>
-      <c r="E38" s="113"/>
-      <c r="F38" s="113"/>
-      <c r="G38" s="113"/>
-      <c r="H38" s="113"/>
-      <c r="I38" s="113"/>
-      <c r="J38" s="113"/>
-      <c r="K38" s="113"/>
-      <c r="L38" s="113"/>
-      <c r="M38" s="113"/>
-      <c r="N38" s="113"/>
-      <c r="O38" s="113"/>
-      <c r="P38" s="113"/>
-      <c r="Q38" s="113"/>
-      <c r="R38" s="113"/>
+      <c r="A38" s="107"/>
+      <c r="B38" s="107"/>
+      <c r="C38" s="107"/>
+      <c r="D38" s="107"/>
+      <c r="E38" s="107"/>
+      <c r="F38" s="107"/>
+      <c r="G38" s="107"/>
+      <c r="H38" s="107"/>
+      <c r="I38" s="107"/>
+      <c r="J38" s="107"/>
+      <c r="K38" s="107"/>
+      <c r="L38" s="107"/>
+      <c r="M38" s="107"/>
+      <c r="N38" s="107"/>
+      <c r="O38" s="107"/>
+      <c r="P38" s="107"/>
+      <c r="Q38" s="107"/>
+      <c r="R38" s="107"/>
     </row>
     <row r="39" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="89" t="s">
+      <c r="A39" s="108" t="s">
         <v>10</v>
       </c>
-      <c r="B39" s="90"/>
-      <c r="C39" s="90"/>
-      <c r="D39" s="90" t="s">
+      <c r="B39" s="109"/>
+      <c r="C39" s="109"/>
+      <c r="D39" s="109" t="s">
         <v>11</v>
       </c>
-      <c r="E39" s="90"/>
-      <c r="F39" s="90"/>
-      <c r="G39" s="93"/>
-      <c r="H39" s="90" t="s">
+      <c r="E39" s="109"/>
+      <c r="F39" s="109"/>
+      <c r="G39" s="110"/>
+      <c r="H39" s="109" t="s">
         <v>10</v>
       </c>
-      <c r="I39" s="90"/>
-      <c r="J39" s="90"/>
-      <c r="K39" s="90" t="s">
+      <c r="I39" s="109"/>
+      <c r="J39" s="109"/>
+      <c r="K39" s="109" t="s">
         <v>11</v>
       </c>
-      <c r="L39" s="90"/>
-      <c r="M39" s="90"/>
-      <c r="N39" s="93"/>
-      <c r="O39" s="90" t="s">
+      <c r="L39" s="109"/>
+      <c r="M39" s="109"/>
+      <c r="N39" s="110"/>
+      <c r="O39" s="109" t="s">
         <v>35</v>
       </c>
-      <c r="P39" s="90"/>
-      <c r="Q39" s="90"/>
-      <c r="R39" s="95"/>
+      <c r="P39" s="109"/>
+      <c r="Q39" s="109"/>
+      <c r="R39" s="112"/>
     </row>
     <row r="40" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="91"/>
-      <c r="B40" s="92"/>
-      <c r="C40" s="92"/>
-      <c r="D40" s="92"/>
-      <c r="E40" s="92"/>
-      <c r="F40" s="92"/>
-      <c r="G40" s="94"/>
-      <c r="H40" s="92"/>
-      <c r="I40" s="92"/>
-      <c r="J40" s="92"/>
-      <c r="K40" s="92"/>
-      <c r="L40" s="92"/>
-      <c r="M40" s="92"/>
-      <c r="N40" s="94"/>
-      <c r="O40" s="92"/>
-      <c r="P40" s="92"/>
-      <c r="Q40" s="92"/>
-      <c r="R40" s="96"/>
+      <c r="A40" s="89"/>
+      <c r="B40" s="90"/>
+      <c r="C40" s="90"/>
+      <c r="D40" s="90"/>
+      <c r="E40" s="90"/>
+      <c r="F40" s="90"/>
+      <c r="G40" s="111"/>
+      <c r="H40" s="90"/>
+      <c r="I40" s="90"/>
+      <c r="J40" s="90"/>
+      <c r="K40" s="90"/>
+      <c r="L40" s="90"/>
+      <c r="M40" s="90"/>
+      <c r="N40" s="111"/>
+      <c r="O40" s="90"/>
+      <c r="P40" s="90"/>
+      <c r="Q40" s="90"/>
+      <c r="R40" s="113"/>
     </row>
     <row r="41" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="64" t="s">
@@ -10742,21 +10722,21 @@
       <c r="A45" s="88" t="s">
         <v>17</v>
       </c>
-      <c r="B45" s="54"/>
-      <c r="C45" s="54"/>
-      <c r="D45" s="52"/>
-      <c r="E45" s="52"/>
-      <c r="F45" s="52"/>
-      <c r="G45" s="53"/>
-      <c r="H45" s="54" t="s">
+      <c r="B45" s="60"/>
+      <c r="C45" s="60"/>
+      <c r="D45" s="58"/>
+      <c r="E45" s="58"/>
+      <c r="F45" s="58"/>
+      <c r="G45" s="59"/>
+      <c r="H45" s="60" t="s">
         <v>17</v>
       </c>
-      <c r="I45" s="54"/>
-      <c r="J45" s="54"/>
-      <c r="K45" s="52"/>
-      <c r="L45" s="52"/>
-      <c r="M45" s="52"/>
-      <c r="N45" s="53"/>
+      <c r="I45" s="60"/>
+      <c r="J45" s="60"/>
+      <c r="K45" s="58"/>
+      <c r="L45" s="58"/>
+      <c r="M45" s="58"/>
+      <c r="N45" s="59"/>
       <c r="O45" s="84"/>
       <c r="P45" s="84"/>
       <c r="Q45" s="84"/>
@@ -11104,9 +11084,7 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.47244094488188981" right="0.47244094488188981" top="0.44" bottom="0.55118110236220474" header="0.25" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="93" orientation="portrait" r:id="rId1"/>
-  <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;R&amp;"ＭＳ Ｐ明朝,標準"&amp;7Ver.3-12.03-01</oddFooter>
-  </headerFooter>
+  <headerFooter alignWithMargins="0"/>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="18" max="1048575" man="1"/>
   </colBreaks>

--- a/storage/app/estimateTemplate/all.xlsx
+++ b/storage/app/estimateTemplate/all.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\ohno\eruful\mitumo\storage\app\estimateTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C6CF19B-00DC-4CFC-9F8B-58715B970AF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF5DC3A3-1F7D-4096-8551-E40E862CC13F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{5432EA10-F847-46F9-8033-2A67B2C19C32}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5432EA10-F847-46F9-8033-2A67B2C19C32}"/>
   </bookViews>
   <sheets>
     <sheet name="普通" sheetId="11" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="78">
   <si>
     <t>御　　見　　積　　書</t>
     <rPh sb="0" eb="1">
@@ -805,6 +805,16 @@
     </rPh>
     <rPh sb="5" eb="7">
       <t>ワリビキ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>作業員人数</t>
+    <rPh sb="0" eb="3">
+      <t>サギョウイン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ニンズ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
@@ -1800,9 +1810,23 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="31" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="179" fontId="10" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="31" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="30" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="32" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="31" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1818,20 +1842,6 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="30" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="distributed" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="10" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="31" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="32" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
     </xf>
@@ -2044,6 +2054,24 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="58" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
@@ -2060,24 +2088,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3346,10 +3356,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="O1" s="135"/>
-      <c r="P1" s="135"/>
-      <c r="Q1" s="135"/>
-      <c r="R1" s="135"/>
+      <c r="O1" s="141"/>
+      <c r="P1" s="141"/>
+      <c r="Q1" s="141"/>
+      <c r="R1" s="141"/>
     </row>
     <row r="2" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="O2" s="2"/>
@@ -3359,16 +3369,16 @@
     </row>
     <row r="3" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A3" s="3"/>
-      <c r="O3" s="136"/>
-      <c r="P3" s="136"/>
-      <c r="Q3" s="136"/>
-      <c r="R3" s="136"/>
+      <c r="O3" s="142"/>
+      <c r="P3" s="142"/>
+      <c r="Q3" s="142"/>
+      <c r="R3" s="142"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="O4" s="136"/>
-      <c r="P4" s="136"/>
-      <c r="Q4" s="136"/>
-      <c r="R4" s="136"/>
+      <c r="O4" s="142"/>
+      <c r="P4" s="142"/>
+      <c r="Q4" s="142"/>
+      <c r="R4" s="142"/>
     </row>
     <row r="5" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="N5" s="4"/>
@@ -3431,71 +3441,71 @@
       <c r="R10" s="8"/>
     </row>
     <row r="11" spans="1:18" ht="21" x14ac:dyDescent="0.4">
-      <c r="A11" s="137" t="s">
+      <c r="A11" s="143" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="137"/>
-      <c r="C11" s="137"/>
-      <c r="D11" s="137"/>
-      <c r="E11" s="137"/>
-      <c r="F11" s="137"/>
-      <c r="G11" s="137"/>
-      <c r="H11" s="137"/>
-      <c r="I11" s="137"/>
-      <c r="J11" s="137"/>
-      <c r="K11" s="137"/>
-      <c r="L11" s="137"/>
-      <c r="M11" s="137"/>
-      <c r="N11" s="137"/>
-      <c r="O11" s="137"/>
-      <c r="P11" s="137"/>
-      <c r="Q11" s="137"/>
-      <c r="R11" s="137"/>
+      <c r="B11" s="143"/>
+      <c r="C11" s="143"/>
+      <c r="D11" s="143"/>
+      <c r="E11" s="143"/>
+      <c r="F11" s="143"/>
+      <c r="G11" s="143"/>
+      <c r="H11" s="143"/>
+      <c r="I11" s="143"/>
+      <c r="J11" s="143"/>
+      <c r="K11" s="143"/>
+      <c r="L11" s="143"/>
+      <c r="M11" s="143"/>
+      <c r="N11" s="143"/>
+      <c r="O11" s="143"/>
+      <c r="P11" s="143"/>
+      <c r="Q11" s="143"/>
+      <c r="R11" s="143"/>
     </row>
     <row r="14" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="15" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A15" s="138" t="s">
+      <c r="A15" s="144" t="s">
         <v>1</v>
       </c>
-      <c r="B15" s="138"/>
-      <c r="C15" s="138"/>
-      <c r="D15" s="138"/>
-      <c r="E15" s="138"/>
-      <c r="F15" s="138"/>
-      <c r="G15" s="138"/>
-      <c r="H15" s="138"/>
-      <c r="I15" s="138"/>
-      <c r="J15" s="138"/>
-      <c r="K15" s="138"/>
-      <c r="L15" s="138"/>
-      <c r="M15" s="138"/>
-      <c r="N15" s="138"/>
-      <c r="O15" s="138"/>
-      <c r="P15" s="138"/>
-      <c r="Q15" s="138"/>
-      <c r="R15" s="138"/>
+      <c r="B15" s="144"/>
+      <c r="C15" s="144"/>
+      <c r="D15" s="144"/>
+      <c r="E15" s="144"/>
+      <c r="F15" s="144"/>
+      <c r="G15" s="144"/>
+      <c r="H15" s="144"/>
+      <c r="I15" s="144"/>
+      <c r="J15" s="144"/>
+      <c r="K15" s="144"/>
+      <c r="L15" s="144"/>
+      <c r="M15" s="144"/>
+      <c r="N15" s="144"/>
+      <c r="O15" s="144"/>
+      <c r="P15" s="144"/>
+      <c r="Q15" s="144"/>
+      <c r="R15" s="144"/>
     </row>
     <row r="18" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A18" s="139" t="s">
+      <c r="A18" s="145" t="s">
         <v>2</v>
       </c>
-      <c r="B18" s="139"/>
-      <c r="C18" s="139"/>
-      <c r="D18" s="139"/>
-      <c r="E18" s="139"/>
-      <c r="F18" s="139"/>
-      <c r="G18" s="139"/>
-      <c r="H18" s="139"/>
-      <c r="I18" s="139"/>
-      <c r="J18" s="139"/>
-      <c r="K18" s="139"/>
-      <c r="L18" s="139"/>
-      <c r="M18" s="139"/>
-      <c r="N18" s="139"/>
-      <c r="O18" s="139"/>
-      <c r="P18" s="139"/>
-      <c r="Q18" s="139"/>
-      <c r="R18" s="139"/>
+      <c r="B18" s="145"/>
+      <c r="C18" s="145"/>
+      <c r="D18" s="145"/>
+      <c r="E18" s="145"/>
+      <c r="F18" s="145"/>
+      <c r="G18" s="145"/>
+      <c r="H18" s="145"/>
+      <c r="I18" s="145"/>
+      <c r="J18" s="145"/>
+      <c r="K18" s="145"/>
+      <c r="L18" s="145"/>
+      <c r="M18" s="145"/>
+      <c r="N18" s="145"/>
+      <c r="O18" s="145"/>
+      <c r="P18" s="145"/>
+      <c r="Q18" s="145"/>
+      <c r="R18" s="145"/>
     </row>
     <row r="19" spans="1:18" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="20" spans="1:18" ht="12.75" thickTop="1" x14ac:dyDescent="0.4">
@@ -3504,41 +3514,41 @@
       </c>
       <c r="B20" s="109"/>
       <c r="C20" s="109"/>
-      <c r="D20" s="140"/>
-      <c r="E20" s="141"/>
-      <c r="F20" s="141"/>
-      <c r="G20" s="141"/>
-      <c r="H20" s="141"/>
-      <c r="I20" s="141"/>
-      <c r="J20" s="141"/>
-      <c r="K20" s="141"/>
-      <c r="L20" s="141"/>
-      <c r="M20" s="141"/>
-      <c r="N20" s="141"/>
-      <c r="O20" s="141"/>
-      <c r="P20" s="141"/>
-      <c r="Q20" s="141"/>
-      <c r="R20" s="142"/>
+      <c r="D20" s="135"/>
+      <c r="E20" s="136"/>
+      <c r="F20" s="136"/>
+      <c r="G20" s="136"/>
+      <c r="H20" s="136"/>
+      <c r="I20" s="136"/>
+      <c r="J20" s="136"/>
+      <c r="K20" s="136"/>
+      <c r="L20" s="136"/>
+      <c r="M20" s="136"/>
+      <c r="N20" s="136"/>
+      <c r="O20" s="136"/>
+      <c r="P20" s="136"/>
+      <c r="Q20" s="136"/>
+      <c r="R20" s="137"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A21" s="89"/>
       <c r="B21" s="90"/>
       <c r="C21" s="90"/>
-      <c r="D21" s="143"/>
-      <c r="E21" s="144"/>
-      <c r="F21" s="144"/>
-      <c r="G21" s="144"/>
-      <c r="H21" s="144"/>
-      <c r="I21" s="144"/>
-      <c r="J21" s="144"/>
-      <c r="K21" s="144"/>
-      <c r="L21" s="144"/>
-      <c r="M21" s="144"/>
-      <c r="N21" s="144"/>
-      <c r="O21" s="144"/>
-      <c r="P21" s="144"/>
-      <c r="Q21" s="144"/>
-      <c r="R21" s="145"/>
+      <c r="D21" s="138"/>
+      <c r="E21" s="139"/>
+      <c r="F21" s="139"/>
+      <c r="G21" s="139"/>
+      <c r="H21" s="139"/>
+      <c r="I21" s="139"/>
+      <c r="J21" s="139"/>
+      <c r="K21" s="139"/>
+      <c r="L21" s="139"/>
+      <c r="M21" s="139"/>
+      <c r="N21" s="139"/>
+      <c r="O21" s="139"/>
+      <c r="P21" s="139"/>
+      <c r="Q21" s="139"/>
+      <c r="R21" s="140"/>
     </row>
     <row r="22" spans="1:18" ht="5.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="89" t="s">
@@ -3987,21 +3997,21 @@
       <c r="A45" s="88" t="s">
         <v>17</v>
       </c>
-      <c r="B45" s="60"/>
-      <c r="C45" s="60"/>
-      <c r="D45" s="58"/>
-      <c r="E45" s="58"/>
-      <c r="F45" s="58"/>
-      <c r="G45" s="59"/>
-      <c r="H45" s="60" t="s">
+      <c r="B45" s="54"/>
+      <c r="C45" s="54"/>
+      <c r="D45" s="52"/>
+      <c r="E45" s="52"/>
+      <c r="F45" s="52"/>
+      <c r="G45" s="53"/>
+      <c r="H45" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="I45" s="60"/>
-      <c r="J45" s="60"/>
-      <c r="K45" s="58"/>
-      <c r="L45" s="58"/>
-      <c r="M45" s="58"/>
-      <c r="N45" s="59"/>
+      <c r="I45" s="54"/>
+      <c r="J45" s="54"/>
+      <c r="K45" s="52"/>
+      <c r="L45" s="52"/>
+      <c r="M45" s="52"/>
+      <c r="N45" s="53"/>
       <c r="O45" s="84"/>
       <c r="P45" s="84"/>
       <c r="Q45" s="84"/>
@@ -4011,31 +4021,31 @@
     <row r="47" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="48" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="24"/>
-      <c r="B48" s="61" t="s">
+      <c r="B48" s="55" t="s">
         <v>18</v>
       </c>
-      <c r="C48" s="61"/>
-      <c r="D48" s="61"/>
-      <c r="E48" s="61"/>
+      <c r="C48" s="55"/>
+      <c r="D48" s="55"/>
+      <c r="E48" s="55"/>
       <c r="F48" s="25"/>
-      <c r="G48" s="52" t="s">
+      <c r="G48" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="H48" s="62"/>
-      <c r="I48" s="63"/>
+      <c r="H48" s="57"/>
+      <c r="I48" s="58"/>
       <c r="J48" s="24"/>
-      <c r="K48" s="61" t="s">
+      <c r="K48" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="L48" s="61"/>
-      <c r="M48" s="61"/>
-      <c r="N48" s="61"/>
+      <c r="L48" s="55"/>
+      <c r="M48" s="55"/>
+      <c r="N48" s="55"/>
       <c r="O48" s="25"/>
-      <c r="P48" s="52" t="s">
+      <c r="P48" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="Q48" s="53"/>
-      <c r="R48" s="54"/>
+      <c r="Q48" s="59"/>
+      <c r="R48" s="60"/>
     </row>
     <row r="49" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="26"/>
@@ -4049,12 +4059,12 @@
       <c r="H49" s="51"/>
       <c r="I49" s="50"/>
       <c r="J49" s="29"/>
-      <c r="K49" s="55" t="s">
+      <c r="K49" s="61" t="s">
         <v>22</v>
       </c>
-      <c r="L49" s="56"/>
-      <c r="M49" s="56"/>
-      <c r="N49" s="57"/>
+      <c r="L49" s="62"/>
+      <c r="M49" s="62"/>
+      <c r="N49" s="63"/>
       <c r="O49" s="30"/>
       <c r="P49" s="48"/>
       <c r="Q49" s="51"/>
@@ -4342,10 +4352,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="O1" s="135"/>
-      <c r="P1" s="135"/>
-      <c r="Q1" s="135"/>
-      <c r="R1" s="135"/>
+      <c r="O1" s="141"/>
+      <c r="P1" s="141"/>
+      <c r="Q1" s="141"/>
+      <c r="R1" s="141"/>
     </row>
     <row r="2" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="O2" s="2"/>
@@ -4355,16 +4365,16 @@
     </row>
     <row r="3" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A3" s="3"/>
-      <c r="O3" s="136"/>
-      <c r="P3" s="136"/>
-      <c r="Q3" s="136"/>
-      <c r="R3" s="136"/>
+      <c r="O3" s="142"/>
+      <c r="P3" s="142"/>
+      <c r="Q3" s="142"/>
+      <c r="R3" s="142"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="O4" s="136"/>
-      <c r="P4" s="136"/>
-      <c r="Q4" s="136"/>
-      <c r="R4" s="136"/>
+      <c r="O4" s="142"/>
+      <c r="P4" s="142"/>
+      <c r="Q4" s="142"/>
+      <c r="R4" s="142"/>
     </row>
     <row r="5" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="N5" s="4"/>
@@ -4427,71 +4437,71 @@
       <c r="R10" s="8"/>
     </row>
     <row r="11" spans="1:18" ht="21" x14ac:dyDescent="0.4">
-      <c r="A11" s="137" t="s">
+      <c r="A11" s="143" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="137"/>
-      <c r="C11" s="137"/>
-      <c r="D11" s="137"/>
-      <c r="E11" s="137"/>
-      <c r="F11" s="137"/>
-      <c r="G11" s="137"/>
-      <c r="H11" s="137"/>
-      <c r="I11" s="137"/>
-      <c r="J11" s="137"/>
-      <c r="K11" s="137"/>
-      <c r="L11" s="137"/>
-      <c r="M11" s="137"/>
-      <c r="N11" s="137"/>
-      <c r="O11" s="137"/>
-      <c r="P11" s="137"/>
-      <c r="Q11" s="137"/>
-      <c r="R11" s="137"/>
+      <c r="B11" s="143"/>
+      <c r="C11" s="143"/>
+      <c r="D11" s="143"/>
+      <c r="E11" s="143"/>
+      <c r="F11" s="143"/>
+      <c r="G11" s="143"/>
+      <c r="H11" s="143"/>
+      <c r="I11" s="143"/>
+      <c r="J11" s="143"/>
+      <c r="K11" s="143"/>
+      <c r="L11" s="143"/>
+      <c r="M11" s="143"/>
+      <c r="N11" s="143"/>
+      <c r="O11" s="143"/>
+      <c r="P11" s="143"/>
+      <c r="Q11" s="143"/>
+      <c r="R11" s="143"/>
     </row>
     <row r="14" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="15" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A15" s="138" t="s">
+      <c r="A15" s="144" t="s">
         <v>1</v>
       </c>
-      <c r="B15" s="138"/>
-      <c r="C15" s="138"/>
-      <c r="D15" s="138"/>
-      <c r="E15" s="138"/>
-      <c r="F15" s="138"/>
-      <c r="G15" s="138"/>
-      <c r="H15" s="138"/>
-      <c r="I15" s="138"/>
-      <c r="J15" s="138"/>
-      <c r="K15" s="138"/>
-      <c r="L15" s="138"/>
-      <c r="M15" s="138"/>
-      <c r="N15" s="138"/>
-      <c r="O15" s="138"/>
-      <c r="P15" s="138"/>
-      <c r="Q15" s="138"/>
-      <c r="R15" s="138"/>
+      <c r="B15" s="144"/>
+      <c r="C15" s="144"/>
+      <c r="D15" s="144"/>
+      <c r="E15" s="144"/>
+      <c r="F15" s="144"/>
+      <c r="G15" s="144"/>
+      <c r="H15" s="144"/>
+      <c r="I15" s="144"/>
+      <c r="J15" s="144"/>
+      <c r="K15" s="144"/>
+      <c r="L15" s="144"/>
+      <c r="M15" s="144"/>
+      <c r="N15" s="144"/>
+      <c r="O15" s="144"/>
+      <c r="P15" s="144"/>
+      <c r="Q15" s="144"/>
+      <c r="R15" s="144"/>
     </row>
     <row r="18" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A18" s="139" t="s">
+      <c r="A18" s="145" t="s">
         <v>2</v>
       </c>
-      <c r="B18" s="139"/>
-      <c r="C18" s="139"/>
-      <c r="D18" s="139"/>
-      <c r="E18" s="139"/>
-      <c r="F18" s="139"/>
-      <c r="G18" s="139"/>
-      <c r="H18" s="139"/>
-      <c r="I18" s="139"/>
-      <c r="J18" s="139"/>
-      <c r="K18" s="139"/>
-      <c r="L18" s="139"/>
-      <c r="M18" s="139"/>
-      <c r="N18" s="139"/>
-      <c r="O18" s="139"/>
-      <c r="P18" s="139"/>
-      <c r="Q18" s="139"/>
-      <c r="R18" s="139"/>
+      <c r="B18" s="145"/>
+      <c r="C18" s="145"/>
+      <c r="D18" s="145"/>
+      <c r="E18" s="145"/>
+      <c r="F18" s="145"/>
+      <c r="G18" s="145"/>
+      <c r="H18" s="145"/>
+      <c r="I18" s="145"/>
+      <c r="J18" s="145"/>
+      <c r="K18" s="145"/>
+      <c r="L18" s="145"/>
+      <c r="M18" s="145"/>
+      <c r="N18" s="145"/>
+      <c r="O18" s="145"/>
+      <c r="P18" s="145"/>
+      <c r="Q18" s="145"/>
+      <c r="R18" s="145"/>
     </row>
     <row r="19" spans="1:18" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="20" spans="1:18" ht="12.75" thickTop="1" x14ac:dyDescent="0.4">
@@ -4500,41 +4510,41 @@
       </c>
       <c r="B20" s="109"/>
       <c r="C20" s="109"/>
-      <c r="D20" s="140"/>
-      <c r="E20" s="141"/>
-      <c r="F20" s="141"/>
-      <c r="G20" s="141"/>
-      <c r="H20" s="141"/>
-      <c r="I20" s="141"/>
-      <c r="J20" s="141"/>
-      <c r="K20" s="141"/>
-      <c r="L20" s="141"/>
-      <c r="M20" s="141"/>
-      <c r="N20" s="141"/>
-      <c r="O20" s="141"/>
-      <c r="P20" s="141"/>
-      <c r="Q20" s="141"/>
-      <c r="R20" s="142"/>
+      <c r="D20" s="135"/>
+      <c r="E20" s="136"/>
+      <c r="F20" s="136"/>
+      <c r="G20" s="136"/>
+      <c r="H20" s="136"/>
+      <c r="I20" s="136"/>
+      <c r="J20" s="136"/>
+      <c r="K20" s="136"/>
+      <c r="L20" s="136"/>
+      <c r="M20" s="136"/>
+      <c r="N20" s="136"/>
+      <c r="O20" s="136"/>
+      <c r="P20" s="136"/>
+      <c r="Q20" s="136"/>
+      <c r="R20" s="137"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A21" s="89"/>
       <c r="B21" s="90"/>
       <c r="C21" s="90"/>
-      <c r="D21" s="143"/>
-      <c r="E21" s="144"/>
-      <c r="F21" s="144"/>
-      <c r="G21" s="144"/>
-      <c r="H21" s="144"/>
-      <c r="I21" s="144"/>
-      <c r="J21" s="144"/>
-      <c r="K21" s="144"/>
-      <c r="L21" s="144"/>
-      <c r="M21" s="144"/>
-      <c r="N21" s="144"/>
-      <c r="O21" s="144"/>
-      <c r="P21" s="144"/>
-      <c r="Q21" s="144"/>
-      <c r="R21" s="145"/>
+      <c r="D21" s="138"/>
+      <c r="E21" s="139"/>
+      <c r="F21" s="139"/>
+      <c r="G21" s="139"/>
+      <c r="H21" s="139"/>
+      <c r="I21" s="139"/>
+      <c r="J21" s="139"/>
+      <c r="K21" s="139"/>
+      <c r="L21" s="139"/>
+      <c r="M21" s="139"/>
+      <c r="N21" s="139"/>
+      <c r="O21" s="139"/>
+      <c r="P21" s="139"/>
+      <c r="Q21" s="139"/>
+      <c r="R21" s="140"/>
     </row>
     <row r="22" spans="1:18" ht="5.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="89" t="s">
@@ -4983,21 +4993,21 @@
       <c r="A45" s="88" t="s">
         <v>17</v>
       </c>
-      <c r="B45" s="60"/>
-      <c r="C45" s="60"/>
-      <c r="D45" s="58"/>
-      <c r="E45" s="58"/>
-      <c r="F45" s="58"/>
-      <c r="G45" s="59"/>
-      <c r="H45" s="60" t="s">
+      <c r="B45" s="54"/>
+      <c r="C45" s="54"/>
+      <c r="D45" s="52"/>
+      <c r="E45" s="52"/>
+      <c r="F45" s="52"/>
+      <c r="G45" s="53"/>
+      <c r="H45" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="I45" s="60"/>
-      <c r="J45" s="60"/>
-      <c r="K45" s="58"/>
-      <c r="L45" s="58"/>
-      <c r="M45" s="58"/>
-      <c r="N45" s="59"/>
+      <c r="I45" s="54"/>
+      <c r="J45" s="54"/>
+      <c r="K45" s="52"/>
+      <c r="L45" s="52"/>
+      <c r="M45" s="52"/>
+      <c r="N45" s="53"/>
       <c r="O45" s="84"/>
       <c r="P45" s="84"/>
       <c r="Q45" s="84"/>
@@ -5007,31 +5017,31 @@
     <row r="47" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="48" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="24"/>
-      <c r="B48" s="61" t="s">
+      <c r="B48" s="55" t="s">
         <v>18</v>
       </c>
-      <c r="C48" s="61"/>
-      <c r="D48" s="61"/>
-      <c r="E48" s="61"/>
+      <c r="C48" s="55"/>
+      <c r="D48" s="55"/>
+      <c r="E48" s="55"/>
       <c r="F48" s="25"/>
-      <c r="G48" s="52" t="s">
+      <c r="G48" s="56" t="s">
         <v>36</v>
       </c>
-      <c r="H48" s="53"/>
-      <c r="I48" s="54"/>
+      <c r="H48" s="59"/>
+      <c r="I48" s="60"/>
       <c r="J48" s="24"/>
-      <c r="K48" s="61" t="s">
+      <c r="K48" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="L48" s="61"/>
-      <c r="M48" s="61"/>
-      <c r="N48" s="61"/>
+      <c r="L48" s="55"/>
+      <c r="M48" s="55"/>
+      <c r="N48" s="55"/>
       <c r="O48" s="25"/>
-      <c r="P48" s="52" t="s">
+      <c r="P48" s="56" t="s">
         <v>36</v>
       </c>
-      <c r="Q48" s="53"/>
-      <c r="R48" s="54"/>
+      <c r="Q48" s="59"/>
+      <c r="R48" s="60"/>
     </row>
     <row r="49" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="26"/>
@@ -5045,12 +5055,12 @@
       <c r="H49" s="51"/>
       <c r="I49" s="50"/>
       <c r="J49" s="29"/>
-      <c r="K49" s="55" t="s">
+      <c r="K49" s="61" t="s">
         <v>22</v>
       </c>
-      <c r="L49" s="56"/>
-      <c r="M49" s="56"/>
-      <c r="N49" s="57"/>
+      <c r="L49" s="62"/>
+      <c r="M49" s="62"/>
+      <c r="N49" s="63"/>
       <c r="O49" s="30"/>
       <c r="P49" s="48"/>
       <c r="Q49" s="51"/>
@@ -5338,10 +5348,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="O1" s="135"/>
-      <c r="P1" s="135"/>
-      <c r="Q1" s="135"/>
-      <c r="R1" s="135"/>
+      <c r="O1" s="141"/>
+      <c r="P1" s="141"/>
+      <c r="Q1" s="141"/>
+      <c r="R1" s="141"/>
     </row>
     <row r="2" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="O2" s="2"/>
@@ -5351,16 +5361,16 @@
     </row>
     <row r="3" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A3" s="3"/>
-      <c r="O3" s="136"/>
-      <c r="P3" s="136"/>
-      <c r="Q3" s="136"/>
-      <c r="R3" s="136"/>
+      <c r="O3" s="142"/>
+      <c r="P3" s="142"/>
+      <c r="Q3" s="142"/>
+      <c r="R3" s="142"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="O4" s="136"/>
-      <c r="P4" s="136"/>
-      <c r="Q4" s="136"/>
-      <c r="R4" s="136"/>
+      <c r="O4" s="142"/>
+      <c r="P4" s="142"/>
+      <c r="Q4" s="142"/>
+      <c r="R4" s="142"/>
     </row>
     <row r="5" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="N5" s="4"/>
@@ -5423,71 +5433,71 @@
       <c r="R10" s="8"/>
     </row>
     <row r="11" spans="1:18" ht="21" x14ac:dyDescent="0.4">
-      <c r="A11" s="137" t="s">
+      <c r="A11" s="143" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="137"/>
-      <c r="C11" s="137"/>
-      <c r="D11" s="137"/>
-      <c r="E11" s="137"/>
-      <c r="F11" s="137"/>
-      <c r="G11" s="137"/>
-      <c r="H11" s="137"/>
-      <c r="I11" s="137"/>
-      <c r="J11" s="137"/>
-      <c r="K11" s="137"/>
-      <c r="L11" s="137"/>
-      <c r="M11" s="137"/>
-      <c r="N11" s="137"/>
-      <c r="O11" s="137"/>
-      <c r="P11" s="137"/>
-      <c r="Q11" s="137"/>
-      <c r="R11" s="137"/>
+      <c r="B11" s="143"/>
+      <c r="C11" s="143"/>
+      <c r="D11" s="143"/>
+      <c r="E11" s="143"/>
+      <c r="F11" s="143"/>
+      <c r="G11" s="143"/>
+      <c r="H11" s="143"/>
+      <c r="I11" s="143"/>
+      <c r="J11" s="143"/>
+      <c r="K11" s="143"/>
+      <c r="L11" s="143"/>
+      <c r="M11" s="143"/>
+      <c r="N11" s="143"/>
+      <c r="O11" s="143"/>
+      <c r="P11" s="143"/>
+      <c r="Q11" s="143"/>
+      <c r="R11" s="143"/>
     </row>
     <row r="14" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="15" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A15" s="138" t="s">
+      <c r="A15" s="144" t="s">
         <v>1</v>
       </c>
-      <c r="B15" s="138"/>
-      <c r="C15" s="138"/>
-      <c r="D15" s="138"/>
-      <c r="E15" s="138"/>
-      <c r="F15" s="138"/>
-      <c r="G15" s="138"/>
-      <c r="H15" s="138"/>
-      <c r="I15" s="138"/>
-      <c r="J15" s="138"/>
-      <c r="K15" s="138"/>
-      <c r="L15" s="138"/>
-      <c r="M15" s="138"/>
-      <c r="N15" s="138"/>
-      <c r="O15" s="138"/>
-      <c r="P15" s="138"/>
-      <c r="Q15" s="138"/>
-      <c r="R15" s="138"/>
+      <c r="B15" s="144"/>
+      <c r="C15" s="144"/>
+      <c r="D15" s="144"/>
+      <c r="E15" s="144"/>
+      <c r="F15" s="144"/>
+      <c r="G15" s="144"/>
+      <c r="H15" s="144"/>
+      <c r="I15" s="144"/>
+      <c r="J15" s="144"/>
+      <c r="K15" s="144"/>
+      <c r="L15" s="144"/>
+      <c r="M15" s="144"/>
+      <c r="N15" s="144"/>
+      <c r="O15" s="144"/>
+      <c r="P15" s="144"/>
+      <c r="Q15" s="144"/>
+      <c r="R15" s="144"/>
     </row>
     <row r="18" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A18" s="139" t="s">
+      <c r="A18" s="145" t="s">
         <v>2</v>
       </c>
-      <c r="B18" s="139"/>
-      <c r="C18" s="139"/>
-      <c r="D18" s="139"/>
-      <c r="E18" s="139"/>
-      <c r="F18" s="139"/>
-      <c r="G18" s="139"/>
-      <c r="H18" s="139"/>
-      <c r="I18" s="139"/>
-      <c r="J18" s="139"/>
-      <c r="K18" s="139"/>
-      <c r="L18" s="139"/>
-      <c r="M18" s="139"/>
-      <c r="N18" s="139"/>
-      <c r="O18" s="139"/>
-      <c r="P18" s="139"/>
-      <c r="Q18" s="139"/>
-      <c r="R18" s="139"/>
+      <c r="B18" s="145"/>
+      <c r="C18" s="145"/>
+      <c r="D18" s="145"/>
+      <c r="E18" s="145"/>
+      <c r="F18" s="145"/>
+      <c r="G18" s="145"/>
+      <c r="H18" s="145"/>
+      <c r="I18" s="145"/>
+      <c r="J18" s="145"/>
+      <c r="K18" s="145"/>
+      <c r="L18" s="145"/>
+      <c r="M18" s="145"/>
+      <c r="N18" s="145"/>
+      <c r="O18" s="145"/>
+      <c r="P18" s="145"/>
+      <c r="Q18" s="145"/>
+      <c r="R18" s="145"/>
     </row>
     <row r="19" spans="1:18" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="20" spans="1:18" ht="12.75" thickTop="1" x14ac:dyDescent="0.4">
@@ -5496,41 +5506,41 @@
       </c>
       <c r="B20" s="109"/>
       <c r="C20" s="109"/>
-      <c r="D20" s="140"/>
-      <c r="E20" s="141"/>
-      <c r="F20" s="141"/>
-      <c r="G20" s="141"/>
-      <c r="H20" s="141"/>
-      <c r="I20" s="141"/>
-      <c r="J20" s="141"/>
-      <c r="K20" s="141"/>
-      <c r="L20" s="141"/>
-      <c r="M20" s="141"/>
-      <c r="N20" s="141"/>
-      <c r="O20" s="141"/>
-      <c r="P20" s="141"/>
-      <c r="Q20" s="141"/>
-      <c r="R20" s="142"/>
+      <c r="D20" s="135"/>
+      <c r="E20" s="136"/>
+      <c r="F20" s="136"/>
+      <c r="G20" s="136"/>
+      <c r="H20" s="136"/>
+      <c r="I20" s="136"/>
+      <c r="J20" s="136"/>
+      <c r="K20" s="136"/>
+      <c r="L20" s="136"/>
+      <c r="M20" s="136"/>
+      <c r="N20" s="136"/>
+      <c r="O20" s="136"/>
+      <c r="P20" s="136"/>
+      <c r="Q20" s="136"/>
+      <c r="R20" s="137"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A21" s="89"/>
       <c r="B21" s="90"/>
       <c r="C21" s="90"/>
-      <c r="D21" s="143"/>
-      <c r="E21" s="144"/>
-      <c r="F21" s="144"/>
-      <c r="G21" s="144"/>
-      <c r="H21" s="144"/>
-      <c r="I21" s="144"/>
-      <c r="J21" s="144"/>
-      <c r="K21" s="144"/>
-      <c r="L21" s="144"/>
-      <c r="M21" s="144"/>
-      <c r="N21" s="144"/>
-      <c r="O21" s="144"/>
-      <c r="P21" s="144"/>
-      <c r="Q21" s="144"/>
-      <c r="R21" s="145"/>
+      <c r="D21" s="138"/>
+      <c r="E21" s="139"/>
+      <c r="F21" s="139"/>
+      <c r="G21" s="139"/>
+      <c r="H21" s="139"/>
+      <c r="I21" s="139"/>
+      <c r="J21" s="139"/>
+      <c r="K21" s="139"/>
+      <c r="L21" s="139"/>
+      <c r="M21" s="139"/>
+      <c r="N21" s="139"/>
+      <c r="O21" s="139"/>
+      <c r="P21" s="139"/>
+      <c r="Q21" s="139"/>
+      <c r="R21" s="140"/>
     </row>
     <row r="22" spans="1:18" ht="5.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="89" t="s">
@@ -5981,21 +5991,21 @@
       <c r="A45" s="88" t="s">
         <v>17</v>
       </c>
-      <c r="B45" s="60"/>
-      <c r="C45" s="60"/>
-      <c r="D45" s="58"/>
-      <c r="E45" s="58"/>
-      <c r="F45" s="58"/>
-      <c r="G45" s="59"/>
-      <c r="H45" s="60" t="s">
+      <c r="B45" s="54"/>
+      <c r="C45" s="54"/>
+      <c r="D45" s="52"/>
+      <c r="E45" s="52"/>
+      <c r="F45" s="52"/>
+      <c r="G45" s="53"/>
+      <c r="H45" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="I45" s="60"/>
-      <c r="J45" s="60"/>
-      <c r="K45" s="58"/>
-      <c r="L45" s="58"/>
-      <c r="M45" s="58"/>
-      <c r="N45" s="59"/>
+      <c r="I45" s="54"/>
+      <c r="J45" s="54"/>
+      <c r="K45" s="52"/>
+      <c r="L45" s="52"/>
+      <c r="M45" s="52"/>
+      <c r="N45" s="53"/>
       <c r="O45" s="163"/>
       <c r="P45" s="164"/>
       <c r="Q45" s="164"/>
@@ -6004,13 +6014,13 @@
     <row r="46" spans="1:18" ht="20.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.4"/>
     <row r="47" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="48" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="52" t="s">
+      <c r="A48" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="B48" s="53"/>
-      <c r="C48" s="53"/>
-      <c r="D48" s="53"/>
-      <c r="E48" s="54"/>
+      <c r="B48" s="59"/>
+      <c r="C48" s="59"/>
+      <c r="D48" s="59"/>
+      <c r="E48" s="60"/>
       <c r="F48" s="158" t="s">
         <v>39</v>
       </c>
@@ -6019,13 +6029,13 @@
         <v>40</v>
       </c>
       <c r="I48" s="157"/>
-      <c r="J48" s="52" t="s">
+      <c r="J48" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="K48" s="53"/>
-      <c r="L48" s="53"/>
-      <c r="M48" s="53"/>
-      <c r="N48" s="54"/>
+      <c r="K48" s="59"/>
+      <c r="L48" s="59"/>
+      <c r="M48" s="59"/>
+      <c r="N48" s="60"/>
       <c r="O48" s="158" t="s">
         <v>39</v>
       </c>
@@ -6036,7 +6046,7 @@
       <c r="R48" s="157"/>
     </row>
     <row r="49" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="57" t="s">
+      <c r="A49" s="63" t="s">
         <v>21</v>
       </c>
       <c r="B49" s="149"/>
@@ -6047,7 +6057,7 @@
       <c r="G49" s="152"/>
       <c r="H49" s="153"/>
       <c r="I49" s="154"/>
-      <c r="J49" s="57" t="s">
+      <c r="J49" s="63" t="s">
         <v>22</v>
       </c>
       <c r="K49" s="149"/>
@@ -6060,7 +6070,7 @@
       <c r="R49" s="154"/>
     </row>
     <row r="50" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="57" t="s">
+      <c r="A50" s="63" t="s">
         <v>23</v>
       </c>
       <c r="B50" s="149"/>
@@ -6071,7 +6081,7 @@
       <c r="G50" s="152"/>
       <c r="H50" s="153"/>
       <c r="I50" s="154"/>
-      <c r="J50" s="57" t="s">
+      <c r="J50" s="63" t="s">
         <v>24</v>
       </c>
       <c r="K50" s="149"/>
@@ -6084,7 +6094,7 @@
       <c r="R50" s="154"/>
     </row>
     <row r="51" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="57" t="s">
+      <c r="A51" s="63" t="s">
         <v>25</v>
       </c>
       <c r="B51" s="149"/>
@@ -6095,20 +6105,20 @@
       <c r="G51" s="152"/>
       <c r="H51" s="153"/>
       <c r="I51" s="154"/>
-      <c r="J51" s="57" t="s">
+      <c r="J51" s="63" t="s">
         <v>26</v>
       </c>
       <c r="K51" s="46"/>
       <c r="L51" s="46"/>
       <c r="M51" s="46"/>
-      <c r="N51" s="55"/>
+      <c r="N51" s="61"/>
       <c r="O51" s="151"/>
       <c r="P51" s="152"/>
       <c r="Q51" s="153"/>
       <c r="R51" s="154"/>
     </row>
     <row r="52" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="57" t="s">
+      <c r="A52" s="63" t="s">
         <v>27</v>
       </c>
       <c r="B52" s="149"/>
@@ -6119,20 +6129,20 @@
       <c r="G52" s="152"/>
       <c r="H52" s="153"/>
       <c r="I52" s="154"/>
-      <c r="J52" s="57" t="s">
+      <c r="J52" s="63" t="s">
         <v>28</v>
       </c>
       <c r="K52" s="46"/>
       <c r="L52" s="46"/>
       <c r="M52" s="46"/>
-      <c r="N52" s="55"/>
+      <c r="N52" s="61"/>
       <c r="O52" s="48"/>
       <c r="P52" s="155"/>
       <c r="Q52" s="51"/>
       <c r="R52" s="50"/>
     </row>
     <row r="53" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="57" t="s">
+      <c r="A53" s="63" t="s">
         <v>29</v>
       </c>
       <c r="B53" s="149"/>
@@ -6143,7 +6153,7 @@
       <c r="G53" s="152"/>
       <c r="H53" s="153"/>
       <c r="I53" s="154"/>
-      <c r="J53" s="57" t="s">
+      <c r="J53" s="63" t="s">
         <v>30</v>
       </c>
       <c r="K53" s="149"/>
@@ -6156,7 +6166,7 @@
       <c r="R53" s="154"/>
     </row>
     <row r="54" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="57" t="s">
+      <c r="A54" s="63" t="s">
         <v>31</v>
       </c>
       <c r="B54" s="149"/>
@@ -6178,7 +6188,7 @@
       <c r="R54" s="33"/>
     </row>
     <row r="55" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="57" t="s">
+      <c r="A55" s="63" t="s">
         <v>32</v>
       </c>
       <c r="B55" s="149"/>
@@ -6200,7 +6210,7 @@
       <c r="R55" s="36"/>
     </row>
     <row r="56" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A56" s="57" t="s">
+      <c r="A56" s="63" t="s">
         <v>33</v>
       </c>
       <c r="B56" s="149"/>
@@ -6222,7 +6232,7 @@
       <c r="R56" s="36"/>
     </row>
     <row r="57" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="57" t="s">
+      <c r="A57" s="63" t="s">
         <v>34</v>
       </c>
       <c r="B57" s="149"/>
@@ -6359,10 +6369,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="O1" s="135"/>
-      <c r="P1" s="135"/>
-      <c r="Q1" s="135"/>
-      <c r="R1" s="135"/>
+      <c r="O1" s="141"/>
+      <c r="P1" s="141"/>
+      <c r="Q1" s="141"/>
+      <c r="R1" s="141"/>
     </row>
     <row r="2" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="O2" s="2"/>
@@ -6372,16 +6382,16 @@
     </row>
     <row r="3" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A3" s="3"/>
-      <c r="O3" s="136"/>
-      <c r="P3" s="136"/>
-      <c r="Q3" s="136"/>
-      <c r="R3" s="136"/>
+      <c r="O3" s="142"/>
+      <c r="P3" s="142"/>
+      <c r="Q3" s="142"/>
+      <c r="R3" s="142"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="O4" s="136"/>
-      <c r="P4" s="136"/>
-      <c r="Q4" s="136"/>
-      <c r="R4" s="136"/>
+      <c r="O4" s="142"/>
+      <c r="P4" s="142"/>
+      <c r="Q4" s="142"/>
+      <c r="R4" s="142"/>
     </row>
     <row r="5" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="N5" s="4"/>
@@ -6517,41 +6527,41 @@
       </c>
       <c r="B20" s="229"/>
       <c r="C20" s="230"/>
-      <c r="D20" s="140"/>
-      <c r="E20" s="141"/>
-      <c r="F20" s="141"/>
-      <c r="G20" s="141"/>
-      <c r="H20" s="141"/>
-      <c r="I20" s="141"/>
-      <c r="J20" s="141"/>
-      <c r="K20" s="141"/>
-      <c r="L20" s="141"/>
-      <c r="M20" s="141"/>
-      <c r="N20" s="141"/>
-      <c r="O20" s="141"/>
-      <c r="P20" s="141"/>
-      <c r="Q20" s="141"/>
-      <c r="R20" s="142"/>
+      <c r="D20" s="135"/>
+      <c r="E20" s="136"/>
+      <c r="F20" s="136"/>
+      <c r="G20" s="136"/>
+      <c r="H20" s="136"/>
+      <c r="I20" s="136"/>
+      <c r="J20" s="136"/>
+      <c r="K20" s="136"/>
+      <c r="L20" s="136"/>
+      <c r="M20" s="136"/>
+      <c r="N20" s="136"/>
+      <c r="O20" s="136"/>
+      <c r="P20" s="136"/>
+      <c r="Q20" s="136"/>
+      <c r="R20" s="137"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A21" s="231"/>
       <c r="B21" s="232"/>
       <c r="C21" s="233"/>
-      <c r="D21" s="143"/>
-      <c r="E21" s="144"/>
-      <c r="F21" s="144"/>
-      <c r="G21" s="144"/>
-      <c r="H21" s="144"/>
-      <c r="I21" s="144"/>
-      <c r="J21" s="144"/>
-      <c r="K21" s="144"/>
-      <c r="L21" s="144"/>
-      <c r="M21" s="144"/>
-      <c r="N21" s="144"/>
-      <c r="O21" s="144"/>
-      <c r="P21" s="144"/>
-      <c r="Q21" s="144"/>
-      <c r="R21" s="145"/>
+      <c r="D21" s="138"/>
+      <c r="E21" s="139"/>
+      <c r="F21" s="139"/>
+      <c r="G21" s="139"/>
+      <c r="H21" s="139"/>
+      <c r="I21" s="139"/>
+      <c r="J21" s="139"/>
+      <c r="K21" s="139"/>
+      <c r="L21" s="139"/>
+      <c r="M21" s="139"/>
+      <c r="N21" s="139"/>
+      <c r="O21" s="139"/>
+      <c r="P21" s="139"/>
+      <c r="Q21" s="139"/>
+      <c r="R21" s="140"/>
     </row>
     <row r="22" spans="1:18" ht="5.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="240" t="s">
@@ -7241,10 +7251,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="O1" s="135"/>
-      <c r="P1" s="135"/>
-      <c r="Q1" s="135"/>
-      <c r="R1" s="135"/>
+      <c r="O1" s="141"/>
+      <c r="P1" s="141"/>
+      <c r="Q1" s="141"/>
+      <c r="R1" s="141"/>
     </row>
     <row r="2" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="O2" s="2"/>
@@ -7254,16 +7264,16 @@
     </row>
     <row r="3" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A3" s="3"/>
-      <c r="O3" s="136"/>
-      <c r="P3" s="136"/>
-      <c r="Q3" s="136"/>
-      <c r="R3" s="136"/>
+      <c r="O3" s="142"/>
+      <c r="P3" s="142"/>
+      <c r="Q3" s="142"/>
+      <c r="R3" s="142"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="O4" s="136"/>
-      <c r="P4" s="136"/>
-      <c r="Q4" s="136"/>
-      <c r="R4" s="136"/>
+      <c r="O4" s="142"/>
+      <c r="P4" s="142"/>
+      <c r="Q4" s="142"/>
+      <c r="R4" s="142"/>
     </row>
     <row r="5" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="N5" s="4"/>
@@ -7326,71 +7336,71 @@
       <c r="R10" s="8"/>
     </row>
     <row r="11" spans="1:18" ht="21" x14ac:dyDescent="0.4">
-      <c r="A11" s="137" t="s">
+      <c r="A11" s="143" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="137"/>
-      <c r="C11" s="137"/>
-      <c r="D11" s="137"/>
-      <c r="E11" s="137"/>
-      <c r="F11" s="137"/>
-      <c r="G11" s="137"/>
-      <c r="H11" s="137"/>
-      <c r="I11" s="137"/>
-      <c r="J11" s="137"/>
-      <c r="K11" s="137"/>
-      <c r="L11" s="137"/>
-      <c r="M11" s="137"/>
-      <c r="N11" s="137"/>
-      <c r="O11" s="137"/>
-      <c r="P11" s="137"/>
-      <c r="Q11" s="137"/>
-      <c r="R11" s="137"/>
+      <c r="B11" s="143"/>
+      <c r="C11" s="143"/>
+      <c r="D11" s="143"/>
+      <c r="E11" s="143"/>
+      <c r="F11" s="143"/>
+      <c r="G11" s="143"/>
+      <c r="H11" s="143"/>
+      <c r="I11" s="143"/>
+      <c r="J11" s="143"/>
+      <c r="K11" s="143"/>
+      <c r="L11" s="143"/>
+      <c r="M11" s="143"/>
+      <c r="N11" s="143"/>
+      <c r="O11" s="143"/>
+      <c r="P11" s="143"/>
+      <c r="Q11" s="143"/>
+      <c r="R11" s="143"/>
     </row>
     <row r="14" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="15" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A15" s="138" t="s">
+      <c r="A15" s="144" t="s">
         <v>1</v>
       </c>
-      <c r="B15" s="138"/>
-      <c r="C15" s="138"/>
-      <c r="D15" s="138"/>
-      <c r="E15" s="138"/>
-      <c r="F15" s="138"/>
-      <c r="G15" s="138"/>
-      <c r="H15" s="138"/>
-      <c r="I15" s="138"/>
-      <c r="J15" s="138"/>
-      <c r="K15" s="138"/>
-      <c r="L15" s="138"/>
-      <c r="M15" s="138"/>
-      <c r="N15" s="138"/>
-      <c r="O15" s="138"/>
-      <c r="P15" s="138"/>
-      <c r="Q15" s="138"/>
-      <c r="R15" s="138"/>
+      <c r="B15" s="144"/>
+      <c r="C15" s="144"/>
+      <c r="D15" s="144"/>
+      <c r="E15" s="144"/>
+      <c r="F15" s="144"/>
+      <c r="G15" s="144"/>
+      <c r="H15" s="144"/>
+      <c r="I15" s="144"/>
+      <c r="J15" s="144"/>
+      <c r="K15" s="144"/>
+      <c r="L15" s="144"/>
+      <c r="M15" s="144"/>
+      <c r="N15" s="144"/>
+      <c r="O15" s="144"/>
+      <c r="P15" s="144"/>
+      <c r="Q15" s="144"/>
+      <c r="R15" s="144"/>
     </row>
     <row r="18" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A18" s="139" t="s">
+      <c r="A18" s="145" t="s">
         <v>2</v>
       </c>
-      <c r="B18" s="139"/>
-      <c r="C18" s="139"/>
-      <c r="D18" s="139"/>
-      <c r="E18" s="139"/>
-      <c r="F18" s="139"/>
-      <c r="G18" s="139"/>
-      <c r="H18" s="139"/>
-      <c r="I18" s="139"/>
-      <c r="J18" s="139"/>
-      <c r="K18" s="139"/>
-      <c r="L18" s="139"/>
-      <c r="M18" s="139"/>
-      <c r="N18" s="139"/>
-      <c r="O18" s="139"/>
-      <c r="P18" s="139"/>
-      <c r="Q18" s="139"/>
-      <c r="R18" s="139"/>
+      <c r="B18" s="145"/>
+      <c r="C18" s="145"/>
+      <c r="D18" s="145"/>
+      <c r="E18" s="145"/>
+      <c r="F18" s="145"/>
+      <c r="G18" s="145"/>
+      <c r="H18" s="145"/>
+      <c r="I18" s="145"/>
+      <c r="J18" s="145"/>
+      <c r="K18" s="145"/>
+      <c r="L18" s="145"/>
+      <c r="M18" s="145"/>
+      <c r="N18" s="145"/>
+      <c r="O18" s="145"/>
+      <c r="P18" s="145"/>
+      <c r="Q18" s="145"/>
+      <c r="R18" s="145"/>
     </row>
     <row r="19" spans="1:18" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="20" spans="1:18" ht="12.75" thickTop="1" x14ac:dyDescent="0.4">
@@ -7399,41 +7409,41 @@
       </c>
       <c r="B20" s="109"/>
       <c r="C20" s="109"/>
-      <c r="D20" s="140"/>
-      <c r="E20" s="141"/>
-      <c r="F20" s="141"/>
-      <c r="G20" s="141"/>
-      <c r="H20" s="141"/>
-      <c r="I20" s="141"/>
-      <c r="J20" s="141"/>
-      <c r="K20" s="141"/>
-      <c r="L20" s="141"/>
-      <c r="M20" s="141"/>
-      <c r="N20" s="141"/>
-      <c r="O20" s="141"/>
-      <c r="P20" s="141"/>
-      <c r="Q20" s="141"/>
-      <c r="R20" s="142"/>
+      <c r="D20" s="135"/>
+      <c r="E20" s="136"/>
+      <c r="F20" s="136"/>
+      <c r="G20" s="136"/>
+      <c r="H20" s="136"/>
+      <c r="I20" s="136"/>
+      <c r="J20" s="136"/>
+      <c r="K20" s="136"/>
+      <c r="L20" s="136"/>
+      <c r="M20" s="136"/>
+      <c r="N20" s="136"/>
+      <c r="O20" s="136"/>
+      <c r="P20" s="136"/>
+      <c r="Q20" s="136"/>
+      <c r="R20" s="137"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A21" s="89"/>
       <c r="B21" s="90"/>
       <c r="C21" s="90"/>
-      <c r="D21" s="143"/>
-      <c r="E21" s="144"/>
-      <c r="F21" s="144"/>
-      <c r="G21" s="144"/>
-      <c r="H21" s="144"/>
-      <c r="I21" s="144"/>
-      <c r="J21" s="144"/>
-      <c r="K21" s="144"/>
-      <c r="L21" s="144"/>
-      <c r="M21" s="144"/>
-      <c r="N21" s="144"/>
-      <c r="O21" s="144"/>
-      <c r="P21" s="144"/>
-      <c r="Q21" s="144"/>
-      <c r="R21" s="145"/>
+      <c r="D21" s="138"/>
+      <c r="E21" s="139"/>
+      <c r="F21" s="139"/>
+      <c r="G21" s="139"/>
+      <c r="H21" s="139"/>
+      <c r="I21" s="139"/>
+      <c r="J21" s="139"/>
+      <c r="K21" s="139"/>
+      <c r="L21" s="139"/>
+      <c r="M21" s="139"/>
+      <c r="N21" s="139"/>
+      <c r="O21" s="139"/>
+      <c r="P21" s="139"/>
+      <c r="Q21" s="139"/>
+      <c r="R21" s="140"/>
     </row>
     <row r="22" spans="1:18" ht="5.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="89" t="s">
@@ -7882,21 +7892,21 @@
       <c r="A45" s="88" t="s">
         <v>17</v>
       </c>
-      <c r="B45" s="60"/>
-      <c r="C45" s="60"/>
-      <c r="D45" s="58"/>
-      <c r="E45" s="58"/>
-      <c r="F45" s="58"/>
-      <c r="G45" s="59"/>
-      <c r="H45" s="60" t="s">
+      <c r="B45" s="54"/>
+      <c r="C45" s="54"/>
+      <c r="D45" s="52"/>
+      <c r="E45" s="52"/>
+      <c r="F45" s="52"/>
+      <c r="G45" s="53"/>
+      <c r="H45" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="I45" s="60"/>
-      <c r="J45" s="60"/>
-      <c r="K45" s="58"/>
-      <c r="L45" s="58"/>
-      <c r="M45" s="58"/>
-      <c r="N45" s="59"/>
+      <c r="I45" s="54"/>
+      <c r="J45" s="54"/>
+      <c r="K45" s="52"/>
+      <c r="L45" s="52"/>
+      <c r="M45" s="52"/>
+      <c r="N45" s="53"/>
       <c r="O45" s="84"/>
       <c r="P45" s="84"/>
       <c r="Q45" s="84"/>
@@ -8123,10 +8133,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="O1" s="135"/>
-      <c r="P1" s="135"/>
-      <c r="Q1" s="135"/>
-      <c r="R1" s="135"/>
+      <c r="O1" s="141"/>
+      <c r="P1" s="141"/>
+      <c r="Q1" s="141"/>
+      <c r="R1" s="141"/>
     </row>
     <row r="2" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="O2" s="2"/>
@@ -8136,16 +8146,16 @@
     </row>
     <row r="3" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A3" s="3"/>
-      <c r="O3" s="136"/>
-      <c r="P3" s="136"/>
-      <c r="Q3" s="136"/>
-      <c r="R3" s="136"/>
+      <c r="O3" s="142"/>
+      <c r="P3" s="142"/>
+      <c r="Q3" s="142"/>
+      <c r="R3" s="142"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="O4" s="136"/>
-      <c r="P4" s="136"/>
-      <c r="Q4" s="136"/>
-      <c r="R4" s="136"/>
+      <c r="O4" s="142"/>
+      <c r="P4" s="142"/>
+      <c r="Q4" s="142"/>
+      <c r="R4" s="142"/>
     </row>
     <row r="5" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="N5" s="4"/>
@@ -8208,71 +8218,71 @@
       <c r="R10" s="8"/>
     </row>
     <row r="11" spans="1:18" ht="21" x14ac:dyDescent="0.4">
-      <c r="A11" s="137" t="s">
+      <c r="A11" s="143" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="137"/>
-      <c r="C11" s="137"/>
-      <c r="D11" s="137"/>
-      <c r="E11" s="137"/>
-      <c r="F11" s="137"/>
-      <c r="G11" s="137"/>
-      <c r="H11" s="137"/>
-      <c r="I11" s="137"/>
-      <c r="J11" s="137"/>
-      <c r="K11" s="137"/>
-      <c r="L11" s="137"/>
-      <c r="M11" s="137"/>
-      <c r="N11" s="137"/>
-      <c r="O11" s="137"/>
-      <c r="P11" s="137"/>
-      <c r="Q11" s="137"/>
-      <c r="R11" s="137"/>
+      <c r="B11" s="143"/>
+      <c r="C11" s="143"/>
+      <c r="D11" s="143"/>
+      <c r="E11" s="143"/>
+      <c r="F11" s="143"/>
+      <c r="G11" s="143"/>
+      <c r="H11" s="143"/>
+      <c r="I11" s="143"/>
+      <c r="J11" s="143"/>
+      <c r="K11" s="143"/>
+      <c r="L11" s="143"/>
+      <c r="M11" s="143"/>
+      <c r="N11" s="143"/>
+      <c r="O11" s="143"/>
+      <c r="P11" s="143"/>
+      <c r="Q11" s="143"/>
+      <c r="R11" s="143"/>
     </row>
     <row r="14" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="15" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A15" s="138" t="s">
+      <c r="A15" s="144" t="s">
         <v>1</v>
       </c>
-      <c r="B15" s="138"/>
-      <c r="C15" s="138"/>
-      <c r="D15" s="138"/>
-      <c r="E15" s="138"/>
-      <c r="F15" s="138"/>
-      <c r="G15" s="138"/>
-      <c r="H15" s="138"/>
-      <c r="I15" s="138"/>
-      <c r="J15" s="138"/>
-      <c r="K15" s="138"/>
-      <c r="L15" s="138"/>
-      <c r="M15" s="138"/>
-      <c r="N15" s="138"/>
-      <c r="O15" s="138"/>
-      <c r="P15" s="138"/>
-      <c r="Q15" s="138"/>
-      <c r="R15" s="138"/>
+      <c r="B15" s="144"/>
+      <c r="C15" s="144"/>
+      <c r="D15" s="144"/>
+      <c r="E15" s="144"/>
+      <c r="F15" s="144"/>
+      <c r="G15" s="144"/>
+      <c r="H15" s="144"/>
+      <c r="I15" s="144"/>
+      <c r="J15" s="144"/>
+      <c r="K15" s="144"/>
+      <c r="L15" s="144"/>
+      <c r="M15" s="144"/>
+      <c r="N15" s="144"/>
+      <c r="O15" s="144"/>
+      <c r="P15" s="144"/>
+      <c r="Q15" s="144"/>
+      <c r="R15" s="144"/>
     </row>
     <row r="18" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A18" s="139" t="s">
+      <c r="A18" s="145" t="s">
         <v>2</v>
       </c>
-      <c r="B18" s="139"/>
-      <c r="C18" s="139"/>
-      <c r="D18" s="139"/>
-      <c r="E18" s="139"/>
-      <c r="F18" s="139"/>
-      <c r="G18" s="139"/>
-      <c r="H18" s="139"/>
-      <c r="I18" s="139"/>
-      <c r="J18" s="139"/>
-      <c r="K18" s="139"/>
-      <c r="L18" s="139"/>
-      <c r="M18" s="139"/>
-      <c r="N18" s="139"/>
-      <c r="O18" s="139"/>
-      <c r="P18" s="139"/>
-      <c r="Q18" s="139"/>
-      <c r="R18" s="139"/>
+      <c r="B18" s="145"/>
+      <c r="C18" s="145"/>
+      <c r="D18" s="145"/>
+      <c r="E18" s="145"/>
+      <c r="F18" s="145"/>
+      <c r="G18" s="145"/>
+      <c r="H18" s="145"/>
+      <c r="I18" s="145"/>
+      <c r="J18" s="145"/>
+      <c r="K18" s="145"/>
+      <c r="L18" s="145"/>
+      <c r="M18" s="145"/>
+      <c r="N18" s="145"/>
+      <c r="O18" s="145"/>
+      <c r="P18" s="145"/>
+      <c r="Q18" s="145"/>
+      <c r="R18" s="145"/>
     </row>
     <row r="19" spans="1:18" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="20" spans="1:18" ht="12.75" thickTop="1" x14ac:dyDescent="0.4">
@@ -8281,41 +8291,41 @@
       </c>
       <c r="B20" s="109"/>
       <c r="C20" s="109"/>
-      <c r="D20" s="140"/>
-      <c r="E20" s="141"/>
-      <c r="F20" s="141"/>
-      <c r="G20" s="141"/>
-      <c r="H20" s="141"/>
-      <c r="I20" s="141"/>
-      <c r="J20" s="141"/>
-      <c r="K20" s="141"/>
-      <c r="L20" s="141"/>
-      <c r="M20" s="141"/>
-      <c r="N20" s="141"/>
-      <c r="O20" s="141"/>
-      <c r="P20" s="141"/>
-      <c r="Q20" s="141"/>
-      <c r="R20" s="142"/>
+      <c r="D20" s="135"/>
+      <c r="E20" s="136"/>
+      <c r="F20" s="136"/>
+      <c r="G20" s="136"/>
+      <c r="H20" s="136"/>
+      <c r="I20" s="136"/>
+      <c r="J20" s="136"/>
+      <c r="K20" s="136"/>
+      <c r="L20" s="136"/>
+      <c r="M20" s="136"/>
+      <c r="N20" s="136"/>
+      <c r="O20" s="136"/>
+      <c r="P20" s="136"/>
+      <c r="Q20" s="136"/>
+      <c r="R20" s="137"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A21" s="89"/>
       <c r="B21" s="90"/>
       <c r="C21" s="90"/>
-      <c r="D21" s="143"/>
-      <c r="E21" s="144"/>
-      <c r="F21" s="144"/>
-      <c r="G21" s="144"/>
-      <c r="H21" s="144"/>
-      <c r="I21" s="144"/>
-      <c r="J21" s="144"/>
-      <c r="K21" s="144"/>
-      <c r="L21" s="144"/>
-      <c r="M21" s="144"/>
-      <c r="N21" s="144"/>
-      <c r="O21" s="144"/>
-      <c r="P21" s="144"/>
-      <c r="Q21" s="144"/>
-      <c r="R21" s="145"/>
+      <c r="D21" s="138"/>
+      <c r="E21" s="139"/>
+      <c r="F21" s="139"/>
+      <c r="G21" s="139"/>
+      <c r="H21" s="139"/>
+      <c r="I21" s="139"/>
+      <c r="J21" s="139"/>
+      <c r="K21" s="139"/>
+      <c r="L21" s="139"/>
+      <c r="M21" s="139"/>
+      <c r="N21" s="139"/>
+      <c r="O21" s="139"/>
+      <c r="P21" s="139"/>
+      <c r="Q21" s="139"/>
+      <c r="R21" s="140"/>
     </row>
     <row r="22" spans="1:18" ht="5.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="89" t="s">
@@ -8766,21 +8776,21 @@
       <c r="A45" s="88" t="s">
         <v>17</v>
       </c>
-      <c r="B45" s="60"/>
-      <c r="C45" s="60"/>
-      <c r="D45" s="58"/>
-      <c r="E45" s="58"/>
-      <c r="F45" s="58"/>
-      <c r="G45" s="59"/>
-      <c r="H45" s="60" t="s">
+      <c r="B45" s="54"/>
+      <c r="C45" s="54"/>
+      <c r="D45" s="52"/>
+      <c r="E45" s="52"/>
+      <c r="F45" s="52"/>
+      <c r="G45" s="53"/>
+      <c r="H45" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="I45" s="60"/>
-      <c r="J45" s="60"/>
-      <c r="K45" s="58"/>
-      <c r="L45" s="58"/>
-      <c r="M45" s="58"/>
-      <c r="N45" s="59"/>
+      <c r="I45" s="54"/>
+      <c r="J45" s="54"/>
+      <c r="K45" s="52"/>
+      <c r="L45" s="52"/>
+      <c r="M45" s="52"/>
+      <c r="N45" s="53"/>
       <c r="O45" s="163"/>
       <c r="P45" s="164"/>
       <c r="Q45" s="164"/>
@@ -9070,10 +9080,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="O1" s="135"/>
-      <c r="P1" s="135"/>
-      <c r="Q1" s="135"/>
-      <c r="R1" s="135"/>
+      <c r="O1" s="141"/>
+      <c r="P1" s="141"/>
+      <c r="Q1" s="141"/>
+      <c r="R1" s="141"/>
     </row>
     <row r="2" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="O2" s="2"/>
@@ -9083,16 +9093,16 @@
     </row>
     <row r="3" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A3" s="3"/>
-      <c r="O3" s="136"/>
-      <c r="P3" s="136"/>
-      <c r="Q3" s="136"/>
-      <c r="R3" s="136"/>
+      <c r="O3" s="142"/>
+      <c r="P3" s="142"/>
+      <c r="Q3" s="142"/>
+      <c r="R3" s="142"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="O4" s="136"/>
-      <c r="P4" s="136"/>
-      <c r="Q4" s="136"/>
-      <c r="R4" s="136"/>
+      <c r="O4" s="142"/>
+      <c r="P4" s="142"/>
+      <c r="Q4" s="142"/>
+      <c r="R4" s="142"/>
     </row>
     <row r="5" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="N5" s="4"/>
@@ -9228,41 +9238,41 @@
       </c>
       <c r="B20" s="109"/>
       <c r="C20" s="109"/>
-      <c r="D20" s="140"/>
-      <c r="E20" s="141"/>
-      <c r="F20" s="141"/>
-      <c r="G20" s="141"/>
-      <c r="H20" s="141"/>
-      <c r="I20" s="141"/>
-      <c r="J20" s="141"/>
-      <c r="K20" s="141"/>
-      <c r="L20" s="141"/>
-      <c r="M20" s="141"/>
-      <c r="N20" s="141"/>
-      <c r="O20" s="141"/>
-      <c r="P20" s="141"/>
-      <c r="Q20" s="141"/>
-      <c r="R20" s="142"/>
+      <c r="D20" s="135"/>
+      <c r="E20" s="136"/>
+      <c r="F20" s="136"/>
+      <c r="G20" s="136"/>
+      <c r="H20" s="136"/>
+      <c r="I20" s="136"/>
+      <c r="J20" s="136"/>
+      <c r="K20" s="136"/>
+      <c r="L20" s="136"/>
+      <c r="M20" s="136"/>
+      <c r="N20" s="136"/>
+      <c r="O20" s="136"/>
+      <c r="P20" s="136"/>
+      <c r="Q20" s="136"/>
+      <c r="R20" s="137"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A21" s="89"/>
       <c r="B21" s="90"/>
       <c r="C21" s="90"/>
-      <c r="D21" s="143"/>
-      <c r="E21" s="144"/>
-      <c r="F21" s="144"/>
-      <c r="G21" s="144"/>
-      <c r="H21" s="144"/>
-      <c r="I21" s="144"/>
-      <c r="J21" s="144"/>
-      <c r="K21" s="144"/>
-      <c r="L21" s="144"/>
-      <c r="M21" s="144"/>
-      <c r="N21" s="144"/>
-      <c r="O21" s="144"/>
-      <c r="P21" s="144"/>
-      <c r="Q21" s="144"/>
-      <c r="R21" s="145"/>
+      <c r="D21" s="138"/>
+      <c r="E21" s="139"/>
+      <c r="F21" s="139"/>
+      <c r="G21" s="139"/>
+      <c r="H21" s="139"/>
+      <c r="I21" s="139"/>
+      <c r="J21" s="139"/>
+      <c r="K21" s="139"/>
+      <c r="L21" s="139"/>
+      <c r="M21" s="139"/>
+      <c r="N21" s="139"/>
+      <c r="O21" s="139"/>
+      <c r="P21" s="139"/>
+      <c r="Q21" s="139"/>
+      <c r="R21" s="140"/>
     </row>
     <row r="22" spans="1:18" ht="5.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="89" t="s">
@@ -9711,21 +9721,21 @@
       <c r="A45" s="88" t="s">
         <v>17</v>
       </c>
-      <c r="B45" s="60"/>
-      <c r="C45" s="60"/>
-      <c r="D45" s="58"/>
-      <c r="E45" s="58"/>
-      <c r="F45" s="58"/>
-      <c r="G45" s="59"/>
-      <c r="H45" s="60" t="s">
+      <c r="B45" s="54"/>
+      <c r="C45" s="54"/>
+      <c r="D45" s="52"/>
+      <c r="E45" s="52"/>
+      <c r="F45" s="52"/>
+      <c r="G45" s="53"/>
+      <c r="H45" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="I45" s="60"/>
-      <c r="J45" s="60"/>
-      <c r="K45" s="58"/>
-      <c r="L45" s="58"/>
-      <c r="M45" s="58"/>
-      <c r="N45" s="59"/>
+      <c r="I45" s="54"/>
+      <c r="J45" s="54"/>
+      <c r="K45" s="52"/>
+      <c r="L45" s="52"/>
+      <c r="M45" s="52"/>
+      <c r="N45" s="53"/>
       <c r="O45" s="84"/>
       <c r="P45" s="84"/>
       <c r="Q45" s="84"/>
@@ -10081,10 +10091,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="O1" s="135"/>
-      <c r="P1" s="135"/>
-      <c r="Q1" s="135"/>
-      <c r="R1" s="135"/>
+      <c r="O1" s="141"/>
+      <c r="P1" s="141"/>
+      <c r="Q1" s="141"/>
+      <c r="R1" s="141"/>
     </row>
     <row r="2" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="O2" s="2"/>
@@ -10094,16 +10104,16 @@
     </row>
     <row r="3" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A3" s="3"/>
-      <c r="O3" s="136"/>
-      <c r="P3" s="136"/>
-      <c r="Q3" s="136"/>
-      <c r="R3" s="136"/>
+      <c r="O3" s="142"/>
+      <c r="P3" s="142"/>
+      <c r="Q3" s="142"/>
+      <c r="R3" s="142"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="O4" s="136"/>
-      <c r="P4" s="136"/>
-      <c r="Q4" s="136"/>
-      <c r="R4" s="136"/>
+      <c r="O4" s="142"/>
+      <c r="P4" s="142"/>
+      <c r="Q4" s="142"/>
+      <c r="R4" s="142"/>
     </row>
     <row r="5" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="N5" s="4"/>
@@ -10239,41 +10249,41 @@
       </c>
       <c r="B20" s="109"/>
       <c r="C20" s="109"/>
-      <c r="D20" s="140"/>
-      <c r="E20" s="141"/>
-      <c r="F20" s="141"/>
-      <c r="G20" s="141"/>
-      <c r="H20" s="141"/>
-      <c r="I20" s="141"/>
-      <c r="J20" s="141"/>
-      <c r="K20" s="141"/>
-      <c r="L20" s="141"/>
-      <c r="M20" s="141"/>
-      <c r="N20" s="141"/>
-      <c r="O20" s="141"/>
-      <c r="P20" s="141"/>
-      <c r="Q20" s="141"/>
-      <c r="R20" s="142"/>
+      <c r="D20" s="135"/>
+      <c r="E20" s="136"/>
+      <c r="F20" s="136"/>
+      <c r="G20" s="136"/>
+      <c r="H20" s="136"/>
+      <c r="I20" s="136"/>
+      <c r="J20" s="136"/>
+      <c r="K20" s="136"/>
+      <c r="L20" s="136"/>
+      <c r="M20" s="136"/>
+      <c r="N20" s="136"/>
+      <c r="O20" s="136"/>
+      <c r="P20" s="136"/>
+      <c r="Q20" s="136"/>
+      <c r="R20" s="137"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A21" s="89"/>
       <c r="B21" s="90"/>
       <c r="C21" s="90"/>
-      <c r="D21" s="143"/>
-      <c r="E21" s="144"/>
-      <c r="F21" s="144"/>
-      <c r="G21" s="144"/>
-      <c r="H21" s="144"/>
-      <c r="I21" s="144"/>
-      <c r="J21" s="144"/>
-      <c r="K21" s="144"/>
-      <c r="L21" s="144"/>
-      <c r="M21" s="144"/>
-      <c r="N21" s="144"/>
-      <c r="O21" s="144"/>
-      <c r="P21" s="144"/>
-      <c r="Q21" s="144"/>
-      <c r="R21" s="145"/>
+      <c r="D21" s="138"/>
+      <c r="E21" s="139"/>
+      <c r="F21" s="139"/>
+      <c r="G21" s="139"/>
+      <c r="H21" s="139"/>
+      <c r="I21" s="139"/>
+      <c r="J21" s="139"/>
+      <c r="K21" s="139"/>
+      <c r="L21" s="139"/>
+      <c r="M21" s="139"/>
+      <c r="N21" s="139"/>
+      <c r="O21" s="139"/>
+      <c r="P21" s="139"/>
+      <c r="Q21" s="139"/>
+      <c r="R21" s="140"/>
     </row>
     <row r="22" spans="1:18" ht="5.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="89" t="s">
@@ -10722,21 +10732,21 @@
       <c r="A45" s="88" t="s">
         <v>17</v>
       </c>
-      <c r="B45" s="60"/>
-      <c r="C45" s="60"/>
-      <c r="D45" s="58"/>
-      <c r="E45" s="58"/>
-      <c r="F45" s="58"/>
-      <c r="G45" s="59"/>
-      <c r="H45" s="60" t="s">
+      <c r="B45" s="54"/>
+      <c r="C45" s="54"/>
+      <c r="D45" s="52"/>
+      <c r="E45" s="52"/>
+      <c r="F45" s="52"/>
+      <c r="G45" s="53"/>
+      <c r="H45" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="I45" s="60"/>
-      <c r="J45" s="60"/>
-      <c r="K45" s="58"/>
-      <c r="L45" s="58"/>
-      <c r="M45" s="58"/>
-      <c r="N45" s="59"/>
+      <c r="I45" s="54"/>
+      <c r="J45" s="54"/>
+      <c r="K45" s="52"/>
+      <c r="L45" s="52"/>
+      <c r="M45" s="52"/>
+      <c r="N45" s="53"/>
       <c r="O45" s="84"/>
       <c r="P45" s="84"/>
       <c r="Q45" s="84"/>
@@ -11094,7 +11104,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8AD63A3-91EE-404F-99BB-96179FDB1D0B}">
-  <dimension ref="B2:N28"/>
+  <dimension ref="B2:N29"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="15" width="4.625" customWidth="1"/>
@@ -11486,7 +11496,7 @@
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B25" s="299" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="C25" s="299"/>
       <c r="D25" s="299"/>
@@ -11501,13 +11511,13 @@
       <c r="M25" s="300"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B26" s="301" t="s">
-        <v>69</v>
-      </c>
-      <c r="C26" s="302"/>
-      <c r="D26" s="303"/>
-      <c r="E26" s="304"/>
-      <c r="F26" s="305"/>
+      <c r="B26" s="299" t="s">
+        <v>67</v>
+      </c>
+      <c r="C26" s="299"/>
+      <c r="D26" s="299"/>
+      <c r="E26" s="300"/>
+      <c r="F26" s="300"/>
       <c r="I26" s="299" t="s">
         <v>72</v>
       </c>
@@ -11518,24 +11528,33 @@
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B27" s="301" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C27" s="302"/>
       <c r="D27" s="303"/>
-      <c r="E27" s="306"/>
-      <c r="F27" s="307"/>
+      <c r="E27" s="304"/>
+      <c r="F27" s="305"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B28" s="299" t="s">
+      <c r="B28" s="301" t="s">
+        <v>70</v>
+      </c>
+      <c r="C28" s="302"/>
+      <c r="D28" s="303"/>
+      <c r="E28" s="306"/>
+      <c r="F28" s="307"/>
+    </row>
+    <row r="29" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B29" s="299" t="s">
         <v>71</v>
       </c>
-      <c r="C28" s="299"/>
-      <c r="D28" s="299"/>
-      <c r="E28" s="300"/>
-      <c r="F28" s="300"/>
+      <c r="C29" s="299"/>
+      <c r="D29" s="299"/>
+      <c r="E29" s="300"/>
+      <c r="F29" s="300"/>
     </row>
   </sheetData>
-  <mergeCells count="96">
+  <mergeCells count="98">
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="E20:F20"/>
     <mergeCell ref="B11:C12"/>
@@ -11610,28 +11629,30 @@
     <mergeCell ref="E23:F23"/>
     <mergeCell ref="I25:K25"/>
     <mergeCell ref="L25:M25"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="E26:F26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="L26:M26"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="L23:M23"/>
-    <mergeCell ref="I24:K24"/>
-    <mergeCell ref="L24:M24"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="E29:F29"/>
     <mergeCell ref="I20:K20"/>
     <mergeCell ref="L20:M20"/>
     <mergeCell ref="I21:K21"/>
     <mergeCell ref="L21:M21"/>
     <mergeCell ref="I22:K22"/>
     <mergeCell ref="L22:M22"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="L24:M24"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
